--- a/data/EVALUACIONES/SALTOS/SALTOS.xlsx
+++ b/data/EVALUACIONES/SALTOS/SALTOS.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30411"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\ADARVE JUV D.H\App_Rendimiento_Futbol\data\EVALUACIONES\SALTOS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83BE7A00-79D9-456D-A745-A053E3BDD699}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="13_ncr:1_{83BE7A00-79D9-456D-A745-A053E3BDD699}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{15F8E504-8D54-4139-BD16-39D7C826A6EB}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{BBC13A56-B43E-4445-9420-3EF783FE99BE}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="610" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="592" uniqueCount="47">
   <si>
     <t>CMJ</t>
   </si>
@@ -88,9 +88,6 @@
   </si>
   <si>
     <t>Alberto_Benedicto_Carpintero</t>
-  </si>
-  <si>
-    <t>Alejandro_Garcia_Gumiel</t>
   </si>
   <si>
     <t>Alex_Balbure</t>
@@ -223,13 +220,13 @@
   </cellStyles>
   <dxfs count="3">
     <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
       <numFmt numFmtId="26" formatCode="h:mm:ss"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -245,10 +242,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{AEC1F9C7-B230-4260-879C-528A4474077A}" name="Tabla1" displayName="Tabla1" ref="A1:P199" totalsRowShown="0">
-  <autoFilter ref="A1:P199" xr:uid="{AEC1F9C7-B230-4260-879C-528A4474077A}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{AEC1F9C7-B230-4260-879C-528A4474077A}" name="Tabla1" displayName="Tabla1" ref="A1:P193" totalsRowShown="0">
+  <autoFilter ref="A1:P193" xr:uid="{AEC1F9C7-B230-4260-879C-528A4474077A}"/>
   <tableColumns count="16">
-    <tableColumn id="1" xr3:uid="{4BA730B7-AA1C-42F2-810B-84C2DD5A4C89}" name="Nombre de atleta" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{4BA730B7-AA1C-42F2-810B-84C2DD5A4C89}" name="Nombre de atleta" dataDxfId="2"/>
     <tableColumn id="2" xr3:uid="{495E4E94-11B3-43E5-ADB9-7D34A29B6091}" name="ID de salto"/>
     <tableColumn id="3" xr3:uid="{BF9032F0-6CCE-4FB6-A2C3-3C4A09D220EA}" name="Tipo"/>
     <tableColumn id="4" xr3:uid="{FF2A5709-4220-4467-B002-B7857FD2EA73}" name="TC"/>
@@ -261,8 +258,8 @@
     <tableColumn id="11" xr3:uid="{96E7B070-2983-48C8-98D5-E5700599E42F}" name="Rigidez"/>
     <tableColumn id="12" xr3:uid="{8C258C0D-795E-44D4-AC53-688CA4AE0D00}" name="Velocidad inicial"/>
     <tableColumn id="13" xr3:uid="{66029D8C-02BB-468B-8793-A94CE40D530E}" name="RSI"/>
-    <tableColumn id="14" xr3:uid="{847C353E-4493-4EA7-9AF0-AB72ED266170}" name="Fecha y hora" dataDxfId="2"/>
-    <tableColumn id="15" xr3:uid="{E4D8B504-2B0D-4F13-B89C-C4B21905A819}" name="DescripciÃ³n" dataDxfId="1"/>
+    <tableColumn id="14" xr3:uid="{847C353E-4493-4EA7-9AF0-AB72ED266170}" name="Fecha y hora" dataDxfId="1"/>
+    <tableColumn id="15" xr3:uid="{E4D8B504-2B0D-4F13-B89C-C4B21905A819}" name="DescripciÃ³n" dataDxfId="0"/>
     <tableColumn id="16" xr3:uid="{D57FE126-347C-42BD-AC9F-87A4942E87E8}" name="Simulado"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -566,7 +563,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5FF0B100-72AE-4E6A-8897-D79B621AF892}">
-  <dimension ref="A1:P199"/>
+  <dimension ref="A1:P193"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19.44140625" bestFit="1" customWidth="1"/>
@@ -1003,12 +1000,12 @@
         <v>0.87891203703703702</v>
       </c>
     </row>
-    <row r="10" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>21</v>
       </c>
       <c r="B10">
-        <v>166</v>
+        <v>40</v>
       </c>
       <c r="C10" t="s">
         <v>0</v>
@@ -1017,7 +1014,7 @@
         <v>0</v>
       </c>
       <c r="E10">
-        <v>0.504</v>
+        <v>0.57899999999999996</v>
       </c>
       <c r="F10">
         <v>0</v>
@@ -1026,10 +1023,10 @@
         <v>0</v>
       </c>
       <c r="H10">
-        <v>31.152999999999999</v>
+        <v>41.158000000000001</v>
       </c>
       <c r="I10">
-        <v>847.55899999999997</v>
+        <v>974.2</v>
       </c>
       <c r="J10" t="s">
         <v>17</v>
@@ -1038,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="L10">
-        <v>2.472</v>
+        <v>2.8420000000000001</v>
       </c>
       <c r="M10">
         <v>0</v>
@@ -1047,15 +1044,15 @@
         <v>46247</v>
       </c>
       <c r="O10" s="3">
-        <v>0.86682870370370368</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
+        <v>0.85290509259259262</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>21</v>
       </c>
       <c r="B11">
-        <v>170</v>
+        <v>43</v>
       </c>
       <c r="C11" t="s">
         <v>0</v>
@@ -1064,7 +1061,7 @@
         <v>0</v>
       </c>
       <c r="E11">
-        <v>0.51</v>
+        <v>0.56999999999999995</v>
       </c>
       <c r="F11">
         <v>0</v>
@@ -1073,10 +1070,10 @@
         <v>0</v>
       </c>
       <c r="H11">
-        <v>31.846</v>
+        <v>39.793999999999997</v>
       </c>
       <c r="I11">
-        <v>856.93499999999995</v>
+        <v>957.923</v>
       </c>
       <c r="J11" t="s">
         <v>17</v>
@@ -1085,7 +1082,7 @@
         <v>0</v>
       </c>
       <c r="L11">
-        <v>2.5</v>
+        <v>2.794</v>
       </c>
       <c r="M11">
         <v>0</v>
@@ -1094,24 +1091,24 @@
         <v>46247</v>
       </c>
       <c r="O11" s="3">
-        <v>0.86849537037037039</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
+        <v>0.85362268518518514</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>21</v>
       </c>
       <c r="B12">
-        <v>174</v>
+        <v>46</v>
       </c>
       <c r="C12" t="s">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="D12">
         <v>0</v>
       </c>
       <c r="E12">
-        <v>0.33100000000000002</v>
+        <v>0.55400000000000005</v>
       </c>
       <c r="F12">
         <v>0</v>
@@ -1120,10 +1117,10 @@
         <v>0</v>
       </c>
       <c r="H12">
-        <v>13.47</v>
+        <v>37.637999999999998</v>
       </c>
       <c r="I12">
-        <v>557.322</v>
+        <v>931.61</v>
       </c>
       <c r="J12" t="s">
         <v>17</v>
@@ -1132,7 +1129,7 @@
         <v>0</v>
       </c>
       <c r="L12">
-        <v>1.6259999999999999</v>
+        <v>2.7170000000000001</v>
       </c>
       <c r="M12">
         <v>0</v>
@@ -1141,15 +1138,15 @@
         <v>46247</v>
       </c>
       <c r="O12" s="3">
-        <v>0.86954861111111115</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
+        <v>0.85415509259259259</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>21</v>
       </c>
       <c r="B13">
-        <v>178</v>
+        <v>49</v>
       </c>
       <c r="C13" t="s">
         <v>19</v>
@@ -1158,7 +1155,7 @@
         <v>0</v>
       </c>
       <c r="E13">
-        <v>0.38500000000000001</v>
+        <v>0.40899999999999997</v>
       </c>
       <c r="F13">
         <v>0</v>
@@ -1167,10 +1164,10 @@
         <v>0</v>
       </c>
       <c r="H13">
-        <v>18.189</v>
+        <v>20.49</v>
       </c>
       <c r="I13">
-        <v>647.62800000000004</v>
+        <v>687.36699999999996</v>
       </c>
       <c r="J13" t="s">
         <v>17</v>
@@ -1179,7 +1176,7 @@
         <v>0</v>
       </c>
       <c r="L13">
-        <v>1.889</v>
+        <v>2.0049999999999999</v>
       </c>
       <c r="M13">
         <v>0</v>
@@ -1188,24 +1185,24 @@
         <v>46247</v>
       </c>
       <c r="O13" s="3">
-        <v>0.87031250000000004</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
+        <v>0.85488425925925926</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>21</v>
       </c>
       <c r="B14">
-        <v>182</v>
+        <v>52</v>
       </c>
       <c r="C14" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D14">
         <v>0</v>
       </c>
       <c r="E14">
-        <v>0.35299999999999998</v>
+        <v>0.41499999999999998</v>
       </c>
       <c r="F14">
         <v>0</v>
@@ -1214,10 +1211,10 @@
         <v>0</v>
       </c>
       <c r="H14">
-        <v>15.297000000000001</v>
+        <v>21.14</v>
       </c>
       <c r="I14">
-        <v>593.92600000000004</v>
+        <v>698.19600000000003</v>
       </c>
       <c r="J14" t="s">
         <v>17</v>
@@ -1226,7 +1223,7 @@
         <v>0</v>
       </c>
       <c r="L14">
-        <v>1.732</v>
+        <v>2.0369999999999999</v>
       </c>
       <c r="M14">
         <v>0</v>
@@ -1235,24 +1232,24 @@
         <v>46247</v>
       </c>
       <c r="O14" s="3">
-        <v>0.87124999999999997</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
+        <v>0.85574074074074069</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>21</v>
       </c>
       <c r="B15">
-        <v>186</v>
+        <v>55</v>
       </c>
       <c r="C15" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D15">
         <v>0</v>
       </c>
       <c r="E15">
-        <v>0.36499999999999999</v>
+        <v>0.441</v>
       </c>
       <c r="F15">
         <v>0</v>
@@ -1261,10 +1258,10 @@
         <v>0</v>
       </c>
       <c r="H15">
-        <v>16.335999999999999</v>
+        <v>23.852</v>
       </c>
       <c r="I15">
-        <v>613.755</v>
+        <v>741.62099999999998</v>
       </c>
       <c r="J15" t="s">
         <v>17</v>
@@ -1273,7 +1270,7 @@
         <v>0</v>
       </c>
       <c r="L15">
-        <v>1.79</v>
+        <v>2.1629999999999998</v>
       </c>
       <c r="M15">
         <v>0</v>
@@ -1282,24 +1279,24 @@
         <v>46247</v>
       </c>
       <c r="O15" s="3">
-        <v>0.8718055555555555</v>
+        <v>0.85622685185185188</v>
       </c>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B16">
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="C16" t="s">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="D16">
         <v>0</v>
       </c>
       <c r="E16">
-        <v>0.57899999999999996</v>
+        <v>0.38200000000000001</v>
       </c>
       <c r="F16">
         <v>0</v>
@@ -1308,10 +1305,10 @@
         <v>0</v>
       </c>
       <c r="H16">
-        <v>41.158000000000001</v>
+        <v>17.869</v>
       </c>
       <c r="I16">
-        <v>974.2</v>
+        <v>641.91099999999994</v>
       </c>
       <c r="J16" t="s">
         <v>17</v>
@@ -1320,7 +1317,7 @@
         <v>0</v>
       </c>
       <c r="L16">
-        <v>2.8420000000000001</v>
+        <v>1.8720000000000001</v>
       </c>
       <c r="M16">
         <v>0</v>
@@ -1329,24 +1326,24 @@
         <v>46247</v>
       </c>
       <c r="O16" s="3">
-        <v>0.85290509259259262</v>
+        <v>0.8568634259259259</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B17">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="C17" t="s">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="D17">
         <v>0</v>
       </c>
       <c r="E17">
-        <v>0.56999999999999995</v>
+        <v>0.35199999999999998</v>
       </c>
       <c r="F17">
         <v>0</v>
@@ -1355,10 +1352,10 @@
         <v>0</v>
       </c>
       <c r="H17">
-        <v>39.793999999999997</v>
+        <v>15.191000000000001</v>
       </c>
       <c r="I17">
-        <v>957.923</v>
+        <v>591.85400000000004</v>
       </c>
       <c r="J17" t="s">
         <v>17</v>
@@ -1367,7 +1364,7 @@
         <v>0</v>
       </c>
       <c r="L17">
-        <v>2.794</v>
+        <v>1.726</v>
       </c>
       <c r="M17">
         <v>0</v>
@@ -1376,24 +1373,24 @@
         <v>46247</v>
       </c>
       <c r="O17" s="3">
-        <v>0.85362268518518514</v>
+        <v>0.85738425925925921</v>
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B18">
-        <v>46</v>
+        <v>64</v>
       </c>
       <c r="C18" t="s">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="D18">
         <v>0</v>
       </c>
       <c r="E18">
-        <v>0.55400000000000005</v>
+        <v>0.307</v>
       </c>
       <c r="F18">
         <v>0</v>
@@ -1402,10 +1399,10 @@
         <v>0</v>
       </c>
       <c r="H18">
-        <v>37.637999999999998</v>
+        <v>11.542</v>
       </c>
       <c r="I18">
-        <v>931.61</v>
+        <v>515.90200000000004</v>
       </c>
       <c r="J18" t="s">
         <v>17</v>
@@ -1414,7 +1411,7 @@
         <v>0</v>
       </c>
       <c r="L18">
-        <v>2.7170000000000001</v>
+        <v>1.5049999999999999</v>
       </c>
       <c r="M18">
         <v>0</v>
@@ -1423,7 +1420,7 @@
         <v>46247</v>
       </c>
       <c r="O18" s="3">
-        <v>0.85415509259259259</v>
+        <v>0.85777777777777775</v>
       </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.3">
@@ -1431,16 +1428,16 @@
         <v>22</v>
       </c>
       <c r="B19">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="C19" t="s">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="D19">
         <v>0</v>
       </c>
       <c r="E19">
-        <v>0.40899999999999997</v>
+        <v>0.56899999999999995</v>
       </c>
       <c r="F19">
         <v>0</v>
@@ -1449,10 +1446,10 @@
         <v>0</v>
       </c>
       <c r="H19">
-        <v>20.49</v>
+        <v>39.747999999999998</v>
       </c>
       <c r="I19">
-        <v>687.36699999999996</v>
+        <v>957.37099999999998</v>
       </c>
       <c r="J19" t="s">
         <v>17</v>
@@ -1461,7 +1458,7 @@
         <v>0</v>
       </c>
       <c r="L19">
-        <v>2.0049999999999999</v>
+        <v>2.7930000000000001</v>
       </c>
       <c r="M19">
         <v>0</v>
@@ -1470,7 +1467,7 @@
         <v>46247</v>
       </c>
       <c r="O19" s="3">
-        <v>0.85488425925925926</v>
+        <v>0.85980324074074077</v>
       </c>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.3">
@@ -1478,16 +1475,16 @@
         <v>22</v>
       </c>
       <c r="B20">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="C20" t="s">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="D20">
         <v>0</v>
       </c>
       <c r="E20">
-        <v>0.41499999999999998</v>
+        <v>0.57799999999999996</v>
       </c>
       <c r="F20">
         <v>0</v>
@@ -1496,10 +1493,10 @@
         <v>0</v>
       </c>
       <c r="H20">
-        <v>21.14</v>
+        <v>40.966999999999999</v>
       </c>
       <c r="I20">
-        <v>698.19600000000003</v>
+        <v>971.94</v>
       </c>
       <c r="J20" t="s">
         <v>17</v>
@@ -1508,7 +1505,7 @@
         <v>0</v>
       </c>
       <c r="L20">
-        <v>2.0369999999999999</v>
+        <v>2.835</v>
       </c>
       <c r="M20">
         <v>0</v>
@@ -1517,7 +1514,7 @@
         <v>46247</v>
       </c>
       <c r="O20" s="3">
-        <v>0.85574074074074069</v>
+        <v>0.86054398148148148</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.3">
@@ -1525,16 +1522,16 @@
         <v>22</v>
       </c>
       <c r="B21">
-        <v>55</v>
+        <v>71</v>
       </c>
       <c r="C21" t="s">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="D21">
         <v>0</v>
       </c>
       <c r="E21">
-        <v>0.441</v>
+        <v>0.58399999999999996</v>
       </c>
       <c r="F21">
         <v>0</v>
@@ -1543,10 +1540,10 @@
         <v>0</v>
       </c>
       <c r="H21">
-        <v>23.852</v>
+        <v>41.871000000000002</v>
       </c>
       <c r="I21">
-        <v>741.62099999999998</v>
+        <v>982.60799999999995</v>
       </c>
       <c r="J21" t="s">
         <v>17</v>
@@ -1555,7 +1552,7 @@
         <v>0</v>
       </c>
       <c r="L21">
-        <v>2.1629999999999998</v>
+        <v>2.8660000000000001</v>
       </c>
       <c r="M21">
         <v>0</v>
@@ -1564,7 +1561,7 @@
         <v>46247</v>
       </c>
       <c r="O21" s="3">
-        <v>0.85622685185185188</v>
+        <v>0.86149305555555555</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.3">
@@ -1572,10 +1569,10 @@
         <v>22</v>
       </c>
       <c r="B22">
-        <v>58</v>
+        <v>74</v>
       </c>
       <c r="C22" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D22">
         <v>0</v>
@@ -1590,10 +1587,10 @@
         <v>0</v>
       </c>
       <c r="H22">
-        <v>17.869</v>
+        <v>17.864999999999998</v>
       </c>
       <c r="I22">
-        <v>641.91099999999994</v>
+        <v>641.84400000000005</v>
       </c>
       <c r="J22" t="s">
         <v>17</v>
@@ -1611,7 +1608,7 @@
         <v>46247</v>
       </c>
       <c r="O22" s="3">
-        <v>0.8568634259259259</v>
+        <v>0.86275462962962968</v>
       </c>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.3">
@@ -1619,16 +1616,16 @@
         <v>22</v>
       </c>
       <c r="B23">
-        <v>61</v>
+        <v>77</v>
       </c>
       <c r="C23" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D23">
         <v>0</v>
       </c>
       <c r="E23">
-        <v>0.35199999999999998</v>
+        <v>0.37</v>
       </c>
       <c r="F23">
         <v>0</v>
@@ -1637,10 +1634,10 @@
         <v>0</v>
       </c>
       <c r="H23">
-        <v>15.191000000000001</v>
+        <v>16.771000000000001</v>
       </c>
       <c r="I23">
-        <v>591.85400000000004</v>
+        <v>621.88</v>
       </c>
       <c r="J23" t="s">
         <v>17</v>
@@ -1649,7 +1646,7 @@
         <v>0</v>
       </c>
       <c r="L23">
-        <v>1.726</v>
+        <v>1.8140000000000001</v>
       </c>
       <c r="M23">
         <v>0</v>
@@ -1658,7 +1655,7 @@
         <v>46247</v>
       </c>
       <c r="O23" s="3">
-        <v>0.85738425925925921</v>
+        <v>0.86390046296296297</v>
       </c>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.3">
@@ -1666,16 +1663,16 @@
         <v>22</v>
       </c>
       <c r="B24">
-        <v>64</v>
+        <v>80</v>
       </c>
       <c r="C24" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D24">
         <v>0</v>
       </c>
       <c r="E24">
-        <v>0.307</v>
+        <v>0.42299999999999999</v>
       </c>
       <c r="F24">
         <v>0</v>
@@ -1684,10 +1681,10 @@
         <v>0</v>
       </c>
       <c r="H24">
-        <v>11.542</v>
+        <v>21.901</v>
       </c>
       <c r="I24">
-        <v>515.90200000000004</v>
+        <v>710.65300000000002</v>
       </c>
       <c r="J24" t="s">
         <v>17</v>
@@ -1696,7 +1693,7 @@
         <v>0</v>
       </c>
       <c r="L24">
-        <v>1.5049999999999999</v>
+        <v>2.073</v>
       </c>
       <c r="M24">
         <v>0</v>
@@ -1705,24 +1702,24 @@
         <v>46247</v>
       </c>
       <c r="O24" s="3">
-        <v>0.85777777777777775</v>
+        <v>0.86471064814814813</v>
       </c>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B25">
-        <v>65</v>
+        <v>83</v>
       </c>
       <c r="C25" t="s">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="D25">
         <v>0</v>
       </c>
       <c r="E25">
-        <v>0.56899999999999995</v>
+        <v>0.41799999999999998</v>
       </c>
       <c r="F25">
         <v>0</v>
@@ -1731,10 +1728,10 @@
         <v>0</v>
       </c>
       <c r="H25">
-        <v>39.747999999999998</v>
+        <v>21.474</v>
       </c>
       <c r="I25">
-        <v>957.37099999999998</v>
+        <v>703.68499999999995</v>
       </c>
       <c r="J25" t="s">
         <v>17</v>
@@ -1743,7 +1740,7 @@
         <v>0</v>
       </c>
       <c r="L25">
-        <v>2.7930000000000001</v>
+        <v>2.0529999999999999</v>
       </c>
       <c r="M25">
         <v>0</v>
@@ -1752,24 +1749,24 @@
         <v>46247</v>
       </c>
       <c r="O25" s="3">
-        <v>0.85980324074074077</v>
+        <v>0.86552083333333329</v>
       </c>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B26">
-        <v>68</v>
+        <v>86</v>
       </c>
       <c r="C26" t="s">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="D26">
         <v>0</v>
       </c>
       <c r="E26">
-        <v>0.57799999999999996</v>
+        <v>0.41399999999999998</v>
       </c>
       <c r="F26">
         <v>0</v>
@@ -1778,10 +1775,10 @@
         <v>0</v>
       </c>
       <c r="H26">
-        <v>40.966999999999999</v>
+        <v>20.981000000000002</v>
       </c>
       <c r="I26">
-        <v>971.94</v>
+        <v>695.55899999999997</v>
       </c>
       <c r="J26" t="s">
         <v>17</v>
@@ -1790,7 +1787,7 @@
         <v>0</v>
       </c>
       <c r="L26">
-        <v>2.835</v>
+        <v>2.0289999999999999</v>
       </c>
       <c r="M26">
         <v>0</v>
@@ -1799,24 +1796,24 @@
         <v>46247</v>
       </c>
       <c r="O26" s="3">
-        <v>0.86054398148148148</v>
+        <v>0.86618055555555551</v>
       </c>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B27">
-        <v>71</v>
+        <v>89</v>
       </c>
       <c r="C27" t="s">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="D27">
         <v>0</v>
       </c>
       <c r="E27">
-        <v>0.58399999999999996</v>
+        <v>0.40300000000000002</v>
       </c>
       <c r="F27">
         <v>0</v>
@@ -1825,10 +1822,10 @@
         <v>0</v>
       </c>
       <c r="H27">
-        <v>41.871000000000002</v>
+        <v>19.888999999999999</v>
       </c>
       <c r="I27">
-        <v>982.60799999999995</v>
+        <v>677.22400000000005</v>
       </c>
       <c r="J27" t="s">
         <v>17</v>
@@ -1837,7 +1834,7 @@
         <v>0</v>
       </c>
       <c r="L27">
-        <v>2.8660000000000001</v>
+        <v>1.9750000000000001</v>
       </c>
       <c r="M27">
         <v>0</v>
@@ -1846,24 +1843,24 @@
         <v>46247</v>
       </c>
       <c r="O27" s="3">
-        <v>0.86149305555555555</v>
-      </c>
-    </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.3">
+        <v>0.86717592592592596</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
         <v>23</v>
       </c>
       <c r="B28">
-        <v>74</v>
+        <v>190</v>
       </c>
       <c r="C28" t="s">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="D28">
         <v>0</v>
       </c>
       <c r="E28">
-        <v>0.38200000000000001</v>
+        <v>0.51400000000000001</v>
       </c>
       <c r="F28">
         <v>0</v>
@@ -1872,10 +1869,10 @@
         <v>0</v>
       </c>
       <c r="H28">
-        <v>17.864999999999998</v>
+        <v>32.448</v>
       </c>
       <c r="I28">
-        <v>641.84400000000005</v>
+        <v>865.00699999999995</v>
       </c>
       <c r="J28" t="s">
         <v>17</v>
@@ -1884,7 +1881,7 @@
         <v>0</v>
       </c>
       <c r="L28">
-        <v>1.8720000000000001</v>
+        <v>2.5230000000000001</v>
       </c>
       <c r="M28">
         <v>0</v>
@@ -1893,24 +1890,24 @@
         <v>46247</v>
       </c>
       <c r="O28" s="3">
-        <v>0.86275462962962968</v>
-      </c>
-    </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
+        <v>0.87594907407407407</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
         <v>23</v>
       </c>
       <c r="B29">
-        <v>77</v>
+        <v>193</v>
       </c>
       <c r="C29" t="s">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="D29">
         <v>0</v>
       </c>
       <c r="E29">
-        <v>0.37</v>
+        <v>0.52200000000000002</v>
       </c>
       <c r="F29">
         <v>0</v>
@@ -1919,10 +1916,10 @@
         <v>0</v>
       </c>
       <c r="H29">
-        <v>16.771000000000001</v>
+        <v>33.371000000000002</v>
       </c>
       <c r="I29">
-        <v>621.88</v>
+        <v>877.221</v>
       </c>
       <c r="J29" t="s">
         <v>17</v>
@@ -1931,7 +1928,7 @@
         <v>0</v>
       </c>
       <c r="L29">
-        <v>1.8140000000000001</v>
+        <v>2.5590000000000002</v>
       </c>
       <c r="M29">
         <v>0</v>
@@ -1940,15 +1937,15 @@
         <v>46247</v>
       </c>
       <c r="O29" s="3">
-        <v>0.86390046296296297</v>
-      </c>
-    </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.3">
+        <v>0.87690972222222219</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
         <v>23</v>
       </c>
       <c r="B30">
-        <v>80</v>
+        <v>196</v>
       </c>
       <c r="C30" t="s">
         <v>19</v>
@@ -1957,7 +1954,7 @@
         <v>0</v>
       </c>
       <c r="E30">
-        <v>0.42299999999999999</v>
+        <v>0.39200000000000002</v>
       </c>
       <c r="F30">
         <v>0</v>
@@ -1966,10 +1963,10 @@
         <v>0</v>
       </c>
       <c r="H30">
-        <v>21.901</v>
+        <v>18.88</v>
       </c>
       <c r="I30">
-        <v>710.65300000000002</v>
+        <v>659.81600000000003</v>
       </c>
       <c r="J30" t="s">
         <v>17</v>
@@ -1978,7 +1975,7 @@
         <v>0</v>
       </c>
       <c r="L30">
-        <v>2.073</v>
+        <v>1.925</v>
       </c>
       <c r="M30">
         <v>0</v>
@@ -1987,24 +1984,24 @@
         <v>46247</v>
       </c>
       <c r="O30" s="3">
-        <v>0.86471064814814813</v>
-      </c>
-    </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.3">
+        <v>0.87809027777777782</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
         <v>23</v>
       </c>
       <c r="B31">
-        <v>83</v>
+        <v>199</v>
       </c>
       <c r="C31" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D31">
         <v>0</v>
       </c>
       <c r="E31">
-        <v>0.41799999999999998</v>
+        <v>0.40300000000000002</v>
       </c>
       <c r="F31">
         <v>0</v>
@@ -2013,10 +2010,10 @@
         <v>0</v>
       </c>
       <c r="H31">
-        <v>21.474</v>
+        <v>19.87</v>
       </c>
       <c r="I31">
-        <v>703.68499999999995</v>
+        <v>676.88699999999994</v>
       </c>
       <c r="J31" t="s">
         <v>17</v>
@@ -2025,7 +2022,7 @@
         <v>0</v>
       </c>
       <c r="L31">
-        <v>2.0529999999999999</v>
+        <v>1.974</v>
       </c>
       <c r="M31">
         <v>0</v>
@@ -2034,15 +2031,15 @@
         <v>46247</v>
       </c>
       <c r="O31" s="3">
-        <v>0.86552083333333329</v>
-      </c>
-    </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
+        <v>0.87958333333333338</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
         <v>23</v>
       </c>
       <c r="B32">
-        <v>86</v>
+        <v>203</v>
       </c>
       <c r="C32" t="s">
         <v>18</v>
@@ -2051,7 +2048,7 @@
         <v>0</v>
       </c>
       <c r="E32">
-        <v>0.41399999999999998</v>
+        <v>0.38400000000000001</v>
       </c>
       <c r="F32">
         <v>0</v>
@@ -2060,10 +2057,10 @@
         <v>0</v>
       </c>
       <c r="H32">
-        <v>20.981000000000002</v>
+        <v>18.122</v>
       </c>
       <c r="I32">
-        <v>695.55899999999997</v>
+        <v>646.43100000000004</v>
       </c>
       <c r="J32" t="s">
         <v>17</v>
@@ -2072,7 +2069,7 @@
         <v>0</v>
       </c>
       <c r="L32">
-        <v>2.0289999999999999</v>
+        <v>1.8859999999999999</v>
       </c>
       <c r="M32">
         <v>0</v>
@@ -2081,15 +2078,15 @@
         <v>46247</v>
       </c>
       <c r="O32" s="3">
-        <v>0.86618055555555551</v>
-      </c>
-    </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.3">
+        <v>0.88086805555555558</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
         <v>23</v>
       </c>
       <c r="B33">
-        <v>89</v>
+        <v>206</v>
       </c>
       <c r="C33" t="s">
         <v>18</v>
@@ -2098,7 +2095,7 @@
         <v>0</v>
       </c>
       <c r="E33">
-        <v>0.40300000000000002</v>
+        <v>0.36299999999999999</v>
       </c>
       <c r="F33">
         <v>0</v>
@@ -2107,10 +2104,10 @@
         <v>0</v>
       </c>
       <c r="H33">
-        <v>19.888999999999999</v>
+        <v>16.158000000000001</v>
       </c>
       <c r="I33">
-        <v>677.22400000000005</v>
+        <v>610.40499999999997</v>
       </c>
       <c r="J33" t="s">
         <v>17</v>
@@ -2119,7 +2116,7 @@
         <v>0</v>
       </c>
       <c r="L33">
-        <v>1.9750000000000001</v>
+        <v>1.7809999999999999</v>
       </c>
       <c r="M33">
         <v>0</v>
@@ -2128,15 +2125,15 @@
         <v>46247</v>
       </c>
       <c r="O33" s="3">
-        <v>0.86717592592592596</v>
-      </c>
-    </row>
-    <row r="34" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+        <v>0.88153935185185184</v>
+      </c>
+    </row>
+    <row r="34" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
         <v>24</v>
       </c>
       <c r="B34">
-        <v>190</v>
+        <v>143</v>
       </c>
       <c r="C34" t="s">
         <v>0</v>
@@ -2145,7 +2142,7 @@
         <v>0</v>
       </c>
       <c r="E34">
-        <v>0.51400000000000001</v>
+        <v>0.55400000000000005</v>
       </c>
       <c r="F34">
         <v>0</v>
@@ -2154,10 +2151,10 @@
         <v>0</v>
       </c>
       <c r="H34">
-        <v>32.448</v>
+        <v>37.588000000000001</v>
       </c>
       <c r="I34">
-        <v>865.00699999999995</v>
+        <v>930.99099999999999</v>
       </c>
       <c r="J34" t="s">
         <v>17</v>
@@ -2166,7 +2163,7 @@
         <v>0</v>
       </c>
       <c r="L34">
-        <v>2.5230000000000001</v>
+        <v>2.7160000000000002</v>
       </c>
       <c r="M34">
         <v>0</v>
@@ -2175,15 +2172,15 @@
         <v>46247</v>
       </c>
       <c r="O34" s="3">
-        <v>0.87594907407407407</v>
-      </c>
-    </row>
-    <row r="35" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+        <v>0.85424768518518523</v>
+      </c>
+    </row>
+    <row r="35" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
         <v>24</v>
       </c>
       <c r="B35">
-        <v>193</v>
+        <v>147</v>
       </c>
       <c r="C35" t="s">
         <v>0</v>
@@ -2192,7 +2189,7 @@
         <v>0</v>
       </c>
       <c r="E35">
-        <v>0.52200000000000002</v>
+        <v>0.59299999999999997</v>
       </c>
       <c r="F35">
         <v>0</v>
@@ -2201,10 +2198,10 @@
         <v>0</v>
       </c>
       <c r="H35">
-        <v>33.371000000000002</v>
+        <v>43.121000000000002</v>
       </c>
       <c r="I35">
-        <v>877.221</v>
+        <v>997.16300000000001</v>
       </c>
       <c r="J35" t="s">
         <v>17</v>
@@ -2213,7 +2210,7 @@
         <v>0</v>
       </c>
       <c r="L35">
-        <v>2.5590000000000002</v>
+        <v>2.9089999999999998</v>
       </c>
       <c r="M35">
         <v>0</v>
@@ -2222,15 +2219,15 @@
         <v>46247</v>
       </c>
       <c r="O35" s="3">
-        <v>0.87690972222222219</v>
-      </c>
-    </row>
-    <row r="36" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+        <v>0.85518518518518516</v>
+      </c>
+    </row>
+    <row r="36" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
         <v>24</v>
       </c>
       <c r="B36">
-        <v>196</v>
+        <v>151</v>
       </c>
       <c r="C36" t="s">
         <v>19</v>
@@ -2239,7 +2236,7 @@
         <v>0</v>
       </c>
       <c r="E36">
-        <v>0.39200000000000002</v>
+        <v>0.4</v>
       </c>
       <c r="F36">
         <v>0</v>
@@ -2248,10 +2245,10 @@
         <v>0</v>
       </c>
       <c r="H36">
-        <v>18.88</v>
+        <v>19.628</v>
       </c>
       <c r="I36">
-        <v>659.81600000000003</v>
+        <v>672.75699999999995</v>
       </c>
       <c r="J36" t="s">
         <v>17</v>
@@ -2260,7 +2257,7 @@
         <v>0</v>
       </c>
       <c r="L36">
-        <v>1.925</v>
+        <v>1.962</v>
       </c>
       <c r="M36">
         <v>0</v>
@@ -2269,15 +2266,15 @@
         <v>46247</v>
       </c>
       <c r="O36" s="3">
-        <v>0.87809027777777782</v>
-      </c>
-    </row>
-    <row r="37" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+        <v>0.85707175925925927</v>
+      </c>
+    </row>
+    <row r="37" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
         <v>24</v>
       </c>
       <c r="B37">
-        <v>199</v>
+        <v>155</v>
       </c>
       <c r="C37" t="s">
         <v>19</v>
@@ -2286,7 +2283,7 @@
         <v>0</v>
       </c>
       <c r="E37">
-        <v>0.40300000000000002</v>
+        <v>0.41699999999999998</v>
       </c>
       <c r="F37">
         <v>0</v>
@@ -2295,10 +2292,10 @@
         <v>0</v>
       </c>
       <c r="H37">
-        <v>19.87</v>
+        <v>21.321000000000002</v>
       </c>
       <c r="I37">
-        <v>676.88699999999994</v>
+        <v>701.16899999999998</v>
       </c>
       <c r="J37" t="s">
         <v>17</v>
@@ -2307,7 +2304,7 @@
         <v>0</v>
       </c>
       <c r="L37">
-        <v>1.974</v>
+        <v>2.0449999999999999</v>
       </c>
       <c r="M37">
         <v>0</v>
@@ -2316,15 +2313,15 @@
         <v>46247</v>
       </c>
       <c r="O37" s="3">
-        <v>0.87958333333333338</v>
-      </c>
-    </row>
-    <row r="38" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+        <v>0.85865740740740737</v>
+      </c>
+    </row>
+    <row r="38" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
         <v>24</v>
       </c>
       <c r="B38">
-        <v>203</v>
+        <v>159</v>
       </c>
       <c r="C38" t="s">
         <v>18</v>
@@ -2333,7 +2330,7 @@
         <v>0</v>
       </c>
       <c r="E38">
-        <v>0.38400000000000001</v>
+        <v>0.39600000000000002</v>
       </c>
       <c r="F38">
         <v>0</v>
@@ -2342,10 +2339,10 @@
         <v>0</v>
       </c>
       <c r="H38">
-        <v>18.122</v>
+        <v>19.257999999999999</v>
       </c>
       <c r="I38">
-        <v>646.43100000000004</v>
+        <v>666.38099999999997</v>
       </c>
       <c r="J38" t="s">
         <v>17</v>
@@ -2354,7 +2351,7 @@
         <v>0</v>
       </c>
       <c r="L38">
-        <v>1.8859999999999999</v>
+        <v>1.944</v>
       </c>
       <c r="M38">
         <v>0</v>
@@ -2363,15 +2360,15 @@
         <v>46247</v>
       </c>
       <c r="O38" s="3">
-        <v>0.88086805555555558</v>
-      </c>
-    </row>
-    <row r="39" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+        <v>0.85947916666666668</v>
+      </c>
+    </row>
+    <row r="39" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
         <v>24</v>
       </c>
       <c r="B39">
-        <v>206</v>
+        <v>163</v>
       </c>
       <c r="C39" t="s">
         <v>18</v>
@@ -2380,7 +2377,7 @@
         <v>0</v>
       </c>
       <c r="E39">
-        <v>0.36299999999999999</v>
+        <v>0.40500000000000003</v>
       </c>
       <c r="F39">
         <v>0</v>
@@ -2389,10 +2386,10 @@
         <v>0</v>
       </c>
       <c r="H39">
-        <v>16.158000000000001</v>
+        <v>20.102</v>
       </c>
       <c r="I39">
-        <v>610.40499999999997</v>
+        <v>680.84199999999998</v>
       </c>
       <c r="J39" t="s">
         <v>17</v>
@@ -2401,7 +2398,7 @@
         <v>0</v>
       </c>
       <c r="L39">
-        <v>1.7809999999999999</v>
+        <v>1.986</v>
       </c>
       <c r="M39">
         <v>0</v>
@@ -2410,7 +2407,7 @@
         <v>46247</v>
       </c>
       <c r="O39" s="3">
-        <v>0.88153935185185184</v>
+        <v>0.86001157407407403</v>
       </c>
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.3">
@@ -2418,7 +2415,7 @@
         <v>25</v>
       </c>
       <c r="B40">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C40" t="s">
         <v>0</v>
@@ -2427,7 +2424,7 @@
         <v>0</v>
       </c>
       <c r="E40">
-        <v>0.55400000000000005</v>
+        <v>0.52800000000000002</v>
       </c>
       <c r="F40">
         <v>0</v>
@@ -2436,10 +2433,10 @@
         <v>0</v>
       </c>
       <c r="H40">
-        <v>37.588000000000001</v>
+        <v>34.134999999999998</v>
       </c>
       <c r="I40">
-        <v>930.99099999999999</v>
+        <v>887.20299999999997</v>
       </c>
       <c r="J40" t="s">
         <v>17</v>
@@ -2448,7 +2445,7 @@
         <v>0</v>
       </c>
       <c r="L40">
-        <v>2.7160000000000002</v>
+        <v>2.5880000000000001</v>
       </c>
       <c r="M40">
         <v>0</v>
@@ -2457,7 +2454,7 @@
         <v>46247</v>
       </c>
       <c r="O40" s="3">
-        <v>0.85424768518518523</v>
+        <v>0.85467592592592589</v>
       </c>
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.3">
@@ -2465,7 +2462,7 @@
         <v>25</v>
       </c>
       <c r="B41">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C41" t="s">
         <v>0</v>
@@ -2474,7 +2471,7 @@
         <v>0</v>
       </c>
       <c r="E41">
-        <v>0.59299999999999997</v>
+        <v>0.56599999999999995</v>
       </c>
       <c r="F41">
         <v>0</v>
@@ -2483,10 +2480,10 @@
         <v>0</v>
       </c>
       <c r="H41">
-        <v>43.121000000000002</v>
+        <v>39.305999999999997</v>
       </c>
       <c r="I41">
-        <v>997.16300000000001</v>
+        <v>952.03</v>
       </c>
       <c r="J41" t="s">
         <v>17</v>
@@ -2495,7 +2492,7 @@
         <v>0</v>
       </c>
       <c r="L41">
-        <v>2.9089999999999998</v>
+        <v>2.7770000000000001</v>
       </c>
       <c r="M41">
         <v>0</v>
@@ -2504,7 +2501,7 @@
         <v>46247</v>
       </c>
       <c r="O41" s="3">
-        <v>0.85518518518518516</v>
+        <v>0.85585648148148152</v>
       </c>
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.3">
@@ -2512,7 +2509,7 @@
         <v>25</v>
       </c>
       <c r="B42">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C42" t="s">
         <v>19</v>
@@ -2521,7 +2518,7 @@
         <v>0</v>
       </c>
       <c r="E42">
-        <v>0.4</v>
+        <v>0.31</v>
       </c>
       <c r="F42">
         <v>0</v>
@@ -2530,10 +2527,10 @@
         <v>0</v>
       </c>
       <c r="H42">
-        <v>19.628</v>
+        <v>11.769</v>
       </c>
       <c r="I42">
-        <v>672.75699999999995</v>
+        <v>520.94600000000003</v>
       </c>
       <c r="J42" t="s">
         <v>17</v>
@@ -2542,7 +2539,7 @@
         <v>0</v>
       </c>
       <c r="L42">
-        <v>1.962</v>
+        <v>1.52</v>
       </c>
       <c r="M42">
         <v>0</v>
@@ -2551,7 +2548,7 @@
         <v>46247</v>
       </c>
       <c r="O42" s="3">
-        <v>0.85707175925925927</v>
+        <v>0.85741898148148143</v>
       </c>
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.3">
@@ -2559,7 +2556,7 @@
         <v>25</v>
       </c>
       <c r="B43">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C43" t="s">
         <v>19</v>
@@ -2568,7 +2565,7 @@
         <v>0</v>
       </c>
       <c r="E43">
-        <v>0.41699999999999998</v>
+        <v>0.36399999999999999</v>
       </c>
       <c r="F43">
         <v>0</v>
@@ -2577,10 +2574,10 @@
         <v>0</v>
       </c>
       <c r="H43">
-        <v>21.321000000000002</v>
+        <v>16.213999999999999</v>
       </c>
       <c r="I43">
-        <v>701.16899999999998</v>
+        <v>611.45500000000004</v>
       </c>
       <c r="J43" t="s">
         <v>17</v>
@@ -2589,7 +2586,7 @@
         <v>0</v>
       </c>
       <c r="L43">
-        <v>2.0449999999999999</v>
+        <v>1.784</v>
       </c>
       <c r="M43">
         <v>0</v>
@@ -2598,7 +2595,7 @@
         <v>46247</v>
       </c>
       <c r="O43" s="3">
-        <v>0.85865740740740737</v>
+        <v>0.85898148148148146</v>
       </c>
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.3">
@@ -2606,7 +2603,7 @@
         <v>25</v>
       </c>
       <c r="B44">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C44" t="s">
         <v>18</v>
@@ -2615,7 +2612,7 @@
         <v>0</v>
       </c>
       <c r="E44">
-        <v>0.39600000000000002</v>
+        <v>0.38900000000000001</v>
       </c>
       <c r="F44">
         <v>0</v>
@@ -2624,10 +2621,10 @@
         <v>0</v>
       </c>
       <c r="H44">
-        <v>19.257999999999999</v>
+        <v>18.553000000000001</v>
       </c>
       <c r="I44">
-        <v>666.38099999999997</v>
+        <v>654.072</v>
       </c>
       <c r="J44" t="s">
         <v>17</v>
@@ -2636,7 +2633,7 @@
         <v>0</v>
       </c>
       <c r="L44">
-        <v>1.944</v>
+        <v>1.9079999999999999</v>
       </c>
       <c r="M44">
         <v>0</v>
@@ -2645,7 +2642,7 @@
         <v>46247</v>
       </c>
       <c r="O44" s="3">
-        <v>0.85947916666666668</v>
+        <v>0.85971064814814813</v>
       </c>
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.3">
@@ -2653,7 +2650,7 @@
         <v>25</v>
       </c>
       <c r="B45">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="C45" t="s">
         <v>18</v>
@@ -2662,7 +2659,7 @@
         <v>0</v>
       </c>
       <c r="E45">
-        <v>0.40500000000000003</v>
+        <v>0.41199999999999998</v>
       </c>
       <c r="F45">
         <v>0</v>
@@ -2671,10 +2668,10 @@
         <v>0</v>
       </c>
       <c r="H45">
-        <v>20.102</v>
+        <v>20.815999999999999</v>
       </c>
       <c r="I45">
-        <v>680.84199999999998</v>
+        <v>692.82899999999995</v>
       </c>
       <c r="J45" t="s">
         <v>17</v>
@@ -2683,7 +2680,7 @@
         <v>0</v>
       </c>
       <c r="L45">
-        <v>1.986</v>
+        <v>2.0209999999999999</v>
       </c>
       <c r="M45">
         <v>0</v>
@@ -2692,15 +2689,15 @@
         <v>46247</v>
       </c>
       <c r="O45" s="3">
-        <v>0.86001157407407403</v>
-      </c>
-    </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.3">
+        <v>0.86026620370370366</v>
+      </c>
+    </row>
+    <row r="46" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
         <v>26</v>
       </c>
       <c r="B46">
-        <v>145</v>
+        <v>66</v>
       </c>
       <c r="C46" t="s">
         <v>0</v>
@@ -2709,7 +2706,7 @@
         <v>0</v>
       </c>
       <c r="E46">
-        <v>0.52800000000000002</v>
+        <v>0.60199999999999998</v>
       </c>
       <c r="F46">
         <v>0</v>
@@ -2718,10 +2715,10 @@
         <v>0</v>
       </c>
       <c r="H46">
-        <v>34.134999999999998</v>
+        <v>44.445999999999998</v>
       </c>
       <c r="I46">
-        <v>887.20299999999997</v>
+        <v>1012.365</v>
       </c>
       <c r="J46" t="s">
         <v>17</v>
@@ -2730,7 +2727,7 @@
         <v>0</v>
       </c>
       <c r="L46">
-        <v>2.5880000000000001</v>
+        <v>2.9529999999999998</v>
       </c>
       <c r="M46">
         <v>0</v>
@@ -2739,15 +2736,15 @@
         <v>46247</v>
       </c>
       <c r="O46" s="3">
-        <v>0.85467592592592589</v>
-      </c>
-    </row>
-    <row r="47" spans="1:15" x14ac:dyDescent="0.3">
+        <v>0.86008101851851848</v>
+      </c>
+    </row>
+    <row r="47" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="s">
         <v>26</v>
       </c>
       <c r="B47">
-        <v>149</v>
+        <v>69</v>
       </c>
       <c r="C47" t="s">
         <v>0</v>
@@ -2756,7 +2753,7 @@
         <v>0</v>
       </c>
       <c r="E47">
-        <v>0.56599999999999995</v>
+        <v>0.60899999999999999</v>
       </c>
       <c r="F47">
         <v>0</v>
@@ -2765,10 +2762,10 @@
         <v>0</v>
       </c>
       <c r="H47">
-        <v>39.305999999999997</v>
+        <v>45.482999999999997</v>
       </c>
       <c r="I47">
-        <v>952.03</v>
+        <v>1024.1089999999999</v>
       </c>
       <c r="J47" t="s">
         <v>17</v>
@@ -2777,7 +2774,7 @@
         <v>0</v>
       </c>
       <c r="L47">
-        <v>2.7770000000000001</v>
+        <v>2.9870000000000001</v>
       </c>
       <c r="M47">
         <v>0</v>
@@ -2786,24 +2783,24 @@
         <v>46247</v>
       </c>
       <c r="O47" s="3">
-        <v>0.85585648148148152</v>
-      </c>
-    </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.3">
+        <v>0.86083333333333334</v>
+      </c>
+    </row>
+    <row r="48" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
         <v>26</v>
       </c>
       <c r="B48">
-        <v>153</v>
+        <v>72</v>
       </c>
       <c r="C48" t="s">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="D48">
         <v>0</v>
       </c>
       <c r="E48">
-        <v>0.31</v>
+        <v>0.61499999999999999</v>
       </c>
       <c r="F48">
         <v>0</v>
@@ -2812,10 +2809,10 @@
         <v>0</v>
       </c>
       <c r="H48">
-        <v>11.769</v>
+        <v>46.350999999999999</v>
       </c>
       <c r="I48">
-        <v>520.94600000000003</v>
+        <v>1033.835</v>
       </c>
       <c r="J48" t="s">
         <v>17</v>
@@ -2824,7 +2821,7 @@
         <v>0</v>
       </c>
       <c r="L48">
-        <v>1.52</v>
+        <v>3.016</v>
       </c>
       <c r="M48">
         <v>0</v>
@@ -2833,15 +2830,15 @@
         <v>46247</v>
       </c>
       <c r="O48" s="3">
-        <v>0.85741898148148143</v>
-      </c>
-    </row>
-    <row r="49" spans="1:15" x14ac:dyDescent="0.3">
+        <v>0.86175925925925922</v>
+      </c>
+    </row>
+    <row r="49" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
         <v>26</v>
       </c>
       <c r="B49">
-        <v>157</v>
+        <v>75</v>
       </c>
       <c r="C49" t="s">
         <v>19</v>
@@ -2850,7 +2847,7 @@
         <v>0</v>
       </c>
       <c r="E49">
-        <v>0.36399999999999999</v>
+        <v>0.40899999999999997</v>
       </c>
       <c r="F49">
         <v>0</v>
@@ -2859,10 +2856,10 @@
         <v>0</v>
       </c>
       <c r="H49">
-        <v>16.213999999999999</v>
+        <v>20.475999999999999</v>
       </c>
       <c r="I49">
-        <v>611.45500000000004</v>
+        <v>687.13800000000003</v>
       </c>
       <c r="J49" t="s">
         <v>17</v>
@@ -2871,7 +2868,7 @@
         <v>0</v>
       </c>
       <c r="L49">
-        <v>1.784</v>
+        <v>2.004</v>
       </c>
       <c r="M49">
         <v>0</v>
@@ -2880,24 +2877,24 @@
         <v>46247</v>
       </c>
       <c r="O49" s="3">
-        <v>0.85898148148148146</v>
-      </c>
-    </row>
-    <row r="50" spans="1:15" x14ac:dyDescent="0.3">
+        <v>0.86306712962962961</v>
+      </c>
+    </row>
+    <row r="50" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A50" s="1" t="s">
         <v>26</v>
       </c>
       <c r="B50">
-        <v>161</v>
+        <v>78</v>
       </c>
       <c r="C50" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D50">
         <v>0</v>
       </c>
       <c r="E50">
-        <v>0.38900000000000001</v>
+        <v>0.42599999999999999</v>
       </c>
       <c r="F50">
         <v>0</v>
@@ -2906,10 +2903,10 @@
         <v>0</v>
       </c>
       <c r="H50">
-        <v>18.553000000000001</v>
+        <v>22.297000000000001</v>
       </c>
       <c r="I50">
-        <v>654.072</v>
+        <v>717.04300000000001</v>
       </c>
       <c r="J50" t="s">
         <v>17</v>
@@ -2918,7 +2915,7 @@
         <v>0</v>
       </c>
       <c r="L50">
-        <v>1.9079999999999999</v>
+        <v>2.0920000000000001</v>
       </c>
       <c r="M50">
         <v>0</v>
@@ -2927,24 +2924,24 @@
         <v>46247</v>
       </c>
       <c r="O50" s="3">
-        <v>0.85971064814814813</v>
-      </c>
-    </row>
-    <row r="51" spans="1:15" x14ac:dyDescent="0.3">
+        <v>0.86421296296296302</v>
+      </c>
+    </row>
+    <row r="51" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
         <v>26</v>
       </c>
       <c r="B51">
-        <v>165</v>
+        <v>81</v>
       </c>
       <c r="C51" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D51">
         <v>0</v>
       </c>
       <c r="E51">
-        <v>0.41199999999999998</v>
+        <v>0.42499999999999999</v>
       </c>
       <c r="F51">
         <v>0</v>
@@ -2953,10 +2950,10 @@
         <v>0</v>
       </c>
       <c r="H51">
-        <v>20.815999999999999</v>
+        <v>22.157</v>
       </c>
       <c r="I51">
-        <v>692.82899999999995</v>
+        <v>714.79600000000005</v>
       </c>
       <c r="J51" t="s">
         <v>17</v>
@@ -2965,7 +2962,7 @@
         <v>0</v>
       </c>
       <c r="L51">
-        <v>2.0209999999999999</v>
+        <v>2.085</v>
       </c>
       <c r="M51">
         <v>0</v>
@@ -2974,24 +2971,24 @@
         <v>46247</v>
       </c>
       <c r="O51" s="3">
-        <v>0.86026620370370366</v>
+        <v>0.8649768518518518</v>
       </c>
     </row>
     <row r="52" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B52">
-        <v>66</v>
+        <v>84</v>
       </c>
       <c r="C52" t="s">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="D52">
         <v>0</v>
       </c>
       <c r="E52">
-        <v>0.60199999999999998</v>
+        <v>0.41899999999999998</v>
       </c>
       <c r="F52">
         <v>0</v>
@@ -3000,10 +2997,10 @@
         <v>0</v>
       </c>
       <c r="H52">
-        <v>44.445999999999998</v>
+        <v>21.5</v>
       </c>
       <c r="I52">
-        <v>1012.365</v>
+        <v>704.11500000000001</v>
       </c>
       <c r="J52" t="s">
         <v>17</v>
@@ -3012,7 +3009,7 @@
         <v>0</v>
       </c>
       <c r="L52">
-        <v>2.9529999999999998</v>
+        <v>2.0539999999999998</v>
       </c>
       <c r="M52">
         <v>0</v>
@@ -3021,24 +3018,24 @@
         <v>46247</v>
       </c>
       <c r="O52" s="3">
-        <v>0.86008101851851848</v>
+        <v>0.86572916666666666</v>
       </c>
     </row>
     <row r="53" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B53">
-        <v>69</v>
+        <v>87</v>
       </c>
       <c r="C53" t="s">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="D53">
         <v>0</v>
       </c>
       <c r="E53">
-        <v>0.60899999999999999</v>
+        <v>0.39500000000000002</v>
       </c>
       <c r="F53">
         <v>0</v>
@@ -3047,10 +3044,10 @@
         <v>0</v>
       </c>
       <c r="H53">
-        <v>45.482999999999997</v>
+        <v>19.146999999999998</v>
       </c>
       <c r="I53">
-        <v>1024.1089999999999</v>
+        <v>664.45699999999999</v>
       </c>
       <c r="J53" t="s">
         <v>17</v>
@@ -3059,7 +3056,7 @@
         <v>0</v>
       </c>
       <c r="L53">
-        <v>2.9870000000000001</v>
+        <v>1.9379999999999999</v>
       </c>
       <c r="M53">
         <v>0</v>
@@ -3068,24 +3065,24 @@
         <v>46247</v>
       </c>
       <c r="O53" s="3">
-        <v>0.86083333333333334</v>
+        <v>0.86657407407407405</v>
       </c>
     </row>
     <row r="54" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B54">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="C54" t="s">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="D54">
         <v>0</v>
       </c>
       <c r="E54">
-        <v>0.61499999999999999</v>
+        <v>0.41499999999999998</v>
       </c>
       <c r="F54">
         <v>0</v>
@@ -3094,10 +3091,10 @@
         <v>0</v>
       </c>
       <c r="H54">
-        <v>46.350999999999999</v>
+        <v>21.074999999999999</v>
       </c>
       <c r="I54">
-        <v>1033.835</v>
+        <v>697.12</v>
       </c>
       <c r="J54" t="s">
         <v>17</v>
@@ -3106,7 +3103,7 @@
         <v>0</v>
       </c>
       <c r="L54">
-        <v>3.016</v>
+        <v>2.0329999999999999</v>
       </c>
       <c r="M54">
         <v>0</v>
@@ -3115,24 +3112,24 @@
         <v>46247</v>
       </c>
       <c r="O54" s="3">
-        <v>0.86175925925925922</v>
-      </c>
-    </row>
-    <row r="55" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+        <v>0.86736111111111114</v>
+      </c>
+    </row>
+    <row r="55" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
         <v>27</v>
       </c>
       <c r="B55">
-        <v>75</v>
+        <v>169</v>
       </c>
       <c r="C55" t="s">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="D55">
         <v>0</v>
       </c>
       <c r="E55">
-        <v>0.40899999999999997</v>
+        <v>0.56299999999999994</v>
       </c>
       <c r="F55">
         <v>0</v>
@@ -3141,10 +3138,10 @@
         <v>0</v>
       </c>
       <c r="H55">
-        <v>20.475999999999999</v>
+        <v>38.837000000000003</v>
       </c>
       <c r="I55">
-        <v>687.13800000000003</v>
+        <v>946.34</v>
       </c>
       <c r="J55" t="s">
         <v>17</v>
@@ -3153,7 +3150,7 @@
         <v>0</v>
       </c>
       <c r="L55">
-        <v>2.004</v>
+        <v>2.76</v>
       </c>
       <c r="M55">
         <v>0</v>
@@ -3162,24 +3159,24 @@
         <v>46247</v>
       </c>
       <c r="O55" s="3">
-        <v>0.86306712962962961</v>
-      </c>
-    </row>
-    <row r="56" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+        <v>0.8682523148148148</v>
+      </c>
+    </row>
+    <row r="56" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
         <v>27</v>
       </c>
       <c r="B56">
-        <v>78</v>
+        <v>173</v>
       </c>
       <c r="C56" t="s">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="D56">
         <v>0</v>
       </c>
       <c r="E56">
-        <v>0.42599999999999999</v>
+        <v>0.59099999999999997</v>
       </c>
       <c r="F56">
         <v>0</v>
@@ -3188,10 +3185,10 @@
         <v>0</v>
       </c>
       <c r="H56">
-        <v>22.297000000000001</v>
+        <v>42.856000000000002</v>
       </c>
       <c r="I56">
-        <v>717.04300000000001</v>
+        <v>994.096</v>
       </c>
       <c r="J56" t="s">
         <v>17</v>
@@ -3200,7 +3197,7 @@
         <v>0</v>
       </c>
       <c r="L56">
-        <v>2.0920000000000001</v>
+        <v>2.9</v>
       </c>
       <c r="M56">
         <v>0</v>
@@ -3209,15 +3206,15 @@
         <v>46247</v>
       </c>
       <c r="O56" s="3">
-        <v>0.86421296296296302</v>
-      </c>
-    </row>
-    <row r="57" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+        <v>0.86905092592592592</v>
+      </c>
+    </row>
+    <row r="57" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
         <v>27</v>
       </c>
       <c r="B57">
-        <v>81</v>
+        <v>177</v>
       </c>
       <c r="C57" t="s">
         <v>19</v>
@@ -3226,7 +3223,7 @@
         <v>0</v>
       </c>
       <c r="E57">
-        <v>0.42499999999999999</v>
+        <v>0.442</v>
       </c>
       <c r="F57">
         <v>0</v>
@@ -3235,10 +3232,10 @@
         <v>0</v>
       </c>
       <c r="H57">
-        <v>22.157</v>
+        <v>23.984000000000002</v>
       </c>
       <c r="I57">
-        <v>714.79600000000005</v>
+        <v>743.67899999999997</v>
       </c>
       <c r="J57" t="s">
         <v>17</v>
@@ -3247,7 +3244,7 @@
         <v>0</v>
       </c>
       <c r="L57">
-        <v>2.085</v>
+        <v>2.169</v>
       </c>
       <c r="M57">
         <v>0</v>
@@ -3256,24 +3253,24 @@
         <v>46247</v>
       </c>
       <c r="O57" s="3">
-        <v>0.8649768518518518</v>
-      </c>
-    </row>
-    <row r="58" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+        <v>0.87019675925925921</v>
+      </c>
+    </row>
+    <row r="58" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
         <v>27</v>
       </c>
       <c r="B58">
-        <v>84</v>
+        <v>181</v>
       </c>
       <c r="C58" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D58">
         <v>0</v>
       </c>
       <c r="E58">
-        <v>0.41899999999999998</v>
+        <v>0.435</v>
       </c>
       <c r="F58">
         <v>0</v>
@@ -3282,10 +3279,10 @@
         <v>0</v>
       </c>
       <c r="H58">
-        <v>21.5</v>
+        <v>23.173999999999999</v>
       </c>
       <c r="I58">
-        <v>704.11500000000001</v>
+        <v>731.00699999999995</v>
       </c>
       <c r="J58" t="s">
         <v>17</v>
@@ -3294,7 +3291,7 @@
         <v>0</v>
       </c>
       <c r="L58">
-        <v>2.0539999999999998</v>
+        <v>2.1320000000000001</v>
       </c>
       <c r="M58">
         <v>0</v>
@@ -3303,15 +3300,15 @@
         <v>46247</v>
       </c>
       <c r="O58" s="3">
-        <v>0.86572916666666666</v>
-      </c>
-    </row>
-    <row r="59" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+        <v>0.87089120370370365</v>
+      </c>
+    </row>
+    <row r="59" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
         <v>27</v>
       </c>
       <c r="B59">
-        <v>87</v>
+        <v>185</v>
       </c>
       <c r="C59" t="s">
         <v>18</v>
@@ -3320,7 +3317,7 @@
         <v>0</v>
       </c>
       <c r="E59">
-        <v>0.39500000000000002</v>
+        <v>0.38200000000000001</v>
       </c>
       <c r="F59">
         <v>0</v>
@@ -3329,10 +3326,10 @@
         <v>0</v>
       </c>
       <c r="H59">
-        <v>19.146999999999998</v>
+        <v>17.850999999999999</v>
       </c>
       <c r="I59">
-        <v>664.45699999999999</v>
+        <v>641.58799999999997</v>
       </c>
       <c r="J59" t="s">
         <v>17</v>
@@ -3341,7 +3338,7 @@
         <v>0</v>
       </c>
       <c r="L59">
-        <v>1.9379999999999999</v>
+        <v>1.871</v>
       </c>
       <c r="M59">
         <v>0</v>
@@ -3350,15 +3347,15 @@
         <v>46247</v>
       </c>
       <c r="O59" s="3">
-        <v>0.86657407407407405</v>
-      </c>
-    </row>
-    <row r="60" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+        <v>0.87167824074074074</v>
+      </c>
+    </row>
+    <row r="60" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
         <v>27</v>
       </c>
       <c r="B60">
-        <v>90</v>
+        <v>189</v>
       </c>
       <c r="C60" t="s">
         <v>18</v>
@@ -3367,7 +3364,7 @@
         <v>0</v>
       </c>
       <c r="E60">
-        <v>0.41499999999999998</v>
+        <v>0.38900000000000001</v>
       </c>
       <c r="F60">
         <v>0</v>
@@ -3376,10 +3373,10 @@
         <v>0</v>
       </c>
       <c r="H60">
-        <v>21.074999999999999</v>
+        <v>18.568999999999999</v>
       </c>
       <c r="I60">
-        <v>697.12</v>
+        <v>654.35400000000004</v>
       </c>
       <c r="J60" t="s">
         <v>17</v>
@@ -3388,7 +3385,7 @@
         <v>0</v>
       </c>
       <c r="L60">
-        <v>2.0329999999999999</v>
+        <v>1.909</v>
       </c>
       <c r="M60">
         <v>0</v>
@@ -3397,7 +3394,7 @@
         <v>46247</v>
       </c>
       <c r="O60" s="3">
-        <v>0.86736111111111114</v>
+        <v>0.8722685185185185</v>
       </c>
     </row>
     <row r="61" spans="1:15" x14ac:dyDescent="0.3">
@@ -3405,7 +3402,7 @@
         <v>28</v>
       </c>
       <c r="B61">
-        <v>169</v>
+        <v>92</v>
       </c>
       <c r="C61" t="s">
         <v>0</v>
@@ -3414,7 +3411,7 @@
         <v>0</v>
       </c>
       <c r="E61">
-        <v>0.56299999999999994</v>
+        <v>0.626</v>
       </c>
       <c r="F61">
         <v>0</v>
@@ -3423,10 +3420,10 @@
         <v>0</v>
       </c>
       <c r="H61">
-        <v>38.837000000000003</v>
+        <v>48.000999999999998</v>
       </c>
       <c r="I61">
-        <v>946.34</v>
+        <v>1052.076</v>
       </c>
       <c r="J61" t="s">
         <v>17</v>
@@ -3435,7 +3432,7 @@
         <v>0</v>
       </c>
       <c r="L61">
-        <v>2.76</v>
+        <v>3.069</v>
       </c>
       <c r="M61">
         <v>0</v>
@@ -3444,7 +3441,7 @@
         <v>46247</v>
       </c>
       <c r="O61" s="3">
-        <v>0.8682523148148148</v>
+        <v>0.86996527777777777</v>
       </c>
     </row>
     <row r="62" spans="1:15" x14ac:dyDescent="0.3">
@@ -3452,7 +3449,7 @@
         <v>28</v>
       </c>
       <c r="B62">
-        <v>173</v>
+        <v>96</v>
       </c>
       <c r="C62" t="s">
         <v>0</v>
@@ -3461,7 +3458,7 @@
         <v>0</v>
       </c>
       <c r="E62">
-        <v>0.59099999999999997</v>
+        <v>0.60399999999999998</v>
       </c>
       <c r="F62">
         <v>0</v>
@@ -3470,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="H62">
-        <v>42.856000000000002</v>
+        <v>44.734000000000002</v>
       </c>
       <c r="I62">
-        <v>994.096</v>
+        <v>1015.647</v>
       </c>
       <c r="J62" t="s">
         <v>17</v>
@@ -3482,7 +3479,7 @@
         <v>0</v>
       </c>
       <c r="L62">
-        <v>2.9</v>
+        <v>2.9630000000000001</v>
       </c>
       <c r="M62">
         <v>0</v>
@@ -3491,7 +3488,7 @@
         <v>46247</v>
       </c>
       <c r="O62" s="3">
-        <v>0.86905092592592592</v>
+        <v>0.87119212962962966</v>
       </c>
     </row>
     <row r="63" spans="1:15" x14ac:dyDescent="0.3">
@@ -3499,16 +3496,16 @@
         <v>28</v>
       </c>
       <c r="B63">
-        <v>177</v>
+        <v>100</v>
       </c>
       <c r="C63" t="s">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="D63">
         <v>0</v>
       </c>
       <c r="E63">
-        <v>0.442</v>
+        <v>0.61099999999999999</v>
       </c>
       <c r="F63">
         <v>0</v>
@@ -3517,10 +3514,10 @@
         <v>0</v>
       </c>
       <c r="H63">
-        <v>23.984000000000002</v>
+        <v>45.828000000000003</v>
       </c>
       <c r="I63">
-        <v>743.67899999999997</v>
+        <v>1027.9829999999999</v>
       </c>
       <c r="J63" t="s">
         <v>17</v>
@@ -3529,7 +3526,7 @@
         <v>0</v>
       </c>
       <c r="L63">
-        <v>2.169</v>
+        <v>2.9990000000000001</v>
       </c>
       <c r="M63">
         <v>0</v>
@@ -3538,7 +3535,7 @@
         <v>46247</v>
       </c>
       <c r="O63" s="3">
-        <v>0.87019675925925921</v>
+        <v>0.87277777777777776</v>
       </c>
     </row>
     <row r="64" spans="1:15" x14ac:dyDescent="0.3">
@@ -3546,7 +3543,7 @@
         <v>28</v>
       </c>
       <c r="B64">
-        <v>181</v>
+        <v>104</v>
       </c>
       <c r="C64" t="s">
         <v>19</v>
@@ -3555,7 +3552,7 @@
         <v>0</v>
       </c>
       <c r="E64">
-        <v>0.435</v>
+        <v>0.36499999999999999</v>
       </c>
       <c r="F64">
         <v>0</v>
@@ -3564,10 +3561,10 @@
         <v>0</v>
       </c>
       <c r="H64">
-        <v>23.173999999999999</v>
+        <v>16.335000000000001</v>
       </c>
       <c r="I64">
-        <v>731.00699999999995</v>
+        <v>613.72799999999995</v>
       </c>
       <c r="J64" t="s">
         <v>17</v>
@@ -3576,7 +3573,7 @@
         <v>0</v>
       </c>
       <c r="L64">
-        <v>2.1320000000000001</v>
+        <v>1.79</v>
       </c>
       <c r="M64">
         <v>0</v>
@@ -3585,7 +3582,7 @@
         <v>46247</v>
       </c>
       <c r="O64" s="3">
-        <v>0.87089120370370365</v>
+        <v>0.87430555555555556</v>
       </c>
     </row>
     <row r="65" spans="1:15" x14ac:dyDescent="0.3">
@@ -3593,16 +3590,16 @@
         <v>28</v>
       </c>
       <c r="B65">
-        <v>185</v>
+        <v>108</v>
       </c>
       <c r="C65" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D65">
         <v>0</v>
       </c>
       <c r="E65">
-        <v>0.38200000000000001</v>
+        <v>0.41699999999999998</v>
       </c>
       <c r="F65">
         <v>0</v>
@@ -3611,10 +3608,10 @@
         <v>0</v>
       </c>
       <c r="H65">
-        <v>17.850999999999999</v>
+        <v>21.335000000000001</v>
       </c>
       <c r="I65">
-        <v>641.58799999999997</v>
+        <v>701.39800000000002</v>
       </c>
       <c r="J65" t="s">
         <v>17</v>
@@ -3623,7 +3620,7 @@
         <v>0</v>
       </c>
       <c r="L65">
-        <v>1.871</v>
+        <v>2.0459999999999998</v>
       </c>
       <c r="M65">
         <v>0</v>
@@ -3632,7 +3629,7 @@
         <v>46247</v>
       </c>
       <c r="O65" s="3">
-        <v>0.87167824074074074</v>
+        <v>0.87512731481481476</v>
       </c>
     </row>
     <row r="66" spans="1:15" x14ac:dyDescent="0.3">
@@ -3640,16 +3637,16 @@
         <v>28</v>
       </c>
       <c r="B66">
-        <v>189</v>
+        <v>112</v>
       </c>
       <c r="C66" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D66">
         <v>0</v>
       </c>
       <c r="E66">
-        <v>0.38900000000000001</v>
+        <v>0.42799999999999999</v>
       </c>
       <c r="F66">
         <v>0</v>
@@ -3658,10 +3655,10 @@
         <v>0</v>
       </c>
       <c r="H66">
-        <v>18.568999999999999</v>
+        <v>22.507000000000001</v>
       </c>
       <c r="I66">
-        <v>654.35400000000004</v>
+        <v>720.41899999999998</v>
       </c>
       <c r="J66" t="s">
         <v>17</v>
@@ -3670,7 +3667,7 @@
         <v>0</v>
       </c>
       <c r="L66">
-        <v>1.909</v>
+        <v>2.101</v>
       </c>
       <c r="M66">
         <v>0</v>
@@ -3679,24 +3676,24 @@
         <v>46247</v>
       </c>
       <c r="O66" s="3">
-        <v>0.8722685185185185</v>
+        <v>0.87619212962962967</v>
       </c>
     </row>
     <row r="67" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A67" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B67">
-        <v>92</v>
+        <v>116</v>
       </c>
       <c r="C67" t="s">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="D67">
         <v>0</v>
       </c>
       <c r="E67">
-        <v>0.626</v>
+        <v>0.439</v>
       </c>
       <c r="F67">
         <v>0</v>
@@ -3705,10 +3702,10 @@
         <v>0</v>
       </c>
       <c r="H67">
-        <v>48.000999999999998</v>
+        <v>23.597999999999999</v>
       </c>
       <c r="I67">
-        <v>1052.076</v>
+        <v>737.66600000000005</v>
       </c>
       <c r="J67" t="s">
         <v>17</v>
@@ -3717,7 +3714,7 @@
         <v>0</v>
       </c>
       <c r="L67">
-        <v>3.069</v>
+        <v>2.1520000000000001</v>
       </c>
       <c r="M67">
         <v>0</v>
@@ -3726,24 +3723,24 @@
         <v>46247</v>
       </c>
       <c r="O67" s="3">
-        <v>0.86996527777777777</v>
+        <v>0.87699074074074079</v>
       </c>
     </row>
     <row r="68" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A68" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B68">
-        <v>96</v>
+        <v>120</v>
       </c>
       <c r="C68" t="s">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="D68">
         <v>0</v>
       </c>
       <c r="E68">
-        <v>0.60399999999999998</v>
+        <v>0.44900000000000001</v>
       </c>
       <c r="F68">
         <v>0</v>
@@ -3752,10 +3749,10 @@
         <v>0</v>
       </c>
       <c r="H68">
-        <v>44.734000000000002</v>
+        <v>24.742999999999999</v>
       </c>
       <c r="I68">
-        <v>1015.647</v>
+        <v>755.35599999999999</v>
       </c>
       <c r="J68" t="s">
         <v>17</v>
@@ -3764,7 +3761,7 @@
         <v>0</v>
       </c>
       <c r="L68">
-        <v>2.9630000000000001</v>
+        <v>2.2029999999999998</v>
       </c>
       <c r="M68">
         <v>0</v>
@@ -3773,15 +3770,15 @@
         <v>46247</v>
       </c>
       <c r="O68" s="3">
-        <v>0.87119212962962966</v>
-      </c>
-    </row>
-    <row r="69" spans="1:15" x14ac:dyDescent="0.3">
+        <v>0.87832175925925926</v>
+      </c>
+    </row>
+    <row r="69" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A69" s="1" t="s">
         <v>29</v>
       </c>
       <c r="B69">
-        <v>100</v>
+        <v>125</v>
       </c>
       <c r="C69" t="s">
         <v>0</v>
@@ -3790,7 +3787,7 @@
         <v>0</v>
       </c>
       <c r="E69">
-        <v>0.61099999999999999</v>
+        <v>0.55700000000000005</v>
       </c>
       <c r="F69">
         <v>0</v>
@@ -3799,10 +3796,10 @@
         <v>0</v>
       </c>
       <c r="H69">
-        <v>45.828000000000003</v>
+        <v>38.018000000000001</v>
       </c>
       <c r="I69">
-        <v>1027.9829999999999</v>
+        <v>936.30499999999995</v>
       </c>
       <c r="J69" t="s">
         <v>17</v>
@@ -3811,7 +3808,7 @@
         <v>0</v>
       </c>
       <c r="L69">
-        <v>2.9990000000000001</v>
+        <v>2.7309999999999999</v>
       </c>
       <c r="M69">
         <v>0</v>
@@ -3820,24 +3817,24 @@
         <v>46247</v>
       </c>
       <c r="O69" s="3">
-        <v>0.87277777777777776</v>
-      </c>
-    </row>
-    <row r="70" spans="1:15" x14ac:dyDescent="0.3">
+        <v>0.84401620370370367</v>
+      </c>
+    </row>
+    <row r="70" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A70" s="1" t="s">
         <v>29</v>
       </c>
       <c r="B70">
-        <v>104</v>
+        <v>128</v>
       </c>
       <c r="C70" t="s">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="D70">
         <v>0</v>
       </c>
       <c r="E70">
-        <v>0.36499999999999999</v>
+        <v>0.57599999999999996</v>
       </c>
       <c r="F70">
         <v>0</v>
@@ -3846,10 +3843,10 @@
         <v>0</v>
       </c>
       <c r="H70">
-        <v>16.335000000000001</v>
+        <v>40.667000000000002</v>
       </c>
       <c r="I70">
-        <v>613.72799999999995</v>
+        <v>968.375</v>
       </c>
       <c r="J70" t="s">
         <v>17</v>
@@ -3858,7 +3855,7 @@
         <v>0</v>
       </c>
       <c r="L70">
-        <v>1.79</v>
+        <v>2.8250000000000002</v>
       </c>
       <c r="M70">
         <v>0</v>
@@ -3867,15 +3864,15 @@
         <v>46247</v>
       </c>
       <c r="O70" s="3">
-        <v>0.87430555555555556</v>
-      </c>
-    </row>
-    <row r="71" spans="1:15" x14ac:dyDescent="0.3">
+        <v>0.84495370370370371</v>
+      </c>
+    </row>
+    <row r="71" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A71" s="1" t="s">
         <v>29</v>
       </c>
       <c r="B71">
-        <v>108</v>
+        <v>131</v>
       </c>
       <c r="C71" t="s">
         <v>19</v>
@@ -3884,7 +3881,7 @@
         <v>0</v>
       </c>
       <c r="E71">
-        <v>0.41699999999999998</v>
+        <v>0.39300000000000002</v>
       </c>
       <c r="F71">
         <v>0</v>
@@ -3893,10 +3890,10 @@
         <v>0</v>
       </c>
       <c r="H71">
-        <v>21.335000000000001</v>
+        <v>18.983000000000001</v>
       </c>
       <c r="I71">
-        <v>701.39800000000002</v>
+        <v>661.61900000000003</v>
       </c>
       <c r="J71" t="s">
         <v>17</v>
@@ -3905,7 +3902,7 @@
         <v>0</v>
       </c>
       <c r="L71">
-        <v>2.0459999999999998</v>
+        <v>1.93</v>
       </c>
       <c r="M71">
         <v>0</v>
@@ -3914,15 +3911,15 @@
         <v>46247</v>
       </c>
       <c r="O71" s="3">
-        <v>0.87512731481481476</v>
-      </c>
-    </row>
-    <row r="72" spans="1:15" x14ac:dyDescent="0.3">
+        <v>0.84611111111111115</v>
+      </c>
+    </row>
+    <row r="72" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A72" s="1" t="s">
         <v>29</v>
       </c>
       <c r="B72">
-        <v>112</v>
+        <v>134</v>
       </c>
       <c r="C72" t="s">
         <v>19</v>
@@ -3931,7 +3928,7 @@
         <v>0</v>
       </c>
       <c r="E72">
-        <v>0.42799999999999999</v>
+        <v>0.39</v>
       </c>
       <c r="F72">
         <v>0</v>
@@ -3940,10 +3937,10 @@
         <v>0</v>
       </c>
       <c r="H72">
-        <v>22.507000000000001</v>
+        <v>18.619</v>
       </c>
       <c r="I72">
-        <v>720.41899999999998</v>
+        <v>655.24199999999996</v>
       </c>
       <c r="J72" t="s">
         <v>17</v>
@@ -3952,7 +3949,7 @@
         <v>0</v>
       </c>
       <c r="L72">
-        <v>2.101</v>
+        <v>1.911</v>
       </c>
       <c r="M72">
         <v>0</v>
@@ -3961,15 +3958,15 @@
         <v>46247</v>
       </c>
       <c r="O72" s="3">
-        <v>0.87619212962962967</v>
-      </c>
-    </row>
-    <row r="73" spans="1:15" x14ac:dyDescent="0.3">
+        <v>0.84696759259259258</v>
+      </c>
+    </row>
+    <row r="73" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A73" s="1" t="s">
         <v>29</v>
       </c>
       <c r="B73">
-        <v>116</v>
+        <v>137</v>
       </c>
       <c r="C73" t="s">
         <v>18</v>
@@ -3978,7 +3975,7 @@
         <v>0</v>
       </c>
       <c r="E73">
-        <v>0.439</v>
+        <v>0.33600000000000002</v>
       </c>
       <c r="F73">
         <v>0</v>
@@ -3987,10 +3984,10 @@
         <v>0</v>
       </c>
       <c r="H73">
-        <v>23.597999999999999</v>
+        <v>13.879</v>
       </c>
       <c r="I73">
-        <v>737.66600000000005</v>
+        <v>565.73</v>
       </c>
       <c r="J73" t="s">
         <v>17</v>
@@ -3999,7 +3996,7 @@
         <v>0</v>
       </c>
       <c r="L73">
-        <v>2.1520000000000001</v>
+        <v>1.65</v>
       </c>
       <c r="M73">
         <v>0</v>
@@ -4008,15 +4005,15 @@
         <v>46247</v>
       </c>
       <c r="O73" s="3">
-        <v>0.87699074074074079</v>
-      </c>
-    </row>
-    <row r="74" spans="1:15" x14ac:dyDescent="0.3">
+        <v>0.84788194444444442</v>
+      </c>
+    </row>
+    <row r="74" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A74" s="1" t="s">
         <v>29</v>
       </c>
       <c r="B74">
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="C74" t="s">
         <v>18</v>
@@ -4025,7 +4022,7 @@
         <v>0</v>
       </c>
       <c r="E74">
-        <v>0.44900000000000001</v>
+        <v>0.377</v>
       </c>
       <c r="F74">
         <v>0</v>
@@ -4034,10 +4031,10 @@
         <v>0</v>
       </c>
       <c r="H74">
-        <v>24.742999999999999</v>
+        <v>17.457000000000001</v>
       </c>
       <c r="I74">
-        <v>755.35599999999999</v>
+        <v>634.47199999999998</v>
       </c>
       <c r="J74" t="s">
         <v>17</v>
@@ -4046,7 +4043,7 @@
         <v>0</v>
       </c>
       <c r="L74">
-        <v>2.2029999999999998</v>
+        <v>1.851</v>
       </c>
       <c r="M74">
         <v>0</v>
@@ -4055,15 +4052,15 @@
         <v>46247</v>
       </c>
       <c r="O74" s="3">
-        <v>0.87832175925925926</v>
-      </c>
-    </row>
-    <row r="75" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+        <v>0.84837962962962965</v>
+      </c>
+    </row>
+    <row r="75" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A75" s="1" t="s">
         <v>30</v>
       </c>
       <c r="B75">
-        <v>125</v>
+        <v>93</v>
       </c>
       <c r="C75" t="s">
         <v>0</v>
@@ -4072,7 +4069,7 @@
         <v>0</v>
       </c>
       <c r="E75">
-        <v>0.55700000000000005</v>
+        <v>0.53700000000000003</v>
       </c>
       <c r="F75">
         <v>0</v>
@@ -4081,10 +4078,10 @@
         <v>0</v>
       </c>
       <c r="H75">
-        <v>38.018000000000001</v>
+        <v>35.348999999999997</v>
       </c>
       <c r="I75">
-        <v>936.30499999999995</v>
+        <v>902.83500000000004</v>
       </c>
       <c r="J75" t="s">
         <v>17</v>
@@ -4093,7 +4090,7 @@
         <v>0</v>
       </c>
       <c r="L75">
-        <v>2.7309999999999999</v>
+        <v>2.6339999999999999</v>
       </c>
       <c r="M75">
         <v>0</v>
@@ -4102,15 +4099,15 @@
         <v>46247</v>
       </c>
       <c r="O75" s="3">
-        <v>0.84401620370370367</v>
-      </c>
-    </row>
-    <row r="76" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+        <v>0.87035879629629631</v>
+      </c>
+    </row>
+    <row r="76" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A76" s="1" t="s">
         <v>30</v>
       </c>
       <c r="B76">
-        <v>128</v>
+        <v>97</v>
       </c>
       <c r="C76" t="s">
         <v>0</v>
@@ -4119,7 +4116,7 @@
         <v>0</v>
       </c>
       <c r="E76">
-        <v>0.57599999999999996</v>
+        <v>0.52400000000000002</v>
       </c>
       <c r="F76">
         <v>0</v>
@@ -4128,10 +4125,10 @@
         <v>0</v>
       </c>
       <c r="H76">
-        <v>40.667000000000002</v>
+        <v>33.618000000000002</v>
       </c>
       <c r="I76">
-        <v>968.375</v>
+        <v>880.46299999999997</v>
       </c>
       <c r="J76" t="s">
         <v>17</v>
@@ -4140,7 +4137,7 @@
         <v>0</v>
       </c>
       <c r="L76">
-        <v>2.8250000000000002</v>
+        <v>2.5680000000000001</v>
       </c>
       <c r="M76">
         <v>0</v>
@@ -4149,24 +4146,24 @@
         <v>46247</v>
       </c>
       <c r="O76" s="3">
-        <v>0.84495370370370371</v>
-      </c>
-    </row>
-    <row r="77" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+        <v>0.87193287037037037</v>
+      </c>
+    </row>
+    <row r="77" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A77" s="1" t="s">
         <v>30</v>
       </c>
       <c r="B77">
-        <v>131</v>
+        <v>101</v>
       </c>
       <c r="C77" t="s">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="D77">
         <v>0</v>
       </c>
       <c r="E77">
-        <v>0.39300000000000002</v>
+        <v>0.54300000000000004</v>
       </c>
       <c r="F77">
         <v>0</v>
@@ -4175,10 +4172,10 @@
         <v>0</v>
       </c>
       <c r="H77">
-        <v>18.983000000000001</v>
+        <v>36.195</v>
       </c>
       <c r="I77">
-        <v>661.61900000000003</v>
+        <v>913.58299999999997</v>
       </c>
       <c r="J77" t="s">
         <v>17</v>
@@ -4187,7 +4184,7 @@
         <v>0</v>
       </c>
       <c r="L77">
-        <v>1.93</v>
+        <v>2.665</v>
       </c>
       <c r="M77">
         <v>0</v>
@@ -4196,15 +4193,15 @@
         <v>46247</v>
       </c>
       <c r="O77" s="3">
-        <v>0.84611111111111115</v>
-      </c>
-    </row>
-    <row r="78" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+        <v>0.87327546296296299</v>
+      </c>
+    </row>
+    <row r="78" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A78" s="1" t="s">
         <v>30</v>
       </c>
       <c r="B78">
-        <v>134</v>
+        <v>105</v>
       </c>
       <c r="C78" t="s">
         <v>19</v>
@@ -4213,7 +4210,7 @@
         <v>0</v>
       </c>
       <c r="E78">
-        <v>0.39</v>
+        <v>0.36299999999999999</v>
       </c>
       <c r="F78">
         <v>0</v>
@@ -4222,10 +4219,10 @@
         <v>0</v>
       </c>
       <c r="H78">
-        <v>18.619</v>
+        <v>16.202000000000002</v>
       </c>
       <c r="I78">
-        <v>655.24199999999996</v>
+        <v>611.23900000000003</v>
       </c>
       <c r="J78" t="s">
         <v>17</v>
@@ -4234,7 +4231,7 @@
         <v>0</v>
       </c>
       <c r="L78">
-        <v>1.911</v>
+        <v>1.7829999999999999</v>
       </c>
       <c r="M78">
         <v>0</v>
@@ -4243,24 +4240,24 @@
         <v>46247</v>
       </c>
       <c r="O78" s="3">
-        <v>0.84696759259259258</v>
-      </c>
-    </row>
-    <row r="79" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+        <v>0.87442129629629628</v>
+      </c>
+    </row>
+    <row r="79" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A79" s="1" t="s">
         <v>30</v>
       </c>
       <c r="B79">
-        <v>137</v>
+        <v>109</v>
       </c>
       <c r="C79" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D79">
         <v>0</v>
       </c>
       <c r="E79">
-        <v>0.33600000000000002</v>
+        <v>0.38400000000000001</v>
       </c>
       <c r="F79">
         <v>0</v>
@@ -4269,10 +4266,10 @@
         <v>0</v>
       </c>
       <c r="H79">
-        <v>13.879</v>
+        <v>18.125</v>
       </c>
       <c r="I79">
-        <v>565.73</v>
+        <v>646.48500000000001</v>
       </c>
       <c r="J79" t="s">
         <v>17</v>
@@ -4281,7 +4278,7 @@
         <v>0</v>
       </c>
       <c r="L79">
-        <v>1.65</v>
+        <v>1.8859999999999999</v>
       </c>
       <c r="M79">
         <v>0</v>
@@ -4290,24 +4287,24 @@
         <v>46247</v>
       </c>
       <c r="O79" s="3">
-        <v>0.84788194444444442</v>
-      </c>
-    </row>
-    <row r="80" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+        <v>0.87541666666666662</v>
+      </c>
+    </row>
+    <row r="80" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A80" s="1" t="s">
         <v>30</v>
       </c>
       <c r="B80">
-        <v>140</v>
+        <v>113</v>
       </c>
       <c r="C80" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D80">
         <v>0</v>
       </c>
       <c r="E80">
-        <v>0.377</v>
+        <v>0.40100000000000002</v>
       </c>
       <c r="F80">
         <v>0</v>
@@ -4316,10 +4313,10 @@
         <v>0</v>
       </c>
       <c r="H80">
-        <v>17.457000000000001</v>
+        <v>19.748999999999999</v>
       </c>
       <c r="I80">
-        <v>634.47199999999998</v>
+        <v>674.82899999999995</v>
       </c>
       <c r="J80" t="s">
         <v>17</v>
@@ -4328,7 +4325,7 @@
         <v>0</v>
       </c>
       <c r="L80">
-        <v>1.851</v>
+        <v>1.968</v>
       </c>
       <c r="M80">
         <v>0</v>
@@ -4337,24 +4334,24 @@
         <v>46247</v>
       </c>
       <c r="O80" s="3">
-        <v>0.84837962962962965</v>
+        <v>0.87633101851851847</v>
       </c>
     </row>
     <row r="81" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A81" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B81">
-        <v>93</v>
+        <v>117</v>
       </c>
       <c r="C81" t="s">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="D81">
         <v>0</v>
       </c>
       <c r="E81">
-        <v>0.53700000000000003</v>
+        <v>0.36299999999999999</v>
       </c>
       <c r="F81">
         <v>0</v>
@@ -4363,10 +4360,10 @@
         <v>0</v>
       </c>
       <c r="H81">
-        <v>35.348999999999997</v>
+        <v>16.143999999999998</v>
       </c>
       <c r="I81">
-        <v>902.83500000000004</v>
+        <v>610.13599999999997</v>
       </c>
       <c r="J81" t="s">
         <v>17</v>
@@ -4375,7 +4372,7 @@
         <v>0</v>
       </c>
       <c r="L81">
-        <v>2.6339999999999999</v>
+        <v>1.78</v>
       </c>
       <c r="M81">
         <v>0</v>
@@ -4384,24 +4381,24 @@
         <v>46247</v>
       </c>
       <c r="O81" s="3">
-        <v>0.87035879629629631</v>
+        <v>0.87732638888888892</v>
       </c>
     </row>
     <row r="82" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A82" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B82">
-        <v>97</v>
+        <v>121</v>
       </c>
       <c r="C82" t="s">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="D82">
         <v>0</v>
       </c>
       <c r="E82">
-        <v>0.52400000000000002</v>
+        <v>0.372</v>
       </c>
       <c r="F82">
         <v>0</v>
@@ -4410,10 +4407,10 @@
         <v>0</v>
       </c>
       <c r="H82">
-        <v>33.618000000000002</v>
+        <v>16.972999999999999</v>
       </c>
       <c r="I82">
-        <v>880.46299999999997</v>
+        <v>625.60699999999997</v>
       </c>
       <c r="J82" t="s">
         <v>17</v>
@@ -4422,7 +4419,7 @@
         <v>0</v>
       </c>
       <c r="L82">
-        <v>2.5680000000000001</v>
+        <v>1.825</v>
       </c>
       <c r="M82">
         <v>0</v>
@@ -4431,7 +4428,7 @@
         <v>46247</v>
       </c>
       <c r="O82" s="3">
-        <v>0.87193287037037037</v>
+        <v>0.87866898148148154</v>
       </c>
     </row>
     <row r="83" spans="1:15" x14ac:dyDescent="0.3">
@@ -4439,7 +4436,7 @@
         <v>31</v>
       </c>
       <c r="B83">
-        <v>101</v>
+        <v>192</v>
       </c>
       <c r="C83" t="s">
         <v>0</v>
@@ -4448,7 +4445,7 @@
         <v>0</v>
       </c>
       <c r="E83">
-        <v>0.54300000000000004</v>
+        <v>0.52</v>
       </c>
       <c r="F83">
         <v>0</v>
@@ -4457,10 +4454,10 @@
         <v>0</v>
       </c>
       <c r="H83">
-        <v>36.195</v>
+        <v>33.219000000000001</v>
       </c>
       <c r="I83">
-        <v>913.58299999999997</v>
+        <v>875.21699999999998</v>
       </c>
       <c r="J83" t="s">
         <v>17</v>
@@ -4469,7 +4466,7 @@
         <v>0</v>
       </c>
       <c r="L83">
-        <v>2.665</v>
+        <v>2.5529999999999999</v>
       </c>
       <c r="M83">
         <v>0</v>
@@ -4478,7 +4475,7 @@
         <v>46247</v>
       </c>
       <c r="O83" s="3">
-        <v>0.87327546296296299</v>
+        <v>0.87642361111111111</v>
       </c>
     </row>
     <row r="84" spans="1:15" x14ac:dyDescent="0.3">
@@ -4486,16 +4483,16 @@
         <v>31</v>
       </c>
       <c r="B84">
-        <v>105</v>
+        <v>195</v>
       </c>
       <c r="C84" t="s">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="D84">
         <v>0</v>
       </c>
       <c r="E84">
-        <v>0.36299999999999999</v>
+        <v>0.53500000000000003</v>
       </c>
       <c r="F84">
         <v>0</v>
@@ -4504,10 +4501,10 @@
         <v>0</v>
       </c>
       <c r="H84">
-        <v>16.202000000000002</v>
+        <v>35.097000000000001</v>
       </c>
       <c r="I84">
-        <v>611.23900000000003</v>
+        <v>899.62</v>
       </c>
       <c r="J84" t="s">
         <v>17</v>
@@ -4516,7 +4513,7 @@
         <v>0</v>
       </c>
       <c r="L84">
-        <v>1.7829999999999999</v>
+        <v>2.6240000000000001</v>
       </c>
       <c r="M84">
         <v>0</v>
@@ -4525,7 +4522,7 @@
         <v>46247</v>
       </c>
       <c r="O84" s="3">
-        <v>0.87442129629629628</v>
+        <v>0.87725694444444446</v>
       </c>
     </row>
     <row r="85" spans="1:15" x14ac:dyDescent="0.3">
@@ -4533,7 +4530,7 @@
         <v>31</v>
       </c>
       <c r="B85">
-        <v>109</v>
+        <v>198</v>
       </c>
       <c r="C85" t="s">
         <v>19</v>
@@ -4542,7 +4539,7 @@
         <v>0</v>
       </c>
       <c r="E85">
-        <v>0.38400000000000001</v>
+        <v>0.376</v>
       </c>
       <c r="F85">
         <v>0</v>
@@ -4551,10 +4548,10 @@
         <v>0</v>
       </c>
       <c r="H85">
-        <v>18.125</v>
+        <v>17.297999999999998</v>
       </c>
       <c r="I85">
-        <v>646.48500000000001</v>
+        <v>631.56600000000003</v>
       </c>
       <c r="J85" t="s">
         <v>17</v>
@@ -4563,7 +4560,7 @@
         <v>0</v>
       </c>
       <c r="L85">
-        <v>1.8859999999999999</v>
+        <v>1.8420000000000001</v>
       </c>
       <c r="M85">
         <v>0</v>
@@ -4572,7 +4569,7 @@
         <v>46247</v>
       </c>
       <c r="O85" s="3">
-        <v>0.87541666666666662</v>
+        <v>0.87887731481481479</v>
       </c>
     </row>
     <row r="86" spans="1:15" x14ac:dyDescent="0.3">
@@ -4580,7 +4577,7 @@
         <v>31</v>
       </c>
       <c r="B86">
-        <v>113</v>
+        <v>201</v>
       </c>
       <c r="C86" t="s">
         <v>19</v>
@@ -4589,7 +4586,7 @@
         <v>0</v>
       </c>
       <c r="E86">
-        <v>0.40100000000000002</v>
+        <v>0.41</v>
       </c>
       <c r="F86">
         <v>0</v>
@@ -4598,10 +4595,10 @@
         <v>0</v>
       </c>
       <c r="H86">
-        <v>19.748999999999999</v>
+        <v>20.658000000000001</v>
       </c>
       <c r="I86">
-        <v>674.82899999999995</v>
+        <v>690.178</v>
       </c>
       <c r="J86" t="s">
         <v>17</v>
@@ -4610,7 +4607,7 @@
         <v>0</v>
       </c>
       <c r="L86">
-        <v>1.968</v>
+        <v>2.0129999999999999</v>
       </c>
       <c r="M86">
         <v>0</v>
@@ -4619,7 +4616,7 @@
         <v>46247</v>
       </c>
       <c r="O86" s="3">
-        <v>0.87633101851851847</v>
+        <v>0.88025462962962964</v>
       </c>
     </row>
     <row r="87" spans="1:15" x14ac:dyDescent="0.3">
@@ -4627,7 +4624,7 @@
         <v>31</v>
       </c>
       <c r="B87">
-        <v>117</v>
+        <v>202</v>
       </c>
       <c r="C87" t="s">
         <v>18</v>
@@ -4636,7 +4633,7 @@
         <v>0</v>
       </c>
       <c r="E87">
-        <v>0.36299999999999999</v>
+        <v>0.41599999999999998</v>
       </c>
       <c r="F87">
         <v>0</v>
@@ -4645,10 +4642,10 @@
         <v>0</v>
       </c>
       <c r="H87">
-        <v>16.143999999999998</v>
+        <v>21.248999999999999</v>
       </c>
       <c r="I87">
-        <v>610.13599999999997</v>
+        <v>699.98500000000001</v>
       </c>
       <c r="J87" t="s">
         <v>17</v>
@@ -4657,7 +4654,7 @@
         <v>0</v>
       </c>
       <c r="L87">
-        <v>1.78</v>
+        <v>2.0419999999999998</v>
       </c>
       <c r="M87">
         <v>0</v>
@@ -4666,7 +4663,7 @@
         <v>46247</v>
       </c>
       <c r="O87" s="3">
-        <v>0.87732638888888892</v>
+        <v>0.88061342592592595</v>
       </c>
     </row>
     <row r="88" spans="1:15" x14ac:dyDescent="0.3">
@@ -4674,7 +4671,7 @@
         <v>31</v>
       </c>
       <c r="B88">
-        <v>121</v>
+        <v>205</v>
       </c>
       <c r="C88" t="s">
         <v>18</v>
@@ -4683,7 +4680,7 @@
         <v>0</v>
       </c>
       <c r="E88">
-        <v>0.372</v>
+        <v>0.40500000000000003</v>
       </c>
       <c r="F88">
         <v>0</v>
@@ -4692,10 +4689,10 @@
         <v>0</v>
       </c>
       <c r="H88">
-        <v>16.972999999999999</v>
+        <v>20.077999999999999</v>
       </c>
       <c r="I88">
-        <v>625.60699999999997</v>
+        <v>680.42499999999995</v>
       </c>
       <c r="J88" t="s">
         <v>17</v>
@@ -4704,7 +4701,7 @@
         <v>0</v>
       </c>
       <c r="L88">
-        <v>1.825</v>
+        <v>1.9850000000000001</v>
       </c>
       <c r="M88">
         <v>0</v>
@@ -4713,15 +4710,15 @@
         <v>46247</v>
       </c>
       <c r="O88" s="3">
-        <v>0.87866898148148154</v>
-      </c>
-    </row>
-    <row r="89" spans="1:15" x14ac:dyDescent="0.3">
+        <v>0.88112268518518522</v>
+      </c>
+    </row>
+    <row r="89" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A89" s="1" t="s">
         <v>32</v>
       </c>
       <c r="B89">
-        <v>192</v>
+        <v>67</v>
       </c>
       <c r="C89" t="s">
         <v>0</v>
@@ -4730,7 +4727,7 @@
         <v>0</v>
       </c>
       <c r="E89">
-        <v>0.52</v>
+        <v>0.56599999999999995</v>
       </c>
       <c r="F89">
         <v>0</v>
@@ -4739,10 +4736,10 @@
         <v>0</v>
       </c>
       <c r="H89">
-        <v>33.219000000000001</v>
+        <v>39.348999999999997</v>
       </c>
       <c r="I89">
-        <v>875.21699999999998</v>
+        <v>952.55499999999995</v>
       </c>
       <c r="J89" t="s">
         <v>17</v>
@@ -4751,7 +4748,7 @@
         <v>0</v>
       </c>
       <c r="L89">
-        <v>2.5529999999999999</v>
+        <v>2.7789999999999999</v>
       </c>
       <c r="M89">
         <v>0</v>
@@ -4760,15 +4757,15 @@
         <v>46247</v>
       </c>
       <c r="O89" s="3">
-        <v>0.87642361111111111</v>
-      </c>
-    </row>
-    <row r="90" spans="1:15" x14ac:dyDescent="0.3">
+        <v>0.86038194444444449</v>
+      </c>
+    </row>
+    <row r="90" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A90" s="1" t="s">
         <v>32</v>
       </c>
       <c r="B90">
-        <v>195</v>
+        <v>70</v>
       </c>
       <c r="C90" t="s">
         <v>0</v>
@@ -4777,7 +4774,7 @@
         <v>0</v>
       </c>
       <c r="E90">
-        <v>0.53500000000000003</v>
+        <v>0.59099999999999997</v>
       </c>
       <c r="F90">
         <v>0</v>
@@ -4786,10 +4783,10 @@
         <v>0</v>
       </c>
       <c r="H90">
-        <v>35.097000000000001</v>
+        <v>42.863999999999997</v>
       </c>
       <c r="I90">
-        <v>899.62</v>
+        <v>994.19</v>
       </c>
       <c r="J90" t="s">
         <v>17</v>
@@ -4798,7 +4795,7 @@
         <v>0</v>
       </c>
       <c r="L90">
-        <v>2.6240000000000001</v>
+        <v>2.9</v>
       </c>
       <c r="M90">
         <v>0</v>
@@ -4807,24 +4804,24 @@
         <v>46247</v>
       </c>
       <c r="O90" s="3">
-        <v>0.87725694444444446</v>
-      </c>
-    </row>
-    <row r="91" spans="1:15" x14ac:dyDescent="0.3">
+        <v>0.86106481481481478</v>
+      </c>
+    </row>
+    <row r="91" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A91" s="1" t="s">
         <v>32</v>
       </c>
       <c r="B91">
-        <v>198</v>
+        <v>73</v>
       </c>
       <c r="C91" t="s">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="D91">
         <v>0</v>
       </c>
       <c r="E91">
-        <v>0.376</v>
+        <v>0.59099999999999997</v>
       </c>
       <c r="F91">
         <v>0</v>
@@ -4833,10 +4830,10 @@
         <v>0</v>
       </c>
       <c r="H91">
-        <v>17.297999999999998</v>
+        <v>42.881999999999998</v>
       </c>
       <c r="I91">
-        <v>631.56600000000003</v>
+        <v>994.39200000000005</v>
       </c>
       <c r="J91" t="s">
         <v>17</v>
@@ -4845,7 +4842,7 @@
         <v>0</v>
       </c>
       <c r="L91">
-        <v>1.8420000000000001</v>
+        <v>2.9009999999999998</v>
       </c>
       <c r="M91">
         <v>0</v>
@@ -4854,15 +4851,15 @@
         <v>46247</v>
       </c>
       <c r="O91" s="3">
-        <v>0.87887731481481479</v>
-      </c>
-    </row>
-    <row r="92" spans="1:15" x14ac:dyDescent="0.3">
+        <v>0.86193287037037036</v>
+      </c>
+    </row>
+    <row r="92" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A92" s="1" t="s">
         <v>32</v>
       </c>
       <c r="B92">
-        <v>201</v>
+        <v>76</v>
       </c>
       <c r="C92" t="s">
         <v>19</v>
@@ -4871,7 +4868,7 @@
         <v>0</v>
       </c>
       <c r="E92">
-        <v>0.41</v>
+        <v>0.36699999999999999</v>
       </c>
       <c r="F92">
         <v>0</v>
@@ -4880,10 +4877,10 @@
         <v>0</v>
       </c>
       <c r="H92">
-        <v>20.658000000000001</v>
+        <v>16.545999999999999</v>
       </c>
       <c r="I92">
-        <v>690.178</v>
+        <v>617.68299999999999</v>
       </c>
       <c r="J92" t="s">
         <v>17</v>
@@ -4892,7 +4889,7 @@
         <v>0</v>
       </c>
       <c r="L92">
-        <v>2.0129999999999999</v>
+        <v>1.802</v>
       </c>
       <c r="M92">
         <v>0</v>
@@ -4901,24 +4898,24 @@
         <v>46247</v>
       </c>
       <c r="O92" s="3">
-        <v>0.88025462962962964</v>
-      </c>
-    </row>
-    <row r="93" spans="1:15" x14ac:dyDescent="0.3">
+        <v>0.86327546296296298</v>
+      </c>
+    </row>
+    <row r="93" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A93" s="1" t="s">
         <v>32</v>
       </c>
       <c r="B93">
-        <v>202</v>
+        <v>79</v>
       </c>
       <c r="C93" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D93">
         <v>0</v>
       </c>
       <c r="E93">
-        <v>0.41599999999999998</v>
+        <v>0.377</v>
       </c>
       <c r="F93">
         <v>0</v>
@@ -4927,10 +4924,10 @@
         <v>0</v>
       </c>
       <c r="H93">
-        <v>21.248999999999999</v>
+        <v>17.396999999999998</v>
       </c>
       <c r="I93">
-        <v>699.98500000000001</v>
+        <v>633.36900000000003</v>
       </c>
       <c r="J93" t="s">
         <v>17</v>
@@ -4939,7 +4936,7 @@
         <v>0</v>
       </c>
       <c r="L93">
-        <v>2.0419999999999998</v>
+        <v>1.847</v>
       </c>
       <c r="M93">
         <v>0</v>
@@ -4948,24 +4945,24 @@
         <v>46247</v>
       </c>
       <c r="O93" s="3">
-        <v>0.88061342592592595</v>
-      </c>
-    </row>
-    <row r="94" spans="1:15" x14ac:dyDescent="0.3">
+        <v>0.86449074074074073</v>
+      </c>
+    </row>
+    <row r="94" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A94" s="1" t="s">
         <v>32</v>
       </c>
       <c r="B94">
-        <v>205</v>
+        <v>82</v>
       </c>
       <c r="C94" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D94">
         <v>0</v>
       </c>
       <c r="E94">
-        <v>0.40500000000000003</v>
+        <v>0.374</v>
       </c>
       <c r="F94">
         <v>0</v>
@@ -4974,10 +4971,10 @@
         <v>0</v>
       </c>
       <c r="H94">
-        <v>20.077999999999999</v>
+        <v>17.126999999999999</v>
       </c>
       <c r="I94">
-        <v>680.42499999999995</v>
+        <v>628.43200000000002</v>
       </c>
       <c r="J94" t="s">
         <v>17</v>
@@ -4986,7 +4983,7 @@
         <v>0</v>
       </c>
       <c r="L94">
-        <v>1.9850000000000001</v>
+        <v>1.833</v>
       </c>
       <c r="M94">
         <v>0</v>
@@ -4995,24 +4992,24 @@
         <v>46247</v>
       </c>
       <c r="O94" s="3">
-        <v>0.88112268518518522</v>
+        <v>0.86535879629629631</v>
       </c>
     </row>
     <row r="95" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A95" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B95">
-        <v>67</v>
+        <v>85</v>
       </c>
       <c r="C95" t="s">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="D95">
         <v>0</v>
       </c>
       <c r="E95">
-        <v>0.56599999999999995</v>
+        <v>0.38500000000000001</v>
       </c>
       <c r="F95">
         <v>0</v>
@@ -5021,10 +5018,10 @@
         <v>0</v>
       </c>
       <c r="H95">
-        <v>39.348999999999997</v>
+        <v>18.158999999999999</v>
       </c>
       <c r="I95">
-        <v>952.55499999999995</v>
+        <v>647.10400000000004</v>
       </c>
       <c r="J95" t="s">
         <v>17</v>
@@ -5033,7 +5030,7 @@
         <v>0</v>
       </c>
       <c r="L95">
-        <v>2.7789999999999999</v>
+        <v>1.8879999999999999</v>
       </c>
       <c r="M95">
         <v>0</v>
@@ -5042,24 +5039,24 @@
         <v>46247</v>
       </c>
       <c r="O95" s="3">
-        <v>0.86038194444444449</v>
+        <v>0.86591435185185184</v>
       </c>
     </row>
     <row r="96" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A96" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B96">
-        <v>70</v>
+        <v>88</v>
       </c>
       <c r="C96" t="s">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="D96">
         <v>0</v>
       </c>
       <c r="E96">
-        <v>0.59099999999999997</v>
+        <v>0.375</v>
       </c>
       <c r="F96">
         <v>0</v>
@@ -5068,10 +5065,10 @@
         <v>0</v>
       </c>
       <c r="H96">
-        <v>42.863999999999997</v>
+        <v>17.254000000000001</v>
       </c>
       <c r="I96">
-        <v>994.19</v>
+        <v>630.75900000000001</v>
       </c>
       <c r="J96" t="s">
         <v>17</v>
@@ -5080,7 +5077,7 @@
         <v>0</v>
       </c>
       <c r="L96">
-        <v>2.9</v>
+        <v>1.84</v>
       </c>
       <c r="M96">
         <v>0</v>
@@ -5089,24 +5086,24 @@
         <v>46247</v>
       </c>
       <c r="O96" s="3">
-        <v>0.86106481481481478</v>
+        <v>0.86694444444444441</v>
       </c>
     </row>
     <row r="97" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A97" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B97">
-        <v>73</v>
+        <v>91</v>
       </c>
       <c r="C97" t="s">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="D97">
         <v>0</v>
       </c>
       <c r="E97">
-        <v>0.59099999999999997</v>
+        <v>0.38500000000000001</v>
       </c>
       <c r="F97">
         <v>0</v>
@@ -5115,10 +5112,10 @@
         <v>0</v>
       </c>
       <c r="H97">
-        <v>42.881999999999998</v>
+        <v>18.178000000000001</v>
       </c>
       <c r="I97">
-        <v>994.39200000000005</v>
+        <v>647.44000000000005</v>
       </c>
       <c r="J97" t="s">
         <v>17</v>
@@ -5127,7 +5124,7 @@
         <v>0</v>
       </c>
       <c r="L97">
-        <v>2.9009999999999998</v>
+        <v>1.889</v>
       </c>
       <c r="M97">
         <v>0</v>
@@ -5136,24 +5133,24 @@
         <v>46247</v>
       </c>
       <c r="O97" s="3">
-        <v>0.86193287037037036</v>
-      </c>
-    </row>
-    <row r="98" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+        <v>0.86752314814814813</v>
+      </c>
+    </row>
+    <row r="98" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A98" s="1" t="s">
         <v>33</v>
       </c>
       <c r="B98">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="C98" t="s">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="D98">
         <v>0</v>
       </c>
       <c r="E98">
-        <v>0.36699999999999999</v>
+        <v>0.55400000000000005</v>
       </c>
       <c r="F98">
         <v>0</v>
@@ -5162,10 +5159,10 @@
         <v>0</v>
       </c>
       <c r="H98">
-        <v>16.545999999999999</v>
+        <v>37.64</v>
       </c>
       <c r="I98">
-        <v>617.68299999999999</v>
+        <v>931.63699999999994</v>
       </c>
       <c r="J98" t="s">
         <v>17</v>
@@ -5174,7 +5171,7 @@
         <v>0</v>
       </c>
       <c r="L98">
-        <v>1.802</v>
+        <v>2.718</v>
       </c>
       <c r="M98">
         <v>0</v>
@@ -5183,24 +5180,24 @@
         <v>46247</v>
       </c>
       <c r="O98" s="3">
-        <v>0.86327546296296298</v>
-      </c>
-    </row>
-    <row r="99" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+        <v>0.87085648148148154</v>
+      </c>
+    </row>
+    <row r="99" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A99" s="1" t="s">
         <v>33</v>
       </c>
       <c r="B99">
-        <v>79</v>
+        <v>98</v>
       </c>
       <c r="C99" t="s">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="D99">
         <v>0</v>
       </c>
       <c r="E99">
-        <v>0.377</v>
+        <v>0.55100000000000005</v>
       </c>
       <c r="F99">
         <v>0</v>
@@ -5209,10 +5206,10 @@
         <v>0</v>
       </c>
       <c r="H99">
-        <v>17.396999999999998</v>
+        <v>37.168999999999997</v>
       </c>
       <c r="I99">
-        <v>633.36900000000003</v>
+        <v>925.78499999999997</v>
       </c>
       <c r="J99" t="s">
         <v>17</v>
@@ -5221,7 +5218,7 @@
         <v>0</v>
       </c>
       <c r="L99">
-        <v>1.847</v>
+        <v>2.7</v>
       </c>
       <c r="M99">
         <v>0</v>
@@ -5230,24 +5227,24 @@
         <v>46247</v>
       </c>
       <c r="O99" s="3">
-        <v>0.86449074074074073</v>
-      </c>
-    </row>
-    <row r="100" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+        <v>0.87224537037037042</v>
+      </c>
+    </row>
+    <row r="100" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A100" s="1" t="s">
         <v>33</v>
       </c>
       <c r="B100">
-        <v>82</v>
+        <v>102</v>
       </c>
       <c r="C100" t="s">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="D100">
         <v>0</v>
       </c>
       <c r="E100">
-        <v>0.374</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="F100">
         <v>0</v>
@@ -5256,10 +5253,10 @@
         <v>0</v>
       </c>
       <c r="H100">
-        <v>17.126999999999999</v>
+        <v>37.070999999999998</v>
       </c>
       <c r="I100">
-        <v>628.43200000000002</v>
+        <v>924.57399999999996</v>
       </c>
       <c r="J100" t="s">
         <v>17</v>
@@ -5268,7 +5265,7 @@
         <v>0</v>
       </c>
       <c r="L100">
-        <v>1.833</v>
+        <v>2.6970000000000001</v>
       </c>
       <c r="M100">
         <v>0</v>
@@ -5277,24 +5274,24 @@
         <v>46247</v>
       </c>
       <c r="O100" s="3">
-        <v>0.86535879629629631</v>
-      </c>
-    </row>
-    <row r="101" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+        <v>0.87349537037037039</v>
+      </c>
+    </row>
+    <row r="101" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A101" s="1" t="s">
         <v>33</v>
       </c>
       <c r="B101">
-        <v>85</v>
+        <v>106</v>
       </c>
       <c r="C101" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D101">
         <v>0</v>
       </c>
       <c r="E101">
-        <v>0.38500000000000001</v>
+        <v>0.36199999999999999</v>
       </c>
       <c r="F101">
         <v>0</v>
@@ -5303,10 +5300,10 @@
         <v>0</v>
       </c>
       <c r="H101">
-        <v>18.158999999999999</v>
+        <v>16.085000000000001</v>
       </c>
       <c r="I101">
-        <v>647.10400000000004</v>
+        <v>609.02</v>
       </c>
       <c r="J101" t="s">
         <v>17</v>
@@ -5315,7 +5312,7 @@
         <v>0</v>
       </c>
       <c r="L101">
-        <v>1.8879999999999999</v>
+        <v>1.776</v>
       </c>
       <c r="M101">
         <v>0</v>
@@ -5324,24 +5321,24 @@
         <v>46247</v>
       </c>
       <c r="O101" s="3">
-        <v>0.86591435185185184</v>
-      </c>
-    </row>
-    <row r="102" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+        <v>0.87486111111111109</v>
+      </c>
+    </row>
+    <row r="102" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A102" s="1" t="s">
         <v>33</v>
       </c>
       <c r="B102">
-        <v>88</v>
+        <v>110</v>
       </c>
       <c r="C102" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D102">
         <v>0</v>
       </c>
       <c r="E102">
-        <v>0.375</v>
+        <v>0.38900000000000001</v>
       </c>
       <c r="F102">
         <v>0</v>
@@ -5350,10 +5347,10 @@
         <v>0</v>
       </c>
       <c r="H102">
-        <v>17.254000000000001</v>
+        <v>18.532</v>
       </c>
       <c r="I102">
-        <v>630.75900000000001</v>
+        <v>653.70899999999995</v>
       </c>
       <c r="J102" t="s">
         <v>17</v>
@@ -5362,7 +5359,7 @@
         <v>0</v>
       </c>
       <c r="L102">
-        <v>1.84</v>
+        <v>1.907</v>
       </c>
       <c r="M102">
         <v>0</v>
@@ -5371,24 +5368,24 @@
         <v>46247</v>
       </c>
       <c r="O102" s="3">
-        <v>0.86694444444444441</v>
-      </c>
-    </row>
-    <row r="103" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+        <v>0.87561342592592595</v>
+      </c>
+    </row>
+    <row r="103" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A103" s="1" t="s">
         <v>33</v>
       </c>
       <c r="B103">
-        <v>91</v>
+        <v>114</v>
       </c>
       <c r="C103" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D103">
         <v>0</v>
       </c>
       <c r="E103">
-        <v>0.38500000000000001</v>
+        <v>0.40799999999999997</v>
       </c>
       <c r="F103">
         <v>0</v>
@@ -5397,10 +5394,10 @@
         <v>0</v>
       </c>
       <c r="H103">
-        <v>18.178000000000001</v>
+        <v>20.411000000000001</v>
       </c>
       <c r="I103">
-        <v>647.44000000000005</v>
+        <v>686.048</v>
       </c>
       <c r="J103" t="s">
         <v>17</v>
@@ -5409,7 +5406,7 @@
         <v>0</v>
       </c>
       <c r="L103">
-        <v>1.889</v>
+        <v>2.0009999999999999</v>
       </c>
       <c r="M103">
         <v>0</v>
@@ -5418,24 +5415,24 @@
         <v>46247</v>
       </c>
       <c r="O103" s="3">
-        <v>0.86752314814814813</v>
+        <v>0.8765856481481481</v>
       </c>
     </row>
     <row r="104" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A104" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B104">
-        <v>94</v>
+        <v>118</v>
       </c>
       <c r="C104" t="s">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="D104">
         <v>0</v>
       </c>
       <c r="E104">
-        <v>0.55400000000000005</v>
+        <v>0.39200000000000002</v>
       </c>
       <c r="F104">
         <v>0</v>
@@ -5444,10 +5441,10 @@
         <v>0</v>
       </c>
       <c r="H104">
-        <v>37.64</v>
+        <v>18.867999999999999</v>
       </c>
       <c r="I104">
-        <v>931.63699999999994</v>
+        <v>659.61400000000003</v>
       </c>
       <c r="J104" t="s">
         <v>17</v>
@@ -5456,7 +5453,7 @@
         <v>0</v>
       </c>
       <c r="L104">
-        <v>2.718</v>
+        <v>1.9239999999999999</v>
       </c>
       <c r="M104">
         <v>0</v>
@@ -5465,24 +5462,24 @@
         <v>46247</v>
       </c>
       <c r="O104" s="3">
-        <v>0.87085648148148154</v>
+        <v>0.87753472222222217</v>
       </c>
     </row>
     <row r="105" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A105" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B105">
-        <v>98</v>
+        <v>122</v>
       </c>
       <c r="C105" t="s">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="D105">
         <v>0</v>
       </c>
       <c r="E105">
-        <v>0.55100000000000005</v>
+        <v>0.39</v>
       </c>
       <c r="F105">
         <v>0</v>
@@ -5491,10 +5488,10 @@
         <v>0</v>
       </c>
       <c r="H105">
-        <v>37.168999999999997</v>
+        <v>18.643999999999998</v>
       </c>
       <c r="I105">
-        <v>925.78499999999997</v>
+        <v>655.673</v>
       </c>
       <c r="J105" t="s">
         <v>17</v>
@@ -5503,7 +5500,7 @@
         <v>0</v>
       </c>
       <c r="L105">
-        <v>2.7</v>
+        <v>1.913</v>
       </c>
       <c r="M105">
         <v>0</v>
@@ -5512,7 +5509,7 @@
         <v>46247</v>
       </c>
       <c r="O105" s="3">
-        <v>0.87224537037037042</v>
+        <v>0.87880787037037034</v>
       </c>
     </row>
     <row r="106" spans="1:15" x14ac:dyDescent="0.3">
@@ -5520,7 +5517,7 @@
         <v>34</v>
       </c>
       <c r="B106">
-        <v>102</v>
+        <v>38</v>
       </c>
       <c r="C106" t="s">
         <v>0</v>
@@ -5529,7 +5526,7 @@
         <v>0</v>
       </c>
       <c r="E106">
-        <v>0.55000000000000004</v>
+        <v>0.53800000000000003</v>
       </c>
       <c r="F106">
         <v>0</v>
@@ -5538,10 +5535,10 @@
         <v>0</v>
       </c>
       <c r="H106">
-        <v>37.070999999999998</v>
+        <v>35.433</v>
       </c>
       <c r="I106">
-        <v>924.57399999999996</v>
+        <v>903.91099999999994</v>
       </c>
       <c r="J106" t="s">
         <v>17</v>
@@ -5550,7 +5547,7 @@
         <v>0</v>
       </c>
       <c r="L106">
-        <v>2.6970000000000001</v>
+        <v>2.637</v>
       </c>
       <c r="M106">
         <v>0</v>
@@ -5559,7 +5556,7 @@
         <v>46247</v>
       </c>
       <c r="O106" s="3">
-        <v>0.87349537037037039</v>
+        <v>0.85239583333333335</v>
       </c>
     </row>
     <row r="107" spans="1:15" x14ac:dyDescent="0.3">
@@ -5567,16 +5564,16 @@
         <v>34</v>
       </c>
       <c r="B107">
-        <v>106</v>
+        <v>41</v>
       </c>
       <c r="C107" t="s">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="D107">
         <v>0</v>
       </c>
       <c r="E107">
-        <v>0.36199999999999999</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="F107">
         <v>0</v>
@@ -5585,10 +5582,10 @@
         <v>0</v>
       </c>
       <c r="H107">
-        <v>16.085000000000001</v>
+        <v>37.052999999999997</v>
       </c>
       <c r="I107">
-        <v>609.02</v>
+        <v>924.34500000000003</v>
       </c>
       <c r="J107" t="s">
         <v>17</v>
@@ -5597,7 +5594,7 @@
         <v>0</v>
       </c>
       <c r="L107">
-        <v>1.776</v>
+        <v>2.6960000000000002</v>
       </c>
       <c r="M107">
         <v>0</v>
@@ -5606,7 +5603,7 @@
         <v>46247</v>
       </c>
       <c r="O107" s="3">
-        <v>0.87486111111111109</v>
+        <v>0.85319444444444448</v>
       </c>
     </row>
     <row r="108" spans="1:15" x14ac:dyDescent="0.3">
@@ -5614,16 +5611,16 @@
         <v>34</v>
       </c>
       <c r="B108">
-        <v>110</v>
+        <v>44</v>
       </c>
       <c r="C108" t="s">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="D108">
         <v>0</v>
       </c>
       <c r="E108">
-        <v>0.38900000000000001</v>
+        <v>0.57399999999999995</v>
       </c>
       <c r="F108">
         <v>0</v>
@@ -5632,10 +5629,10 @@
         <v>0</v>
       </c>
       <c r="H108">
-        <v>18.532</v>
+        <v>40.445</v>
       </c>
       <c r="I108">
-        <v>653.70899999999995</v>
+        <v>965.72500000000002</v>
       </c>
       <c r="J108" t="s">
         <v>17</v>
@@ -5644,7 +5641,7 @@
         <v>0</v>
       </c>
       <c r="L108">
-        <v>1.907</v>
+        <v>2.8170000000000002</v>
       </c>
       <c r="M108">
         <v>0</v>
@@ -5653,7 +5650,7 @@
         <v>46247</v>
       </c>
       <c r="O108" s="3">
-        <v>0.87561342592592595</v>
+        <v>0.85381944444444446</v>
       </c>
     </row>
     <row r="109" spans="1:15" x14ac:dyDescent="0.3">
@@ -5661,7 +5658,7 @@
         <v>34</v>
       </c>
       <c r="B109">
-        <v>114</v>
+        <v>47</v>
       </c>
       <c r="C109" t="s">
         <v>19</v>
@@ -5670,7 +5667,7 @@
         <v>0</v>
       </c>
       <c r="E109">
-        <v>0.40799999999999997</v>
+        <v>0.36899999999999999</v>
       </c>
       <c r="F109">
         <v>0</v>
@@ -5679,10 +5676,10 @@
         <v>0</v>
       </c>
       <c r="H109">
-        <v>20.411000000000001</v>
+        <v>16.702999999999999</v>
       </c>
       <c r="I109">
-        <v>686.048</v>
+        <v>620.61599999999999</v>
       </c>
       <c r="J109" t="s">
         <v>17</v>
@@ -5691,7 +5688,7 @@
         <v>0</v>
       </c>
       <c r="L109">
-        <v>2.0009999999999999</v>
+        <v>1.81</v>
       </c>
       <c r="M109">
         <v>0</v>
@@ -5700,7 +5697,7 @@
         <v>46247</v>
       </c>
       <c r="O109" s="3">
-        <v>0.8765856481481481</v>
+        <v>0.85456018518518517</v>
       </c>
     </row>
     <row r="110" spans="1:15" x14ac:dyDescent="0.3">
@@ -5708,16 +5705,16 @@
         <v>34</v>
       </c>
       <c r="B110">
-        <v>118</v>
+        <v>50</v>
       </c>
       <c r="C110" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D110">
         <v>0</v>
       </c>
       <c r="E110">
-        <v>0.39200000000000002</v>
+        <v>0.40300000000000002</v>
       </c>
       <c r="F110">
         <v>0</v>
@@ -5726,10 +5723,10 @@
         <v>0</v>
       </c>
       <c r="H110">
-        <v>18.867999999999999</v>
+        <v>19.957000000000001</v>
       </c>
       <c r="I110">
-        <v>659.61400000000003</v>
+        <v>678.36699999999996</v>
       </c>
       <c r="J110" t="s">
         <v>17</v>
@@ -5738,7 +5735,7 @@
         <v>0</v>
       </c>
       <c r="L110">
-        <v>1.9239999999999999</v>
+        <v>1.9790000000000001</v>
       </c>
       <c r="M110">
         <v>0</v>
@@ -5747,7 +5744,7 @@
         <v>46247</v>
       </c>
       <c r="O110" s="3">
-        <v>0.87753472222222217</v>
+        <v>0.85510416666666667</v>
       </c>
     </row>
     <row r="111" spans="1:15" x14ac:dyDescent="0.3">
@@ -5755,16 +5752,16 @@
         <v>34</v>
       </c>
       <c r="B111">
-        <v>122</v>
+        <v>53</v>
       </c>
       <c r="C111" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D111">
         <v>0</v>
       </c>
       <c r="E111">
-        <v>0.39</v>
+        <v>0.39600000000000002</v>
       </c>
       <c r="F111">
         <v>0</v>
@@ -5773,10 +5770,10 @@
         <v>0</v>
       </c>
       <c r="H111">
-        <v>18.643999999999998</v>
+        <v>19.204000000000001</v>
       </c>
       <c r="I111">
-        <v>655.673</v>
+        <v>665.45299999999997</v>
       </c>
       <c r="J111" t="s">
         <v>17</v>
@@ -5785,7 +5782,7 @@
         <v>0</v>
       </c>
       <c r="L111">
-        <v>1.913</v>
+        <v>1.9410000000000001</v>
       </c>
       <c r="M111">
         <v>0</v>
@@ -5794,24 +5791,24 @@
         <v>46247</v>
       </c>
       <c r="O111" s="3">
-        <v>0.87880787037037034</v>
+        <v>0.8559606481481481</v>
       </c>
     </row>
     <row r="112" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A112" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B112">
-        <v>38</v>
+        <v>56</v>
       </c>
       <c r="C112" t="s">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="D112">
         <v>0</v>
       </c>
       <c r="E112">
-        <v>0.53800000000000003</v>
+        <v>0.41499999999999998</v>
       </c>
       <c r="F112">
         <v>0</v>
@@ -5820,10 +5817,10 @@
         <v>0</v>
       </c>
       <c r="H112">
-        <v>35.433</v>
+        <v>21.103000000000002</v>
       </c>
       <c r="I112">
-        <v>903.91099999999994</v>
+        <v>697.577</v>
       </c>
       <c r="J112" t="s">
         <v>17</v>
@@ -5832,7 +5829,7 @@
         <v>0</v>
       </c>
       <c r="L112">
-        <v>2.637</v>
+        <v>2.0350000000000001</v>
       </c>
       <c r="M112">
         <v>0</v>
@@ -5841,24 +5838,24 @@
         <v>46247</v>
       </c>
       <c r="O112" s="3">
-        <v>0.85239583333333335</v>
+        <v>0.85645833333333332</v>
       </c>
     </row>
     <row r="113" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A113" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B113">
-        <v>41</v>
+        <v>59</v>
       </c>
       <c r="C113" t="s">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="D113">
         <v>0</v>
       </c>
       <c r="E113">
-        <v>0.55000000000000004</v>
+        <v>0.36099999999999999</v>
       </c>
       <c r="F113">
         <v>0</v>
@@ -5867,10 +5864,10 @@
         <v>0</v>
       </c>
       <c r="H113">
-        <v>37.052999999999997</v>
+        <v>15.973000000000001</v>
       </c>
       <c r="I113">
-        <v>924.34500000000003</v>
+        <v>606.89400000000001</v>
       </c>
       <c r="J113" t="s">
         <v>17</v>
@@ -5879,7 +5876,7 @@
         <v>0</v>
       </c>
       <c r="L113">
-        <v>2.6960000000000002</v>
+        <v>1.77</v>
       </c>
       <c r="M113">
         <v>0</v>
@@ -5888,24 +5885,24 @@
         <v>46247</v>
       </c>
       <c r="O113" s="3">
-        <v>0.85319444444444448</v>
+        <v>0.857025462962963</v>
       </c>
     </row>
     <row r="114" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A114" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B114">
-        <v>44</v>
+        <v>62</v>
       </c>
       <c r="C114" t="s">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="D114">
         <v>0</v>
       </c>
       <c r="E114">
-        <v>0.57399999999999995</v>
+        <v>0.42099999999999999</v>
       </c>
       <c r="F114">
         <v>0</v>
@@ -5914,10 +5911,10 @@
         <v>0</v>
       </c>
       <c r="H114">
-        <v>40.445</v>
+        <v>21.773</v>
       </c>
       <c r="I114">
-        <v>965.72500000000002</v>
+        <v>708.56799999999998</v>
       </c>
       <c r="J114" t="s">
         <v>17</v>
@@ -5926,7 +5923,7 @@
         <v>0</v>
       </c>
       <c r="L114">
-        <v>2.8170000000000002</v>
+        <v>2.0670000000000002</v>
       </c>
       <c r="M114">
         <v>0</v>
@@ -5935,7 +5932,7 @@
         <v>46247</v>
       </c>
       <c r="O114" s="3">
-        <v>0.85381944444444446</v>
+        <v>0.85754629629629631</v>
       </c>
     </row>
     <row r="115" spans="1:15" x14ac:dyDescent="0.3">
@@ -5943,16 +5940,16 @@
         <v>35</v>
       </c>
       <c r="B115">
-        <v>47</v>
+        <v>12</v>
       </c>
       <c r="C115" t="s">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="D115">
         <v>0</v>
       </c>
       <c r="E115">
-        <v>0.36899999999999999</v>
+        <v>0.50600000000000001</v>
       </c>
       <c r="F115">
         <v>0</v>
@@ -5961,10 +5958,10 @@
         <v>0</v>
       </c>
       <c r="H115">
-        <v>16.702999999999999</v>
+        <v>31.422000000000001</v>
       </c>
       <c r="I115">
-        <v>620.61599999999999</v>
+        <v>851.21799999999996</v>
       </c>
       <c r="J115" t="s">
         <v>17</v>
@@ -5973,7 +5970,7 @@
         <v>0</v>
       </c>
       <c r="L115">
-        <v>1.81</v>
+        <v>2.4830000000000001</v>
       </c>
       <c r="M115">
         <v>0</v>
@@ -5982,7 +5979,7 @@
         <v>46247</v>
       </c>
       <c r="O115" s="3">
-        <v>0.85456018518518517</v>
+        <v>0.84004629629629635</v>
       </c>
     </row>
     <row r="116" spans="1:15" x14ac:dyDescent="0.3">
@@ -5990,16 +5987,16 @@
         <v>35</v>
       </c>
       <c r="B116">
-        <v>50</v>
+        <v>16</v>
       </c>
       <c r="C116" t="s">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="D116">
         <v>0</v>
       </c>
       <c r="E116">
-        <v>0.40300000000000002</v>
+        <v>0.54200000000000004</v>
       </c>
       <c r="F116">
         <v>0</v>
@@ -6008,10 +6005,10 @@
         <v>0</v>
       </c>
       <c r="H116">
-        <v>19.957000000000001</v>
+        <v>36.011000000000003</v>
       </c>
       <c r="I116">
-        <v>678.36699999999996</v>
+        <v>911.25599999999997</v>
       </c>
       <c r="J116" t="s">
         <v>17</v>
@@ -6020,7 +6017,7 @@
         <v>0</v>
       </c>
       <c r="L116">
-        <v>1.9790000000000001</v>
+        <v>2.6579999999999999</v>
       </c>
       <c r="M116">
         <v>0</v>
@@ -6029,7 +6026,7 @@
         <v>46247</v>
       </c>
       <c r="O116" s="3">
-        <v>0.85510416666666667</v>
+        <v>0.8407175925925926</v>
       </c>
     </row>
     <row r="117" spans="1:15" x14ac:dyDescent="0.3">
@@ -6037,16 +6034,16 @@
         <v>35</v>
       </c>
       <c r="B117">
-        <v>53</v>
+        <v>20</v>
       </c>
       <c r="C117" t="s">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="D117">
         <v>0</v>
       </c>
       <c r="E117">
-        <v>0.39600000000000002</v>
+        <v>0.53800000000000003</v>
       </c>
       <c r="F117">
         <v>0</v>
@@ -6055,10 +6052,10 @@
         <v>0</v>
       </c>
       <c r="H117">
-        <v>19.204000000000001</v>
+        <v>35.47</v>
       </c>
       <c r="I117">
-        <v>665.45299999999997</v>
+        <v>904.38199999999995</v>
       </c>
       <c r="J117" t="s">
         <v>17</v>
@@ -6067,7 +6064,7 @@
         <v>0</v>
       </c>
       <c r="L117">
-        <v>1.9410000000000001</v>
+        <v>2.6379999999999999</v>
       </c>
       <c r="M117">
         <v>0</v>
@@ -6076,7 +6073,7 @@
         <v>46247</v>
       </c>
       <c r="O117" s="3">
-        <v>0.8559606481481481</v>
+        <v>0.84175925925925921</v>
       </c>
     </row>
     <row r="118" spans="1:15" x14ac:dyDescent="0.3">
@@ -6084,28 +6081,28 @@
         <v>35</v>
       </c>
       <c r="B118">
-        <v>56</v>
+        <v>24</v>
       </c>
       <c r="C118" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D118">
         <v>0</v>
       </c>
       <c r="E118">
-        <v>0.41499999999999998</v>
+        <v>0.29699999999999999</v>
       </c>
       <c r="F118">
         <v>0</v>
       </c>
       <c r="G118">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="H118">
-        <v>21.103000000000002</v>
+        <v>10.846</v>
       </c>
       <c r="I118">
-        <v>697.577</v>
+        <v>1000.19</v>
       </c>
       <c r="J118" t="s">
         <v>17</v>
@@ -6114,7 +6111,7 @@
         <v>0</v>
       </c>
       <c r="L118">
-        <v>2.0350000000000001</v>
+        <v>1.4590000000000001</v>
       </c>
       <c r="M118">
         <v>0</v>
@@ -6123,7 +6120,7 @@
         <v>46247</v>
       </c>
       <c r="O118" s="3">
-        <v>0.85645833333333332</v>
+        <v>0.84275462962962966</v>
       </c>
     </row>
     <row r="119" spans="1:15" x14ac:dyDescent="0.3">
@@ -6131,28 +6128,28 @@
         <v>35</v>
       </c>
       <c r="B119">
-        <v>59</v>
+        <v>28</v>
       </c>
       <c r="C119" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D119">
         <v>0</v>
       </c>
       <c r="E119">
-        <v>0.36099999999999999</v>
+        <v>0.32</v>
       </c>
       <c r="F119">
         <v>0</v>
       </c>
       <c r="G119">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="H119">
-        <v>15.973000000000001</v>
+        <v>12.59</v>
       </c>
       <c r="I119">
-        <v>606.89400000000001</v>
+        <v>1077.623</v>
       </c>
       <c r="J119" t="s">
         <v>17</v>
@@ -6161,7 +6158,7 @@
         <v>0</v>
       </c>
       <c r="L119">
-        <v>1.77</v>
+        <v>1.5720000000000001</v>
       </c>
       <c r="M119">
         <v>0</v>
@@ -6170,7 +6167,7 @@
         <v>46247</v>
       </c>
       <c r="O119" s="3">
-        <v>0.857025462962963</v>
+        <v>0.84359953703703705</v>
       </c>
     </row>
     <row r="120" spans="1:15" x14ac:dyDescent="0.3">
@@ -6178,7 +6175,7 @@
         <v>35</v>
       </c>
       <c r="B120">
-        <v>62</v>
+        <v>32</v>
       </c>
       <c r="C120" t="s">
         <v>18</v>
@@ -6187,7 +6184,7 @@
         <v>0</v>
       </c>
       <c r="E120">
-        <v>0.42099999999999999</v>
+        <v>0.32700000000000001</v>
       </c>
       <c r="F120">
         <v>0</v>
@@ -6196,10 +6193,10 @@
         <v>0</v>
       </c>
       <c r="H120">
-        <v>21.773</v>
+        <v>13.129</v>
       </c>
       <c r="I120">
-        <v>708.56799999999998</v>
+        <v>550.21900000000005</v>
       </c>
       <c r="J120" t="s">
         <v>17</v>
@@ -6208,7 +6205,7 @@
         <v>0</v>
       </c>
       <c r="L120">
-        <v>2.0670000000000002</v>
+        <v>1.605</v>
       </c>
       <c r="M120">
         <v>0</v>
@@ -6217,24 +6214,24 @@
         <v>46247</v>
       </c>
       <c r="O120" s="3">
-        <v>0.85754629629629631</v>
+        <v>0.84515046296296292</v>
       </c>
     </row>
     <row r="121" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A121" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B121">
         <v>36</v>
       </c>
-      <c r="B121">
-        <v>12</v>
-      </c>
       <c r="C121" t="s">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="D121">
         <v>0</v>
       </c>
       <c r="E121">
-        <v>0.50600000000000001</v>
+        <v>0.29499999999999998</v>
       </c>
       <c r="F121">
         <v>0</v>
@@ -6243,10 +6240,10 @@
         <v>0</v>
       </c>
       <c r="H121">
-        <v>31.422000000000001</v>
+        <v>10.657999999999999</v>
       </c>
       <c r="I121">
-        <v>851.21799999999996</v>
+        <v>495.75</v>
       </c>
       <c r="J121" t="s">
         <v>17</v>
@@ -6255,7 +6252,7 @@
         <v>0</v>
       </c>
       <c r="L121">
-        <v>2.4830000000000001</v>
+        <v>1.446</v>
       </c>
       <c r="M121">
         <v>0</v>
@@ -6264,7 +6261,7 @@
         <v>46247</v>
       </c>
       <c r="O121" s="3">
-        <v>0.84004629629629635</v>
+        <v>0.84589120370370374</v>
       </c>
     </row>
     <row r="122" spans="1:15" x14ac:dyDescent="0.3">
@@ -6272,7 +6269,7 @@
         <v>36</v>
       </c>
       <c r="B122">
-        <v>16</v>
+        <v>167</v>
       </c>
       <c r="C122" t="s">
         <v>0</v>
@@ -6281,7 +6278,7 @@
         <v>0</v>
       </c>
       <c r="E122">
-        <v>0.54200000000000004</v>
+        <v>0.52900000000000003</v>
       </c>
       <c r="F122">
         <v>0</v>
@@ -6290,10 +6287,10 @@
         <v>0</v>
       </c>
       <c r="H122">
-        <v>36.011000000000003</v>
+        <v>34.374000000000002</v>
       </c>
       <c r="I122">
-        <v>911.25599999999997</v>
+        <v>890.29700000000003</v>
       </c>
       <c r="J122" t="s">
         <v>17</v>
@@ -6302,7 +6299,7 @@
         <v>0</v>
       </c>
       <c r="L122">
-        <v>2.6579999999999999</v>
+        <v>2.597</v>
       </c>
       <c r="M122">
         <v>0</v>
@@ -6311,7 +6308,7 @@
         <v>46247</v>
       </c>
       <c r="O122" s="3">
-        <v>0.8407175925925926</v>
+        <v>0.86697916666666663</v>
       </c>
     </row>
     <row r="123" spans="1:15" x14ac:dyDescent="0.3">
@@ -6319,7 +6316,7 @@
         <v>36</v>
       </c>
       <c r="B123">
-        <v>20</v>
+        <v>171</v>
       </c>
       <c r="C123" t="s">
         <v>0</v>
@@ -6328,7 +6325,7 @@
         <v>0</v>
       </c>
       <c r="E123">
-        <v>0.53800000000000003</v>
+        <v>0.498</v>
       </c>
       <c r="F123">
         <v>0</v>
@@ -6337,10 +6334,10 @@
         <v>0</v>
       </c>
       <c r="H123">
-        <v>35.47</v>
+        <v>30.434000000000001</v>
       </c>
       <c r="I123">
-        <v>904.38199999999995</v>
+        <v>837.72500000000002</v>
       </c>
       <c r="J123" t="s">
         <v>17</v>
@@ -6349,7 +6346,7 @@
         <v>0</v>
       </c>
       <c r="L123">
-        <v>2.6379999999999999</v>
+        <v>2.444</v>
       </c>
       <c r="M123">
         <v>0</v>
@@ -6358,7 +6355,7 @@
         <v>46247</v>
       </c>
       <c r="O123" s="3">
-        <v>0.84175925925925921</v>
+        <v>0.8686342592592593</v>
       </c>
     </row>
     <row r="124" spans="1:15" x14ac:dyDescent="0.3">
@@ -6366,7 +6363,7 @@
         <v>36</v>
       </c>
       <c r="B124">
-        <v>24</v>
+        <v>175</v>
       </c>
       <c r="C124" t="s">
         <v>19</v>
@@ -6375,19 +6372,19 @@
         <v>0</v>
       </c>
       <c r="E124">
-        <v>0.29699999999999999</v>
+        <v>0.38400000000000001</v>
       </c>
       <c r="F124">
         <v>0</v>
       </c>
       <c r="G124">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="H124">
-        <v>10.846</v>
+        <v>18.074999999999999</v>
       </c>
       <c r="I124">
-        <v>1000.19</v>
+        <v>645.59699999999998</v>
       </c>
       <c r="J124" t="s">
         <v>17</v>
@@ -6396,7 +6393,7 @@
         <v>0</v>
       </c>
       <c r="L124">
-        <v>1.4590000000000001</v>
+        <v>1.883</v>
       </c>
       <c r="M124">
         <v>0</v>
@@ -6405,7 +6402,7 @@
         <v>46247</v>
       </c>
       <c r="O124" s="3">
-        <v>0.84275462962962966</v>
+        <v>0.86980324074074078</v>
       </c>
     </row>
     <row r="125" spans="1:15" x14ac:dyDescent="0.3">
@@ -6413,7 +6410,7 @@
         <v>36</v>
       </c>
       <c r="B125">
-        <v>28</v>
+        <v>179</v>
       </c>
       <c r="C125" t="s">
         <v>19</v>
@@ -6422,19 +6419,19 @@
         <v>0</v>
       </c>
       <c r="E125">
-        <v>0.32</v>
+        <v>0.4</v>
       </c>
       <c r="F125">
         <v>0</v>
       </c>
       <c r="G125">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="H125">
-        <v>12.59</v>
+        <v>19.579999999999998</v>
       </c>
       <c r="I125">
-        <v>1077.623</v>
+        <v>671.93700000000001</v>
       </c>
       <c r="J125" t="s">
         <v>17</v>
@@ -6443,7 +6440,7 @@
         <v>0</v>
       </c>
       <c r="L125">
-        <v>1.5720000000000001</v>
+        <v>1.96</v>
       </c>
       <c r="M125">
         <v>0</v>
@@ -6452,7 +6449,7 @@
         <v>46247</v>
       </c>
       <c r="O125" s="3">
-        <v>0.84359953703703705</v>
+        <v>0.87047453703703703</v>
       </c>
     </row>
     <row r="126" spans="1:15" x14ac:dyDescent="0.3">
@@ -6460,7 +6457,7 @@
         <v>36</v>
       </c>
       <c r="B126">
-        <v>32</v>
+        <v>183</v>
       </c>
       <c r="C126" t="s">
         <v>18</v>
@@ -6469,7 +6466,7 @@
         <v>0</v>
       </c>
       <c r="E126">
-        <v>0.32700000000000001</v>
+        <v>0.34699999999999998</v>
       </c>
       <c r="F126">
         <v>0</v>
@@ -6478,10 +6475,10 @@
         <v>0</v>
       </c>
       <c r="H126">
-        <v>13.129</v>
+        <v>14.743</v>
       </c>
       <c r="I126">
-        <v>550.21900000000005</v>
+        <v>583.05600000000004</v>
       </c>
       <c r="J126" t="s">
         <v>17</v>
@@ -6490,7 +6487,7 @@
         <v>0</v>
       </c>
       <c r="L126">
-        <v>1.605</v>
+        <v>1.7010000000000001</v>
       </c>
       <c r="M126">
         <v>0</v>
@@ -6499,7 +6496,7 @@
         <v>46247</v>
       </c>
       <c r="O126" s="3">
-        <v>0.84515046296296292</v>
+        <v>0.87138888888888888</v>
       </c>
     </row>
     <row r="127" spans="1:15" x14ac:dyDescent="0.3">
@@ -6507,7 +6504,7 @@
         <v>36</v>
       </c>
       <c r="B127">
-        <v>36</v>
+        <v>187</v>
       </c>
       <c r="C127" t="s">
         <v>18</v>
@@ -6516,7 +6513,7 @@
         <v>0</v>
       </c>
       <c r="E127">
-        <v>0.29499999999999998</v>
+        <v>0.38200000000000001</v>
       </c>
       <c r="F127">
         <v>0</v>
@@ -6525,10 +6522,10 @@
         <v>0</v>
       </c>
       <c r="H127">
-        <v>10.657999999999999</v>
+        <v>17.911000000000001</v>
       </c>
       <c r="I127">
-        <v>495.75</v>
+        <v>642.66399999999999</v>
       </c>
       <c r="J127" t="s">
         <v>17</v>
@@ -6537,7 +6534,7 @@
         <v>0</v>
       </c>
       <c r="L127">
-        <v>1.446</v>
+        <v>1.875</v>
       </c>
       <c r="M127">
         <v>0</v>
@@ -6546,7 +6543,7 @@
         <v>46247</v>
       </c>
       <c r="O127" s="3">
-        <v>0.84589120370370374</v>
+        <v>0.8719675925925926</v>
       </c>
     </row>
     <row r="128" spans="1:15" x14ac:dyDescent="0.3">
@@ -6554,7 +6551,7 @@
         <v>37</v>
       </c>
       <c r="B128">
-        <v>167</v>
+        <v>39</v>
       </c>
       <c r="C128" t="s">
         <v>0</v>
@@ -6563,7 +6560,7 @@
         <v>0</v>
       </c>
       <c r="E128">
-        <v>0.52900000000000003</v>
+        <v>0.52</v>
       </c>
       <c r="F128">
         <v>0</v>
@@ -6572,10 +6569,10 @@
         <v>0</v>
       </c>
       <c r="H128">
-        <v>34.374000000000002</v>
+        <v>33.149000000000001</v>
       </c>
       <c r="I128">
-        <v>890.29700000000003</v>
+        <v>874.28899999999999</v>
       </c>
       <c r="J128" t="s">
         <v>17</v>
@@ -6584,7 +6581,7 @@
         <v>0</v>
       </c>
       <c r="L128">
-        <v>2.597</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="M128">
         <v>0</v>
@@ -6593,7 +6590,7 @@
         <v>46247</v>
       </c>
       <c r="O128" s="3">
-        <v>0.86697916666666663</v>
+        <v>0.85276620370370371</v>
       </c>
     </row>
     <row r="129" spans="1:15" x14ac:dyDescent="0.3">
@@ -6601,7 +6598,7 @@
         <v>37</v>
       </c>
       <c r="B129">
-        <v>171</v>
+        <v>42</v>
       </c>
       <c r="C129" t="s">
         <v>0</v>
@@ -6610,7 +6607,7 @@
         <v>0</v>
       </c>
       <c r="E129">
-        <v>0.498</v>
+        <v>0.60099999999999998</v>
       </c>
       <c r="F129">
         <v>0</v>
@@ -6619,10 +6616,10 @@
         <v>0</v>
       </c>
       <c r="H129">
-        <v>30.434000000000001</v>
+        <v>44.335000000000001</v>
       </c>
       <c r="I129">
-        <v>837.72500000000002</v>
+        <v>1011.1</v>
       </c>
       <c r="J129" t="s">
         <v>17</v>
@@ -6631,7 +6628,7 @@
         <v>0</v>
       </c>
       <c r="L129">
-        <v>2.444</v>
+        <v>2.9489999999999998</v>
       </c>
       <c r="M129">
         <v>0</v>
@@ -6640,7 +6637,7 @@
         <v>46247</v>
       </c>
       <c r="O129" s="3">
-        <v>0.8686342592592593</v>
+        <v>0.85340277777777773</v>
       </c>
     </row>
     <row r="130" spans="1:15" x14ac:dyDescent="0.3">
@@ -6648,16 +6645,16 @@
         <v>37</v>
       </c>
       <c r="B130">
-        <v>175</v>
+        <v>45</v>
       </c>
       <c r="C130" t="s">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="D130">
         <v>0</v>
       </c>
       <c r="E130">
-        <v>0.38400000000000001</v>
+        <v>0.54200000000000004</v>
       </c>
       <c r="F130">
         <v>0</v>
@@ -6666,10 +6663,10 @@
         <v>0</v>
       </c>
       <c r="H130">
-        <v>18.074999999999999</v>
+        <v>36.021999999999998</v>
       </c>
       <c r="I130">
-        <v>645.59699999999998</v>
+        <v>911.39099999999996</v>
       </c>
       <c r="J130" t="s">
         <v>17</v>
@@ -6678,7 +6675,7 @@
         <v>0</v>
       </c>
       <c r="L130">
-        <v>1.883</v>
+        <v>2.6579999999999999</v>
       </c>
       <c r="M130">
         <v>0</v>
@@ -6687,7 +6684,7 @@
         <v>46247</v>
       </c>
       <c r="O130" s="3">
-        <v>0.86980324074074078</v>
+        <v>0.85398148148148145</v>
       </c>
     </row>
     <row r="131" spans="1:15" x14ac:dyDescent="0.3">
@@ -6695,7 +6692,7 @@
         <v>37</v>
       </c>
       <c r="B131">
-        <v>179</v>
+        <v>48</v>
       </c>
       <c r="C131" t="s">
         <v>19</v>
@@ -6704,7 +6701,7 @@
         <v>0</v>
       </c>
       <c r="E131">
-        <v>0.4</v>
+        <v>0.36299999999999999</v>
       </c>
       <c r="F131">
         <v>0</v>
@@ -6713,10 +6710,10 @@
         <v>0</v>
       </c>
       <c r="H131">
-        <v>19.579999999999998</v>
+        <v>16.141999999999999</v>
       </c>
       <c r="I131">
-        <v>671.93700000000001</v>
+        <v>610.096</v>
       </c>
       <c r="J131" t="s">
         <v>17</v>
@@ -6725,7 +6722,7 @@
         <v>0</v>
       </c>
       <c r="L131">
-        <v>1.96</v>
+        <v>1.78</v>
       </c>
       <c r="M131">
         <v>0</v>
@@ -6734,7 +6731,7 @@
         <v>46247</v>
       </c>
       <c r="O131" s="3">
-        <v>0.87047453703703703</v>
+        <v>0.85473379629629631</v>
       </c>
     </row>
     <row r="132" spans="1:15" x14ac:dyDescent="0.3">
@@ -6742,16 +6739,16 @@
         <v>37</v>
       </c>
       <c r="B132">
-        <v>183</v>
+        <v>51</v>
       </c>
       <c r="C132" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D132">
         <v>0</v>
       </c>
       <c r="E132">
-        <v>0.34699999999999998</v>
+        <v>0.373</v>
       </c>
       <c r="F132">
         <v>0</v>
@@ -6760,10 +6757,10 @@
         <v>0</v>
       </c>
       <c r="H132">
-        <v>14.743</v>
+        <v>17.035</v>
       </c>
       <c r="I132">
-        <v>583.05600000000004</v>
+        <v>626.75</v>
       </c>
       <c r="J132" t="s">
         <v>17</v>
@@ -6772,7 +6769,7 @@
         <v>0</v>
       </c>
       <c r="L132">
-        <v>1.7010000000000001</v>
+        <v>1.8280000000000001</v>
       </c>
       <c r="M132">
         <v>0</v>
@@ -6781,7 +6778,7 @@
         <v>46247</v>
       </c>
       <c r="O132" s="3">
-        <v>0.87138888888888888</v>
+        <v>0.85523148148148154</v>
       </c>
     </row>
     <row r="133" spans="1:15" x14ac:dyDescent="0.3">
@@ -6789,16 +6786,16 @@
         <v>37</v>
       </c>
       <c r="B133">
-        <v>187</v>
+        <v>54</v>
       </c>
       <c r="C133" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D133">
         <v>0</v>
       </c>
       <c r="E133">
-        <v>0.38200000000000001</v>
+        <v>0.39400000000000002</v>
       </c>
       <c r="F133">
         <v>0</v>
@@ -6807,10 +6804,10 @@
         <v>0</v>
       </c>
       <c r="H133">
-        <v>17.911000000000001</v>
+        <v>19.045000000000002</v>
       </c>
       <c r="I133">
-        <v>642.66399999999999</v>
+        <v>662.69500000000005</v>
       </c>
       <c r="J133" t="s">
         <v>17</v>
@@ -6819,7 +6816,7 @@
         <v>0</v>
       </c>
       <c r="L133">
-        <v>1.875</v>
+        <v>1.9330000000000001</v>
       </c>
       <c r="M133">
         <v>0</v>
@@ -6828,24 +6825,24 @@
         <v>46247</v>
       </c>
       <c r="O133" s="3">
-        <v>0.8719675925925926</v>
+        <v>0.85609953703703701</v>
       </c>
     </row>
     <row r="134" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A134" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B134">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="C134" t="s">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="D134">
         <v>0</v>
       </c>
       <c r="E134">
-        <v>0.52</v>
+        <v>0.36399999999999999</v>
       </c>
       <c r="F134">
         <v>0</v>
@@ -6854,10 +6851,10 @@
         <v>0</v>
       </c>
       <c r="H134">
-        <v>33.149000000000001</v>
+        <v>16.254000000000001</v>
       </c>
       <c r="I134">
-        <v>874.28899999999999</v>
+        <v>612.221</v>
       </c>
       <c r="J134" t="s">
         <v>17</v>
@@ -6866,7 +6863,7 @@
         <v>0</v>
       </c>
       <c r="L134">
-        <v>2.5499999999999998</v>
+        <v>1.786</v>
       </c>
       <c r="M134">
         <v>0</v>
@@ -6875,24 +6872,24 @@
         <v>46247</v>
       </c>
       <c r="O134" s="3">
-        <v>0.85276620370370371</v>
+        <v>0.8566435185185185</v>
       </c>
     </row>
     <row r="135" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A135" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B135">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="C135" t="s">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="D135">
         <v>0</v>
       </c>
       <c r="E135">
-        <v>0.60099999999999998</v>
+        <v>0.38300000000000001</v>
       </c>
       <c r="F135">
         <v>0</v>
@@ -6901,10 +6898,10 @@
         <v>0</v>
       </c>
       <c r="H135">
-        <v>44.335000000000001</v>
+        <v>17.972999999999999</v>
       </c>
       <c r="I135">
-        <v>1011.1</v>
+        <v>643.76700000000005</v>
       </c>
       <c r="J135" t="s">
         <v>17</v>
@@ -6913,7 +6910,7 @@
         <v>0</v>
       </c>
       <c r="L135">
-        <v>2.9489999999999998</v>
+        <v>1.8779999999999999</v>
       </c>
       <c r="M135">
         <v>0</v>
@@ -6922,24 +6919,24 @@
         <v>46247</v>
       </c>
       <c r="O135" s="3">
-        <v>0.85340277777777773</v>
+        <v>0.85726851851851849</v>
       </c>
     </row>
     <row r="136" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A136" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B136">
-        <v>45</v>
+        <v>63</v>
       </c>
       <c r="C136" t="s">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="D136">
         <v>0</v>
       </c>
       <c r="E136">
-        <v>0.54200000000000004</v>
+        <v>0.38800000000000001</v>
       </c>
       <c r="F136">
         <v>0</v>
@@ -6948,10 +6945,10 @@
         <v>0</v>
       </c>
       <c r="H136">
-        <v>36.021999999999998</v>
+        <v>18.463000000000001</v>
       </c>
       <c r="I136">
-        <v>911.39099999999996</v>
+        <v>652.48500000000001</v>
       </c>
       <c r="J136" t="s">
         <v>17</v>
@@ -6960,7 +6957,7 @@
         <v>0</v>
       </c>
       <c r="L136">
-        <v>2.6579999999999999</v>
+        <v>1.903</v>
       </c>
       <c r="M136">
         <v>0</v>
@@ -6969,24 +6966,24 @@
         <v>46247</v>
       </c>
       <c r="O136" s="3">
-        <v>0.85398148148148145</v>
-      </c>
-    </row>
-    <row r="137" spans="1:15" x14ac:dyDescent="0.3">
+        <v>0.85765046296296299</v>
+      </c>
+    </row>
+    <row r="137" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A137" s="1" t="s">
         <v>38</v>
       </c>
       <c r="B137">
-        <v>48</v>
+        <v>191</v>
       </c>
       <c r="C137" t="s">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="D137">
         <v>0</v>
       </c>
       <c r="E137">
-        <v>0.36299999999999999</v>
+        <v>0.53900000000000003</v>
       </c>
       <c r="F137">
         <v>0</v>
@@ -6995,10 +6992,10 @@
         <v>0</v>
       </c>
       <c r="H137">
-        <v>16.141999999999999</v>
+        <v>35.590000000000003</v>
       </c>
       <c r="I137">
-        <v>610.096</v>
+        <v>905.91499999999996</v>
       </c>
       <c r="J137" t="s">
         <v>17</v>
@@ -7007,7 +7004,7 @@
         <v>0</v>
       </c>
       <c r="L137">
-        <v>1.78</v>
+        <v>2.6429999999999998</v>
       </c>
       <c r="M137">
         <v>0</v>
@@ -7016,24 +7013,24 @@
         <v>46247</v>
       </c>
       <c r="O137" s="3">
-        <v>0.85473379629629631</v>
-      </c>
-    </row>
-    <row r="138" spans="1:15" x14ac:dyDescent="0.3">
+        <v>0.87616898148148148</v>
+      </c>
+    </row>
+    <row r="138" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A138" s="1" t="s">
         <v>38</v>
       </c>
       <c r="B138">
-        <v>51</v>
+        <v>194</v>
       </c>
       <c r="C138" t="s">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="D138">
         <v>0</v>
       </c>
       <c r="E138">
-        <v>0.373</v>
+        <v>0.52100000000000002</v>
       </c>
       <c r="F138">
         <v>0</v>
@@ -7042,10 +7039,10 @@
         <v>0</v>
       </c>
       <c r="H138">
-        <v>17.035</v>
+        <v>33.250999999999998</v>
       </c>
       <c r="I138">
-        <v>626.75</v>
+        <v>875.63400000000001</v>
       </c>
       <c r="J138" t="s">
         <v>17</v>
@@ -7054,7 +7051,7 @@
         <v>0</v>
       </c>
       <c r="L138">
-        <v>1.8280000000000001</v>
+        <v>2.5539999999999998</v>
       </c>
       <c r="M138">
         <v>0</v>
@@ -7063,15 +7060,15 @@
         <v>46247</v>
       </c>
       <c r="O138" s="3">
-        <v>0.85523148148148154</v>
-      </c>
-    </row>
-    <row r="139" spans="1:15" x14ac:dyDescent="0.3">
+        <v>0.87703703703703706</v>
+      </c>
+    </row>
+    <row r="139" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A139" s="1" t="s">
         <v>38</v>
       </c>
       <c r="B139">
-        <v>54</v>
+        <v>197</v>
       </c>
       <c r="C139" t="s">
         <v>19</v>
@@ -7080,7 +7077,7 @@
         <v>0</v>
       </c>
       <c r="E139">
-        <v>0.39400000000000002</v>
+        <v>0.36</v>
       </c>
       <c r="F139">
         <v>0</v>
@@ -7089,10 +7086,10 @@
         <v>0</v>
       </c>
       <c r="H139">
-        <v>19.045000000000002</v>
+        <v>15.933</v>
       </c>
       <c r="I139">
-        <v>662.69500000000005</v>
+        <v>606.14099999999996</v>
       </c>
       <c r="J139" t="s">
         <v>17</v>
@@ -7101,7 +7098,7 @@
         <v>0</v>
       </c>
       <c r="L139">
-        <v>1.9330000000000001</v>
+        <v>1.768</v>
       </c>
       <c r="M139">
         <v>0</v>
@@ -7110,24 +7107,24 @@
         <v>46247</v>
       </c>
       <c r="O139" s="3">
-        <v>0.85609953703703701</v>
-      </c>
-    </row>
-    <row r="140" spans="1:15" x14ac:dyDescent="0.3">
+        <v>0.8783333333333333</v>
+      </c>
+    </row>
+    <row r="140" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A140" s="1" t="s">
         <v>38</v>
       </c>
       <c r="B140">
-        <v>57</v>
+        <v>200</v>
       </c>
       <c r="C140" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D140">
         <v>0</v>
       </c>
       <c r="E140">
-        <v>0.36399999999999999</v>
+        <v>0.38100000000000001</v>
       </c>
       <c r="F140">
         <v>0</v>
@@ -7136,10 +7133,10 @@
         <v>0</v>
       </c>
       <c r="H140">
-        <v>16.254000000000001</v>
+        <v>17.789000000000001</v>
       </c>
       <c r="I140">
-        <v>612.221</v>
+        <v>640.47199999999998</v>
       </c>
       <c r="J140" t="s">
         <v>17</v>
@@ -7148,7 +7145,7 @@
         <v>0</v>
       </c>
       <c r="L140">
-        <v>1.786</v>
+        <v>1.8680000000000001</v>
       </c>
       <c r="M140">
         <v>0</v>
@@ -7157,15 +7154,15 @@
         <v>46247</v>
       </c>
       <c r="O140" s="3">
-        <v>0.8566435185185185</v>
-      </c>
-    </row>
-    <row r="141" spans="1:15" x14ac:dyDescent="0.3">
+        <v>0.88009259259259254</v>
+      </c>
+    </row>
+    <row r="141" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A141" s="1" t="s">
         <v>38</v>
       </c>
       <c r="B141">
-        <v>60</v>
+        <v>204</v>
       </c>
       <c r="C141" t="s">
         <v>18</v>
@@ -7174,7 +7171,7 @@
         <v>0</v>
       </c>
       <c r="E141">
-        <v>0.38300000000000001</v>
+        <v>0.372</v>
       </c>
       <c r="F141">
         <v>0</v>
@@ -7183,10 +7180,10 @@
         <v>0</v>
       </c>
       <c r="H141">
-        <v>17.972999999999999</v>
+        <v>17.004999999999999</v>
       </c>
       <c r="I141">
-        <v>643.76700000000005</v>
+        <v>626.19799999999998</v>
       </c>
       <c r="J141" t="s">
         <v>17</v>
@@ -7195,7 +7192,7 @@
         <v>0</v>
       </c>
       <c r="L141">
-        <v>1.8779999999999999</v>
+        <v>1.827</v>
       </c>
       <c r="M141">
         <v>0</v>
@@ -7204,15 +7201,15 @@
         <v>46247</v>
       </c>
       <c r="O141" s="3">
-        <v>0.85726851851851849</v>
-      </c>
-    </row>
-    <row r="142" spans="1:15" x14ac:dyDescent="0.3">
+        <v>0.8810069444444445</v>
+      </c>
+    </row>
+    <row r="142" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A142" s="1" t="s">
         <v>38</v>
       </c>
       <c r="B142">
-        <v>63</v>
+        <v>207</v>
       </c>
       <c r="C142" t="s">
         <v>18</v>
@@ -7221,7 +7218,7 @@
         <v>0</v>
       </c>
       <c r="E142">
-        <v>0.38800000000000001</v>
+        <v>0.35</v>
       </c>
       <c r="F142">
         <v>0</v>
@@ -7230,10 +7227,10 @@
         <v>0</v>
       </c>
       <c r="H142">
-        <v>18.463000000000001</v>
+        <v>15.004</v>
       </c>
       <c r="I142">
-        <v>652.48500000000001</v>
+        <v>588.20899999999995</v>
       </c>
       <c r="J142" t="s">
         <v>17</v>
@@ -7242,7 +7239,7 @@
         <v>0</v>
       </c>
       <c r="L142">
-        <v>1.903</v>
+        <v>1.716</v>
       </c>
       <c r="M142">
         <v>0</v>
@@ -7251,7 +7248,7 @@
         <v>46247</v>
       </c>
       <c r="O142" s="3">
-        <v>0.85765046296296299</v>
+        <v>0.88170138888888894</v>
       </c>
     </row>
     <row r="143" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
@@ -7259,7 +7256,7 @@
         <v>39</v>
       </c>
       <c r="B143">
-        <v>191</v>
+        <v>11</v>
       </c>
       <c r="C143" t="s">
         <v>0</v>
@@ -7268,7 +7265,7 @@
         <v>0</v>
       </c>
       <c r="E143">
-        <v>0.53900000000000003</v>
+        <v>0.53700000000000003</v>
       </c>
       <c r="F143">
         <v>0</v>
@@ -7277,10 +7274,10 @@
         <v>0</v>
       </c>
       <c r="H143">
-        <v>35.590000000000003</v>
+        <v>35.404000000000003</v>
       </c>
       <c r="I143">
-        <v>905.91499999999996</v>
+        <v>903.548</v>
       </c>
       <c r="J143" t="s">
         <v>17</v>
@@ -7289,7 +7286,7 @@
         <v>0</v>
       </c>
       <c r="L143">
-        <v>2.6429999999999998</v>
+        <v>2.6360000000000001</v>
       </c>
       <c r="M143">
         <v>0</v>
@@ -7298,7 +7295,7 @@
         <v>46247</v>
       </c>
       <c r="O143" s="3">
-        <v>0.87616898148148148</v>
+        <v>0.83969907407407407</v>
       </c>
     </row>
     <row r="144" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
@@ -7306,7 +7303,7 @@
         <v>39</v>
       </c>
       <c r="B144">
-        <v>194</v>
+        <v>15</v>
       </c>
       <c r="C144" t="s">
         <v>0</v>
@@ -7315,7 +7312,7 @@
         <v>0</v>
       </c>
       <c r="E144">
-        <v>0.52100000000000002</v>
+        <v>0.54</v>
       </c>
       <c r="F144">
         <v>0</v>
@@ -7324,10 +7321,10 @@
         <v>0</v>
       </c>
       <c r="H144">
-        <v>33.250999999999998</v>
+        <v>35.731999999999999</v>
       </c>
       <c r="I144">
-        <v>875.63400000000001</v>
+        <v>907.71799999999996</v>
       </c>
       <c r="J144" t="s">
         <v>17</v>
@@ -7336,7 +7333,7 @@
         <v>0</v>
       </c>
       <c r="L144">
-        <v>2.5539999999999998</v>
+        <v>2.6480000000000001</v>
       </c>
       <c r="M144">
         <v>0</v>
@@ -7345,7 +7342,7 @@
         <v>46247</v>
       </c>
       <c r="O144" s="3">
-        <v>0.87703703703703706</v>
+        <v>0.8405555555555555</v>
       </c>
     </row>
     <row r="145" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
@@ -7353,16 +7350,16 @@
         <v>39</v>
       </c>
       <c r="B145">
-        <v>197</v>
+        <v>19</v>
       </c>
       <c r="C145" t="s">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="D145">
         <v>0</v>
       </c>
       <c r="E145">
-        <v>0.36</v>
+        <v>0.53400000000000003</v>
       </c>
       <c r="F145">
         <v>0</v>
@@ -7371,10 +7368,10 @@
         <v>0</v>
       </c>
       <c r="H145">
-        <v>15.933</v>
+        <v>35.000999999999998</v>
       </c>
       <c r="I145">
-        <v>606.14099999999996</v>
+        <v>898.38199999999995</v>
       </c>
       <c r="J145" t="s">
         <v>17</v>
@@ -7383,7 +7380,7 @@
         <v>0</v>
       </c>
       <c r="L145">
-        <v>1.768</v>
+        <v>2.621</v>
       </c>
       <c r="M145">
         <v>0</v>
@@ -7392,7 +7389,7 @@
         <v>46247</v>
       </c>
       <c r="O145" s="3">
-        <v>0.8783333333333333</v>
+        <v>0.84163194444444445</v>
       </c>
     </row>
     <row r="146" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
@@ -7400,7 +7397,7 @@
         <v>39</v>
       </c>
       <c r="B146">
-        <v>200</v>
+        <v>23</v>
       </c>
       <c r="C146" t="s">
         <v>19</v>
@@ -7409,19 +7406,19 @@
         <v>0</v>
       </c>
       <c r="E146">
-        <v>0.38100000000000001</v>
+        <v>0.37</v>
       </c>
       <c r="F146">
         <v>0</v>
       </c>
       <c r="G146">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="H146">
-        <v>17.789000000000001</v>
+        <v>16.821999999999999</v>
       </c>
       <c r="I146">
-        <v>640.47199999999998</v>
+        <v>1245.644</v>
       </c>
       <c r="J146" t="s">
         <v>17</v>
@@ -7430,7 +7427,7 @@
         <v>0</v>
       </c>
       <c r="L146">
-        <v>1.8680000000000001</v>
+        <v>1.8169999999999999</v>
       </c>
       <c r="M146">
         <v>0</v>
@@ -7439,7 +7436,7 @@
         <v>46247</v>
       </c>
       <c r="O146" s="3">
-        <v>0.88009259259259254</v>
+        <v>0.84261574074074075</v>
       </c>
     </row>
     <row r="147" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
@@ -7447,28 +7444,28 @@
         <v>39</v>
       </c>
       <c r="B147">
-        <v>204</v>
+        <v>27</v>
       </c>
       <c r="C147" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D147">
         <v>0</v>
       </c>
       <c r="E147">
-        <v>0.372</v>
+        <v>0.38400000000000001</v>
       </c>
       <c r="F147">
         <v>0</v>
       </c>
       <c r="G147">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="H147">
-        <v>17.004999999999999</v>
+        <v>18.084</v>
       </c>
       <c r="I147">
-        <v>626.19799999999998</v>
+        <v>1291.5170000000001</v>
       </c>
       <c r="J147" t="s">
         <v>17</v>
@@ -7477,7 +7474,7 @@
         <v>0</v>
       </c>
       <c r="L147">
-        <v>1.827</v>
+        <v>1.8839999999999999</v>
       </c>
       <c r="M147">
         <v>0</v>
@@ -7486,7 +7483,7 @@
         <v>46247</v>
       </c>
       <c r="O147" s="3">
-        <v>0.8810069444444445</v>
+        <v>0.84341435185185187</v>
       </c>
     </row>
     <row r="148" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
@@ -7494,7 +7491,7 @@
         <v>39</v>
       </c>
       <c r="B148">
-        <v>207</v>
+        <v>31</v>
       </c>
       <c r="C148" t="s">
         <v>18</v>
@@ -7503,7 +7500,7 @@
         <v>0</v>
       </c>
       <c r="E148">
-        <v>0.35</v>
+        <v>0.32600000000000001</v>
       </c>
       <c r="F148">
         <v>0</v>
@@ -7512,10 +7509,10 @@
         <v>0</v>
       </c>
       <c r="H148">
-        <v>15.004</v>
+        <v>13.013999999999999</v>
       </c>
       <c r="I148">
-        <v>588.20899999999995</v>
+        <v>547.81100000000004</v>
       </c>
       <c r="J148" t="s">
         <v>17</v>
@@ -7524,7 +7521,7 @@
         <v>0</v>
       </c>
       <c r="L148">
-        <v>1.716</v>
+        <v>1.5980000000000001</v>
       </c>
       <c r="M148">
         <v>0</v>
@@ -7533,62 +7530,62 @@
         <v>46247</v>
       </c>
       <c r="O148" s="3">
-        <v>0.88170138888888894</v>
+        <v>0.8449768518518519</v>
       </c>
     </row>
     <row r="149" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A149" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B149">
+        <v>35</v>
+      </c>
+      <c r="C149" t="s">
+        <v>18</v>
+      </c>
+      <c r="D149">
+        <v>0</v>
+      </c>
+      <c r="E149">
+        <v>0.34300000000000003</v>
+      </c>
+      <c r="F149">
+        <v>0</v>
+      </c>
+      <c r="G149">
+        <v>0</v>
+      </c>
+      <c r="H149">
+        <v>14.407</v>
+      </c>
+      <c r="I149">
+        <v>576.37099999999998</v>
+      </c>
+      <c r="J149" t="s">
+        <v>17</v>
+      </c>
+      <c r="K149">
+        <v>0</v>
+      </c>
+      <c r="L149">
+        <v>1.681</v>
+      </c>
+      <c r="M149">
+        <v>0</v>
+      </c>
+      <c r="N149" s="2">
+        <v>46247</v>
+      </c>
+      <c r="O149" s="3">
+        <v>0.84572916666666664</v>
+      </c>
+    </row>
+    <row r="150" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A150" t="s">
         <v>40</v>
       </c>
-      <c r="B149">
-        <v>11</v>
-      </c>
-      <c r="C149" t="s">
-        <v>0</v>
-      </c>
-      <c r="D149">
-        <v>0</v>
-      </c>
-      <c r="E149">
-        <v>0.53700000000000003</v>
-      </c>
-      <c r="F149">
-        <v>0</v>
-      </c>
-      <c r="G149">
-        <v>0</v>
-      </c>
-      <c r="H149">
-        <v>35.404000000000003</v>
-      </c>
-      <c r="I149">
-        <v>903.548</v>
-      </c>
-      <c r="J149" t="s">
-        <v>17</v>
-      </c>
-      <c r="K149">
-        <v>0</v>
-      </c>
-      <c r="L149">
-        <v>2.6360000000000001</v>
-      </c>
-      <c r="M149">
-        <v>0</v>
-      </c>
-      <c r="N149" s="2">
-        <v>46247</v>
-      </c>
-      <c r="O149" s="3">
-        <v>0.83969907407407407</v>
-      </c>
-    </row>
-    <row r="150" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A150" s="1" t="s">
-        <v>40</v>
-      </c>
       <c r="B150">
-        <v>15</v>
+        <v>168</v>
       </c>
       <c r="C150" t="s">
         <v>0</v>
@@ -7597,7 +7594,7 @@
         <v>0</v>
       </c>
       <c r="E150">
-        <v>0.54</v>
+        <v>0.56000000000000005</v>
       </c>
       <c r="F150">
         <v>0</v>
@@ -7606,10 +7603,10 @@
         <v>0</v>
       </c>
       <c r="H150">
-        <v>35.731999999999999</v>
+        <v>38.405000000000001</v>
       </c>
       <c r="I150">
-        <v>907.71799999999996</v>
+        <v>941.053</v>
       </c>
       <c r="J150" t="s">
         <v>17</v>
@@ -7618,7 +7615,7 @@
         <v>0</v>
       </c>
       <c r="L150">
-        <v>2.6480000000000001</v>
+        <v>2.7450000000000001</v>
       </c>
       <c r="M150">
         <v>0</v>
@@ -7627,15 +7624,15 @@
         <v>46247</v>
       </c>
       <c r="O150" s="3">
-        <v>0.8405555555555555</v>
-      </c>
-    </row>
-    <row r="151" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+        <v>0.86763888888888885</v>
+      </c>
+    </row>
+    <row r="151" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A151" s="1" t="s">
         <v>40</v>
       </c>
       <c r="B151">
-        <v>19</v>
+        <v>172</v>
       </c>
       <c r="C151" t="s">
         <v>0</v>
@@ -7644,7 +7641,7 @@
         <v>0</v>
       </c>
       <c r="E151">
-        <v>0.53400000000000003</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="F151">
         <v>0</v>
@@ -7653,10 +7650,10 @@
         <v>0</v>
       </c>
       <c r="H151">
-        <v>35.000999999999998</v>
+        <v>37.037999999999997</v>
       </c>
       <c r="I151">
-        <v>898.38199999999995</v>
+        <v>924.15700000000004</v>
       </c>
       <c r="J151" t="s">
         <v>17</v>
@@ -7665,7 +7662,7 @@
         <v>0</v>
       </c>
       <c r="L151">
-        <v>2.621</v>
+        <v>2.6960000000000002</v>
       </c>
       <c r="M151">
         <v>0</v>
@@ -7674,15 +7671,15 @@
         <v>46247</v>
       </c>
       <c r="O151" s="3">
-        <v>0.84163194444444445</v>
-      </c>
-    </row>
-    <row r="152" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+        <v>0.86883101851851852</v>
+      </c>
+    </row>
+    <row r="152" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A152" s="1" t="s">
         <v>40</v>
       </c>
       <c r="B152">
-        <v>23</v>
+        <v>176</v>
       </c>
       <c r="C152" t="s">
         <v>19</v>
@@ -7691,19 +7688,19 @@
         <v>0</v>
       </c>
       <c r="E152">
-        <v>0.37</v>
+        <v>0.43</v>
       </c>
       <c r="F152">
         <v>0</v>
       </c>
       <c r="G152">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="H152">
-        <v>16.821999999999999</v>
+        <v>22.672000000000001</v>
       </c>
       <c r="I152">
-        <v>1245.644</v>
+        <v>723.04300000000001</v>
       </c>
       <c r="J152" t="s">
         <v>17</v>
@@ -7712,7 +7709,7 @@
         <v>0</v>
       </c>
       <c r="L152">
-        <v>1.8169999999999999</v>
+        <v>2.109</v>
       </c>
       <c r="M152">
         <v>0</v>
@@ -7721,15 +7718,15 @@
         <v>46247</v>
       </c>
       <c r="O152" s="3">
-        <v>0.84261574074074075</v>
-      </c>
-    </row>
-    <row r="153" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A153" s="1" t="s">
+        <v>0.87002314814814818</v>
+      </c>
+    </row>
+    <row r="153" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A153" t="s">
         <v>40</v>
       </c>
       <c r="B153">
-        <v>27</v>
+        <v>180</v>
       </c>
       <c r="C153" t="s">
         <v>19</v>
@@ -7738,19 +7735,19 @@
         <v>0</v>
       </c>
       <c r="E153">
-        <v>0.38400000000000001</v>
+        <v>0.436</v>
       </c>
       <c r="F153">
         <v>0</v>
       </c>
       <c r="G153">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="H153">
-        <v>18.084</v>
+        <v>23.321999999999999</v>
       </c>
       <c r="I153">
-        <v>1291.5170000000001</v>
+        <v>733.33399999999995</v>
       </c>
       <c r="J153" t="s">
         <v>17</v>
@@ -7759,7 +7756,7 @@
         <v>0</v>
       </c>
       <c r="L153">
-        <v>1.8839999999999999</v>
+        <v>2.1389999999999998</v>
       </c>
       <c r="M153">
         <v>0</v>
@@ -7768,15 +7765,15 @@
         <v>46247</v>
       </c>
       <c r="O153" s="3">
-        <v>0.84341435185185187</v>
-      </c>
-    </row>
-    <row r="154" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A154" s="1" t="s">
+        <v>0.87063657407407402</v>
+      </c>
+    </row>
+    <row r="154" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A154" t="s">
         <v>40</v>
       </c>
       <c r="B154">
-        <v>31</v>
+        <v>184</v>
       </c>
       <c r="C154" t="s">
         <v>18</v>
@@ -7785,7 +7782,7 @@
         <v>0</v>
       </c>
       <c r="E154">
-        <v>0.32600000000000001</v>
+        <v>0.41099999999999998</v>
       </c>
       <c r="F154">
         <v>0</v>
@@ -7794,10 +7791,10 @@
         <v>0</v>
       </c>
       <c r="H154">
-        <v>13.013999999999999</v>
+        <v>20.718</v>
       </c>
       <c r="I154">
-        <v>547.81100000000004</v>
+        <v>691.18700000000001</v>
       </c>
       <c r="J154" t="s">
         <v>17</v>
@@ -7806,7 +7803,7 @@
         <v>0</v>
       </c>
       <c r="L154">
-        <v>1.5980000000000001</v>
+        <v>2.016</v>
       </c>
       <c r="M154">
         <v>0</v>
@@ -7815,15 +7812,15 @@
         <v>46247</v>
       </c>
       <c r="O154" s="3">
-        <v>0.8449768518518519</v>
-      </c>
-    </row>
-    <row r="155" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+        <v>0.87153935185185183</v>
+      </c>
+    </row>
+    <row r="155" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A155" s="1" t="s">
         <v>40</v>
       </c>
       <c r="B155">
-        <v>35</v>
+        <v>188</v>
       </c>
       <c r="C155" t="s">
         <v>18</v>
@@ -7832,7 +7829,7 @@
         <v>0</v>
       </c>
       <c r="E155">
-        <v>0.34300000000000003</v>
+        <v>0.40400000000000003</v>
       </c>
       <c r="F155">
         <v>0</v>
@@ -7841,10 +7838,10 @@
         <v>0</v>
       </c>
       <c r="H155">
-        <v>14.407</v>
+        <v>20.055</v>
       </c>
       <c r="I155">
-        <v>576.37099999999998</v>
+        <v>680.03499999999997</v>
       </c>
       <c r="J155" t="s">
         <v>17</v>
@@ -7853,7 +7850,7 @@
         <v>0</v>
       </c>
       <c r="L155">
-        <v>1.681</v>
+        <v>1.984</v>
       </c>
       <c r="M155">
         <v>0</v>
@@ -7862,24 +7859,24 @@
         <v>46247</v>
       </c>
       <c r="O155" s="3">
-        <v>0.84572916666666664</v>
+        <v>0.87212962962962959</v>
       </c>
     </row>
     <row r="156" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A156" t="s">
+      <c r="A156" s="1" t="s">
         <v>41</v>
       </c>
       <c r="B156">
-        <v>168</v>
+        <v>144</v>
       </c>
       <c r="C156" t="s">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="D156">
         <v>0</v>
       </c>
       <c r="E156">
-        <v>0.56000000000000005</v>
+        <v>0.59</v>
       </c>
       <c r="F156">
         <v>0</v>
@@ -7888,10 +7885,10 @@
         <v>0</v>
       </c>
       <c r="H156">
-        <v>38.405000000000001</v>
+        <v>42.649000000000001</v>
       </c>
       <c r="I156">
-        <v>941.053</v>
+        <v>991.68799999999999</v>
       </c>
       <c r="J156" t="s">
         <v>17</v>
@@ -7900,7 +7897,7 @@
         <v>0</v>
       </c>
       <c r="L156">
-        <v>2.7450000000000001</v>
+        <v>2.8929999999999998</v>
       </c>
       <c r="M156">
         <v>0</v>
@@ -7909,7 +7906,7 @@
         <v>46247</v>
       </c>
       <c r="O156" s="3">
-        <v>0.86763888888888885</v>
+        <v>0.85443287037037041</v>
       </c>
     </row>
     <row r="157" spans="1:15" x14ac:dyDescent="0.3">
@@ -7917,16 +7914,16 @@
         <v>41</v>
       </c>
       <c r="B157">
-        <v>172</v>
+        <v>148</v>
       </c>
       <c r="C157" t="s">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="D157">
         <v>0</v>
       </c>
       <c r="E157">
-        <v>0.55000000000000004</v>
+        <v>0.58199999999999996</v>
       </c>
       <c r="F157">
         <v>0</v>
@@ -7935,10 +7932,10 @@
         <v>0</v>
       </c>
       <c r="H157">
-        <v>37.037999999999997</v>
+        <v>41.557000000000002</v>
       </c>
       <c r="I157">
-        <v>924.15700000000004</v>
+        <v>978.90800000000002</v>
       </c>
       <c r="J157" t="s">
         <v>17</v>
@@ -7947,7 +7944,7 @@
         <v>0</v>
       </c>
       <c r="L157">
-        <v>2.6960000000000002</v>
+        <v>2.855</v>
       </c>
       <c r="M157">
         <v>0</v>
@@ -7956,7 +7953,7 @@
         <v>46247</v>
       </c>
       <c r="O157" s="3">
-        <v>0.86883101851851852</v>
+        <v>0.85556712962962966</v>
       </c>
     </row>
     <row r="158" spans="1:15" x14ac:dyDescent="0.3">
@@ -7964,7 +7961,7 @@
         <v>41</v>
       </c>
       <c r="B158">
-        <v>176</v>
+        <v>152</v>
       </c>
       <c r="C158" t="s">
         <v>19</v>
@@ -7973,7 +7970,7 @@
         <v>0</v>
       </c>
       <c r="E158">
-        <v>0.43</v>
+        <v>0.42099999999999999</v>
       </c>
       <c r="F158">
         <v>0</v>
@@ -7982,10 +7979,10 @@
         <v>0</v>
       </c>
       <c r="H158">
-        <v>22.672000000000001</v>
+        <v>21.693000000000001</v>
       </c>
       <c r="I158">
-        <v>723.04300000000001</v>
+        <v>707.26300000000003</v>
       </c>
       <c r="J158" t="s">
         <v>17</v>
@@ -7994,7 +7991,7 @@
         <v>0</v>
       </c>
       <c r="L158">
-        <v>2.109</v>
+        <v>2.0630000000000002</v>
       </c>
       <c r="M158">
         <v>0</v>
@@ -8003,15 +8000,15 @@
         <v>46247</v>
       </c>
       <c r="O158" s="3">
-        <v>0.87002314814814818</v>
+        <v>0.85723379629629626</v>
       </c>
     </row>
     <row r="159" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A159" t="s">
+      <c r="A159" s="1" t="s">
         <v>41</v>
       </c>
       <c r="B159">
-        <v>180</v>
+        <v>156</v>
       </c>
       <c r="C159" t="s">
         <v>19</v>
@@ -8020,7 +8017,7 @@
         <v>0</v>
       </c>
       <c r="E159">
-        <v>0.436</v>
+        <v>0.41699999999999998</v>
       </c>
       <c r="F159">
         <v>0</v>
@@ -8029,10 +8026,10 @@
         <v>0</v>
       </c>
       <c r="H159">
-        <v>23.321999999999999</v>
+        <v>21.279</v>
       </c>
       <c r="I159">
-        <v>733.33399999999995</v>
+        <v>700.48299999999995</v>
       </c>
       <c r="J159" t="s">
         <v>17</v>
@@ -8041,7 +8038,7 @@
         <v>0</v>
       </c>
       <c r="L159">
-        <v>2.1389999999999998</v>
+        <v>2.0430000000000001</v>
       </c>
       <c r="M159">
         <v>0</v>
@@ -8050,15 +8047,15 @@
         <v>46247</v>
       </c>
       <c r="O159" s="3">
-        <v>0.87063657407407402</v>
+        <v>0.85883101851851851</v>
       </c>
     </row>
     <row r="160" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A160" t="s">
+      <c r="A160" s="1" t="s">
         <v>41</v>
       </c>
       <c r="B160">
-        <v>184</v>
+        <v>160</v>
       </c>
       <c r="C160" t="s">
         <v>18</v>
@@ -8067,7 +8064,7 @@
         <v>0</v>
       </c>
       <c r="E160">
-        <v>0.41099999999999998</v>
+        <v>0.42299999999999999</v>
       </c>
       <c r="F160">
         <v>0</v>
@@ -8076,10 +8073,10 @@
         <v>0</v>
       </c>
       <c r="H160">
-        <v>20.718</v>
+        <v>21.901</v>
       </c>
       <c r="I160">
-        <v>691.18700000000001</v>
+        <v>710.65300000000002</v>
       </c>
       <c r="J160" t="s">
         <v>17</v>
@@ -8088,7 +8085,7 @@
         <v>0</v>
       </c>
       <c r="L160">
-        <v>2.016</v>
+        <v>2.073</v>
       </c>
       <c r="M160">
         <v>0</v>
@@ -8097,7 +8094,7 @@
         <v>46247</v>
       </c>
       <c r="O160" s="3">
-        <v>0.87153935185185183</v>
+        <v>0.8595949074074074</v>
       </c>
     </row>
     <row r="161" spans="1:15" x14ac:dyDescent="0.3">
@@ -8105,7 +8102,7 @@
         <v>41</v>
       </c>
       <c r="B161">
-        <v>188</v>
+        <v>164</v>
       </c>
       <c r="C161" t="s">
         <v>18</v>
@@ -8114,7 +8111,7 @@
         <v>0</v>
       </c>
       <c r="E161">
-        <v>0.40400000000000003</v>
+        <v>0.42199999999999999</v>
       </c>
       <c r="F161">
         <v>0</v>
@@ -8123,10 +8120,10 @@
         <v>0</v>
       </c>
       <c r="H161">
-        <v>20.055</v>
+        <v>21.815999999999999</v>
       </c>
       <c r="I161">
-        <v>680.03499999999997</v>
+        <v>709.26700000000005</v>
       </c>
       <c r="J161" t="s">
         <v>17</v>
@@ -8135,7 +8132,7 @@
         <v>0</v>
       </c>
       <c r="L161">
-        <v>1.984</v>
+        <v>2.069</v>
       </c>
       <c r="M161">
         <v>0</v>
@@ -8144,7 +8141,7 @@
         <v>46247</v>
       </c>
       <c r="O161" s="3">
-        <v>0.87212962962962959</v>
+        <v>0.86016203703703709</v>
       </c>
     </row>
     <row r="162" spans="1:15" x14ac:dyDescent="0.3">
@@ -8152,16 +8149,16 @@
         <v>42</v>
       </c>
       <c r="B162">
-        <v>144</v>
+        <v>124</v>
       </c>
       <c r="C162" t="s">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="D162">
         <v>0</v>
       </c>
       <c r="E162">
-        <v>0.59</v>
+        <v>0.57899999999999996</v>
       </c>
       <c r="F162">
         <v>0</v>
@@ -8170,10 +8167,10 @@
         <v>0</v>
       </c>
       <c r="H162">
-        <v>42.649000000000001</v>
+        <v>41.082000000000001</v>
       </c>
       <c r="I162">
-        <v>991.68799999999999</v>
+        <v>973.29899999999998</v>
       </c>
       <c r="J162" t="s">
         <v>17</v>
@@ -8182,7 +8179,7 @@
         <v>0</v>
       </c>
       <c r="L162">
-        <v>2.8929999999999998</v>
+        <v>2.839</v>
       </c>
       <c r="M162">
         <v>0</v>
@@ -8191,7 +8188,7 @@
         <v>46247</v>
       </c>
       <c r="O162" s="3">
-        <v>0.85443287037037041</v>
+        <v>0.84378472222222223</v>
       </c>
     </row>
     <row r="163" spans="1:15" x14ac:dyDescent="0.3">
@@ -8199,16 +8196,16 @@
         <v>42</v>
       </c>
       <c r="B163">
-        <v>148</v>
+        <v>127</v>
       </c>
       <c r="C163" t="s">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="D163">
         <v>0</v>
       </c>
       <c r="E163">
-        <v>0.58199999999999996</v>
+        <v>0.624</v>
       </c>
       <c r="F163">
         <v>0</v>
@@ -8217,10 +8214,10 @@
         <v>0</v>
       </c>
       <c r="H163">
-        <v>41.557000000000002</v>
+        <v>47.79</v>
       </c>
       <c r="I163">
-        <v>978.90800000000002</v>
+        <v>1049.7629999999999</v>
       </c>
       <c r="J163" t="s">
         <v>17</v>
@@ -8229,7 +8226,7 @@
         <v>0</v>
       </c>
       <c r="L163">
-        <v>2.855</v>
+        <v>3.0619999999999998</v>
       </c>
       <c r="M163">
         <v>0</v>
@@ -8238,7 +8235,7 @@
         <v>46247</v>
       </c>
       <c r="O163" s="3">
-        <v>0.85556712962962966</v>
+        <v>0.84478009259259257</v>
       </c>
     </row>
     <row r="164" spans="1:15" x14ac:dyDescent="0.3">
@@ -8246,7 +8243,7 @@
         <v>42</v>
       </c>
       <c r="B164">
-        <v>152</v>
+        <v>130</v>
       </c>
       <c r="C164" t="s">
         <v>19</v>
@@ -8255,7 +8252,7 @@
         <v>0</v>
       </c>
       <c r="E164">
-        <v>0.42099999999999999</v>
+        <v>0.36799999999999999</v>
       </c>
       <c r="F164">
         <v>0</v>
@@ -8264,10 +8261,10 @@
         <v>0</v>
       </c>
       <c r="H164">
-        <v>21.693000000000001</v>
+        <v>16.609000000000002</v>
       </c>
       <c r="I164">
-        <v>707.26300000000003</v>
+        <v>618.86699999999996</v>
       </c>
       <c r="J164" t="s">
         <v>17</v>
@@ -8276,7 +8273,7 @@
         <v>0</v>
       </c>
       <c r="L164">
-        <v>2.0630000000000002</v>
+        <v>1.8049999999999999</v>
       </c>
       <c r="M164">
         <v>0</v>
@@ -8285,7 +8282,7 @@
         <v>46247</v>
       </c>
       <c r="O164" s="3">
-        <v>0.85723379629629626</v>
+        <v>0.84591435185185182</v>
       </c>
     </row>
     <row r="165" spans="1:15" x14ac:dyDescent="0.3">
@@ -8293,7 +8290,7 @@
         <v>42</v>
       </c>
       <c r="B165">
-        <v>156</v>
+        <v>133</v>
       </c>
       <c r="C165" t="s">
         <v>19</v>
@@ -8302,7 +8299,7 @@
         <v>0</v>
       </c>
       <c r="E165">
-        <v>0.41699999999999998</v>
+        <v>0.40600000000000003</v>
       </c>
       <c r="F165">
         <v>0</v>
@@ -8311,10 +8308,10 @@
         <v>0</v>
       </c>
       <c r="H165">
-        <v>21.279</v>
+        <v>20.233000000000001</v>
       </c>
       <c r="I165">
-        <v>700.48299999999995</v>
+        <v>683.04899999999998</v>
       </c>
       <c r="J165" t="s">
         <v>17</v>
@@ -8323,7 +8320,7 @@
         <v>0</v>
       </c>
       <c r="L165">
-        <v>2.0430000000000001</v>
+        <v>1.992</v>
       </c>
       <c r="M165">
         <v>0</v>
@@ -8332,7 +8329,7 @@
         <v>46247</v>
       </c>
       <c r="O165" s="3">
-        <v>0.85883101851851851</v>
+        <v>0.84672453703703698</v>
       </c>
     </row>
     <row r="166" spans="1:15" x14ac:dyDescent="0.3">
@@ -8340,7 +8337,7 @@
         <v>42</v>
       </c>
       <c r="B166">
-        <v>160</v>
+        <v>136</v>
       </c>
       <c r="C166" t="s">
         <v>18</v>
@@ -8349,7 +8346,7 @@
         <v>0</v>
       </c>
       <c r="E166">
-        <v>0.42299999999999999</v>
+        <v>0.41599999999999998</v>
       </c>
       <c r="F166">
         <v>0</v>
@@ -8358,10 +8355,10 @@
         <v>0</v>
       </c>
       <c r="H166">
-        <v>21.901</v>
+        <v>21.234999999999999</v>
       </c>
       <c r="I166">
-        <v>710.65300000000002</v>
+        <v>699.75699999999995</v>
       </c>
       <c r="J166" t="s">
         <v>17</v>
@@ -8370,7 +8367,7 @@
         <v>0</v>
       </c>
       <c r="L166">
-        <v>2.073</v>
+        <v>2.0409999999999999</v>
       </c>
       <c r="M166">
         <v>0</v>
@@ -8379,7 +8376,7 @@
         <v>46247</v>
       </c>
       <c r="O166" s="3">
-        <v>0.8595949074074074</v>
+        <v>0.84755787037037034</v>
       </c>
     </row>
     <row r="167" spans="1:15" x14ac:dyDescent="0.3">
@@ -8387,7 +8384,7 @@
         <v>42</v>
       </c>
       <c r="B167">
-        <v>164</v>
+        <v>139</v>
       </c>
       <c r="C167" t="s">
         <v>18</v>
@@ -8396,7 +8393,7 @@
         <v>0</v>
       </c>
       <c r="E167">
-        <v>0.42199999999999999</v>
+        <v>0.41099999999999998</v>
       </c>
       <c r="F167">
         <v>0</v>
@@ -8405,10 +8402,10 @@
         <v>0</v>
       </c>
       <c r="H167">
-        <v>21.815999999999999</v>
+        <v>20.754000000000001</v>
       </c>
       <c r="I167">
-        <v>709.26700000000005</v>
+        <v>691.79300000000001</v>
       </c>
       <c r="J167" t="s">
         <v>17</v>
@@ -8417,7 +8414,7 @@
         <v>0</v>
       </c>
       <c r="L167">
-        <v>2.069</v>
+        <v>2.0179999999999998</v>
       </c>
       <c r="M167">
         <v>0</v>
@@ -8426,7 +8423,7 @@
         <v>46247</v>
       </c>
       <c r="O167" s="3">
-        <v>0.86016203703703709</v>
+        <v>0.8482291666666667</v>
       </c>
     </row>
     <row r="168" spans="1:15" x14ac:dyDescent="0.3">
@@ -8434,7 +8431,7 @@
         <v>43</v>
       </c>
       <c r="B168">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C168" t="s">
         <v>0</v>
@@ -8443,7 +8440,7 @@
         <v>0</v>
       </c>
       <c r="E168">
-        <v>0.57899999999999996</v>
+        <v>0.496</v>
       </c>
       <c r="F168">
         <v>0</v>
@@ -8452,10 +8449,10 @@
         <v>0</v>
       </c>
       <c r="H168">
-        <v>41.082000000000001</v>
+        <v>30.172999999999998</v>
       </c>
       <c r="I168">
-        <v>973.29899999999998</v>
+        <v>834.12</v>
       </c>
       <c r="J168" t="s">
         <v>17</v>
@@ -8464,7 +8461,7 @@
         <v>0</v>
       </c>
       <c r="L168">
-        <v>2.839</v>
+        <v>2.4329999999999998</v>
       </c>
       <c r="M168">
         <v>0</v>
@@ -8473,7 +8470,7 @@
         <v>46247</v>
       </c>
       <c r="O168" s="3">
-        <v>0.84378472222222223</v>
+        <v>0.84442129629629625</v>
       </c>
     </row>
     <row r="169" spans="1:15" x14ac:dyDescent="0.3">
@@ -8481,7 +8478,7 @@
         <v>43</v>
       </c>
       <c r="B169">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C169" t="s">
         <v>0</v>
@@ -8490,7 +8487,7 @@
         <v>0</v>
       </c>
       <c r="E169">
-        <v>0.624</v>
+        <v>0.51500000000000001</v>
       </c>
       <c r="F169">
         <v>0</v>
@@ -8499,10 +8496,10 @@
         <v>0</v>
       </c>
       <c r="H169">
-        <v>47.79</v>
+        <v>32.582999999999998</v>
       </c>
       <c r="I169">
-        <v>1049.7629999999999</v>
+        <v>866.79600000000005</v>
       </c>
       <c r="J169" t="s">
         <v>17</v>
@@ -8511,7 +8508,7 @@
         <v>0</v>
       </c>
       <c r="L169">
-        <v>3.0619999999999998</v>
+        <v>2.528</v>
       </c>
       <c r="M169">
         <v>0</v>
@@ -8520,7 +8517,7 @@
         <v>46247</v>
       </c>
       <c r="O169" s="3">
-        <v>0.84478009259259257</v>
+        <v>0.84540509259259256</v>
       </c>
     </row>
     <row r="170" spans="1:15" x14ac:dyDescent="0.3">
@@ -8528,7 +8525,7 @@
         <v>43</v>
       </c>
       <c r="B170">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C170" t="s">
         <v>19</v>
@@ -8537,7 +8534,7 @@
         <v>0</v>
       </c>
       <c r="E170">
-        <v>0.36799999999999999</v>
+        <v>0.30299999999999999</v>
       </c>
       <c r="F170">
         <v>0</v>
@@ -8546,10 +8543,10 @@
         <v>0</v>
       </c>
       <c r="H170">
-        <v>16.609000000000002</v>
+        <v>11.252000000000001</v>
       </c>
       <c r="I170">
-        <v>618.86699999999996</v>
+        <v>509.37700000000001</v>
       </c>
       <c r="J170" t="s">
         <v>17</v>
@@ -8558,7 +8555,7 @@
         <v>0</v>
       </c>
       <c r="L170">
-        <v>1.8049999999999999</v>
+        <v>1.486</v>
       </c>
       <c r="M170">
         <v>0</v>
@@ -8567,7 +8564,7 @@
         <v>46247</v>
       </c>
       <c r="O170" s="3">
-        <v>0.84591435185185182</v>
+        <v>0.84630787037037036</v>
       </c>
     </row>
     <row r="171" spans="1:15" x14ac:dyDescent="0.3">
@@ -8575,7 +8572,7 @@
         <v>43</v>
       </c>
       <c r="B171">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C171" t="s">
         <v>19</v>
@@ -8584,7 +8581,7 @@
         <v>0</v>
       </c>
       <c r="E171">
-        <v>0.40600000000000003</v>
+        <v>0.34799999999999998</v>
       </c>
       <c r="F171">
         <v>0</v>
@@ -8593,10 +8590,10 @@
         <v>0</v>
       </c>
       <c r="H171">
-        <v>20.233000000000001</v>
+        <v>14.821</v>
       </c>
       <c r="I171">
-        <v>683.04899999999998</v>
+        <v>584.60299999999995</v>
       </c>
       <c r="J171" t="s">
         <v>17</v>
@@ -8605,7 +8602,7 @@
         <v>0</v>
       </c>
       <c r="L171">
-        <v>1.992</v>
+        <v>1.7050000000000001</v>
       </c>
       <c r="M171">
         <v>0</v>
@@ -8614,7 +8611,7 @@
         <v>46247</v>
       </c>
       <c r="O171" s="3">
-        <v>0.84672453703703698</v>
+        <v>0.84733796296296293</v>
       </c>
     </row>
     <row r="172" spans="1:15" x14ac:dyDescent="0.3">
@@ -8622,7 +8619,7 @@
         <v>43</v>
       </c>
       <c r="B172">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C172" t="s">
         <v>18</v>
@@ -8631,7 +8628,7 @@
         <v>0</v>
       </c>
       <c r="E172">
-        <v>0.41599999999999998</v>
+        <v>0.35099999999999998</v>
       </c>
       <c r="F172">
         <v>0</v>
@@ -8640,10 +8637,10 @@
         <v>0</v>
       </c>
       <c r="H172">
-        <v>21.234999999999999</v>
+        <v>15.105</v>
       </c>
       <c r="I172">
-        <v>699.75699999999995</v>
+        <v>590.18600000000004</v>
       </c>
       <c r="J172" t="s">
         <v>17</v>
@@ -8652,7 +8649,7 @@
         <v>0</v>
       </c>
       <c r="L172">
-        <v>2.0409999999999999</v>
+        <v>1.722</v>
       </c>
       <c r="M172">
         <v>0</v>
@@ -8661,7 +8658,7 @@
         <v>46247</v>
       </c>
       <c r="O172" s="3">
-        <v>0.84755787037037034</v>
+        <v>0.8480671296296296</v>
       </c>
     </row>
     <row r="173" spans="1:15" x14ac:dyDescent="0.3">
@@ -8669,7 +8666,7 @@
         <v>43</v>
       </c>
       <c r="B173">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C173" t="s">
         <v>18</v>
@@ -8678,7 +8675,7 @@
         <v>0</v>
       </c>
       <c r="E173">
-        <v>0.41099999999999998</v>
+        <v>0.33200000000000002</v>
       </c>
       <c r="F173">
         <v>0</v>
@@ -8687,10 +8684,10 @@
         <v>0</v>
       </c>
       <c r="H173">
-        <v>20.754000000000001</v>
+        <v>13.492000000000001</v>
       </c>
       <c r="I173">
-        <v>691.79300000000001</v>
+        <v>557.779</v>
       </c>
       <c r="J173" t="s">
         <v>17</v>
@@ -8699,7 +8696,7 @@
         <v>0</v>
       </c>
       <c r="L173">
-        <v>2.0179999999999998</v>
+        <v>1.627</v>
       </c>
       <c r="M173">
         <v>0</v>
@@ -8708,15 +8705,15 @@
         <v>46247</v>
       </c>
       <c r="O173" s="3">
-        <v>0.8482291666666667</v>
-      </c>
-    </row>
-    <row r="174" spans="1:15" x14ac:dyDescent="0.3">
+        <v>0.84864583333333332</v>
+      </c>
+    </row>
+    <row r="174" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A174" s="1" t="s">
         <v>44</v>
       </c>
       <c r="B174">
-        <v>126</v>
+        <v>146</v>
       </c>
       <c r="C174" t="s">
         <v>0</v>
@@ -8725,7 +8722,7 @@
         <v>0</v>
       </c>
       <c r="E174">
-        <v>0.496</v>
+        <v>0.52800000000000002</v>
       </c>
       <c r="F174">
         <v>0</v>
@@ -8734,10 +8731,10 @@
         <v>0</v>
       </c>
       <c r="H174">
-        <v>30.172999999999998</v>
+        <v>34.200000000000003</v>
       </c>
       <c r="I174">
-        <v>834.12</v>
+        <v>888.05100000000004</v>
       </c>
       <c r="J174" t="s">
         <v>17</v>
@@ -8746,7 +8743,7 @@
         <v>0</v>
       </c>
       <c r="L174">
-        <v>2.4329999999999998</v>
+        <v>2.59</v>
       </c>
       <c r="M174">
         <v>0</v>
@@ -8755,15 +8752,15 @@
         <v>46247</v>
       </c>
       <c r="O174" s="3">
-        <v>0.84442129629629625</v>
-      </c>
-    </row>
-    <row r="175" spans="1:15" x14ac:dyDescent="0.3">
+        <v>0.85502314814814817</v>
+      </c>
+    </row>
+    <row r="175" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A175" s="1" t="s">
         <v>44</v>
       </c>
       <c r="B175">
-        <v>129</v>
+        <v>142</v>
       </c>
       <c r="C175" t="s">
         <v>0</v>
@@ -8772,7 +8769,7 @@
         <v>0</v>
       </c>
       <c r="E175">
-        <v>0.51500000000000001</v>
+        <v>0.50800000000000001</v>
       </c>
       <c r="F175">
         <v>0</v>
@@ -8781,10 +8778,10 @@
         <v>0</v>
       </c>
       <c r="H175">
-        <v>32.582999999999998</v>
+        <v>31.695</v>
       </c>
       <c r="I175">
-        <v>866.79600000000005</v>
+        <v>854.904</v>
       </c>
       <c r="J175" t="s">
         <v>17</v>
@@ -8793,7 +8790,7 @@
         <v>0</v>
       </c>
       <c r="L175">
-        <v>2.528</v>
+        <v>2.4940000000000002</v>
       </c>
       <c r="M175">
         <v>0</v>
@@ -8802,15 +8799,15 @@
         <v>46247</v>
       </c>
       <c r="O175" s="3">
-        <v>0.84540509259259256</v>
-      </c>
-    </row>
-    <row r="176" spans="1:15" x14ac:dyDescent="0.3">
+        <v>0.8539930555555556</v>
+      </c>
+    </row>
+    <row r="176" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A176" s="1" t="s">
         <v>44</v>
       </c>
       <c r="B176">
-        <v>132</v>
+        <v>150</v>
       </c>
       <c r="C176" t="s">
         <v>19</v>
@@ -8819,7 +8816,7 @@
         <v>0</v>
       </c>
       <c r="E176">
-        <v>0.30299999999999999</v>
+        <v>0.35699999999999998</v>
       </c>
       <c r="F176">
         <v>0</v>
@@ -8828,10 +8825,10 @@
         <v>0</v>
       </c>
       <c r="H176">
-        <v>11.252000000000001</v>
+        <v>15.625999999999999</v>
       </c>
       <c r="I176">
-        <v>509.37700000000001</v>
+        <v>600.27599999999995</v>
       </c>
       <c r="J176" t="s">
         <v>17</v>
@@ -8840,7 +8837,7 @@
         <v>0</v>
       </c>
       <c r="L176">
-        <v>1.486</v>
+        <v>1.7509999999999999</v>
       </c>
       <c r="M176">
         <v>0</v>
@@ -8849,15 +8846,15 @@
         <v>46247</v>
       </c>
       <c r="O176" s="3">
-        <v>0.84630787037037036</v>
-      </c>
-    </row>
-    <row r="177" spans="1:15" x14ac:dyDescent="0.3">
+        <v>0.85682870370370368</v>
+      </c>
+    </row>
+    <row r="177" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A177" s="1" t="s">
         <v>44</v>
       </c>
       <c r="B177">
-        <v>135</v>
+        <v>154</v>
       </c>
       <c r="C177" t="s">
         <v>19</v>
@@ -8866,7 +8863,7 @@
         <v>0</v>
       </c>
       <c r="E177">
-        <v>0.34799999999999998</v>
+        <v>0.35</v>
       </c>
       <c r="F177">
         <v>0</v>
@@ -8875,10 +8872,10 @@
         <v>0</v>
       </c>
       <c r="H177">
-        <v>14.821</v>
+        <v>15.005000000000001</v>
       </c>
       <c r="I177">
-        <v>584.60299999999995</v>
+        <v>588.22199999999998</v>
       </c>
       <c r="J177" t="s">
         <v>17</v>
@@ -8887,7 +8884,7 @@
         <v>0</v>
       </c>
       <c r="L177">
-        <v>1.7050000000000001</v>
+        <v>1.716</v>
       </c>
       <c r="M177">
         <v>0</v>
@@ -8896,15 +8893,15 @@
         <v>46247</v>
       </c>
       <c r="O177" s="3">
-        <v>0.84733796296296293</v>
-      </c>
-    </row>
-    <row r="178" spans="1:15" x14ac:dyDescent="0.3">
+        <v>0.85851851851851857</v>
+      </c>
+    </row>
+    <row r="178" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A178" s="1" t="s">
         <v>44</v>
       </c>
       <c r="B178">
-        <v>138</v>
+        <v>158</v>
       </c>
       <c r="C178" t="s">
         <v>18</v>
@@ -8913,7 +8910,7 @@
         <v>0</v>
       </c>
       <c r="E178">
-        <v>0.35099999999999998</v>
+        <v>0.374</v>
       </c>
       <c r="F178">
         <v>0</v>
@@ -8922,10 +8919,10 @@
         <v>0</v>
       </c>
       <c r="H178">
-        <v>15.105</v>
+        <v>17.195</v>
       </c>
       <c r="I178">
-        <v>590.18600000000004</v>
+        <v>629.68299999999999</v>
       </c>
       <c r="J178" t="s">
         <v>17</v>
@@ -8934,7 +8931,7 @@
         <v>0</v>
       </c>
       <c r="L178">
-        <v>1.722</v>
+        <v>1.837</v>
       </c>
       <c r="M178">
         <v>0</v>
@@ -8943,15 +8940,15 @@
         <v>46247</v>
       </c>
       <c r="O178" s="3">
-        <v>0.8480671296296296</v>
-      </c>
-    </row>
-    <row r="179" spans="1:15" x14ac:dyDescent="0.3">
+        <v>0.85935185185185181</v>
+      </c>
+    </row>
+    <row r="179" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A179" s="1" t="s">
         <v>44</v>
       </c>
       <c r="B179">
-        <v>141</v>
+        <v>162</v>
       </c>
       <c r="C179" t="s">
         <v>18</v>
@@ -8960,7 +8957,7 @@
         <v>0</v>
       </c>
       <c r="E179">
-        <v>0.33200000000000002</v>
+        <v>0.39200000000000002</v>
       </c>
       <c r="F179">
         <v>0</v>
@@ -8969,10 +8966,10 @@
         <v>0</v>
       </c>
       <c r="H179">
-        <v>13.492000000000001</v>
+        <v>18.869</v>
       </c>
       <c r="I179">
-        <v>557.779</v>
+        <v>659.62800000000004</v>
       </c>
       <c r="J179" t="s">
         <v>17</v>
@@ -8981,7 +8978,7 @@
         <v>0</v>
       </c>
       <c r="L179">
-        <v>1.627</v>
+        <v>1.9239999999999999</v>
       </c>
       <c r="M179">
         <v>0</v>
@@ -8990,15 +8987,15 @@
         <v>46247</v>
       </c>
       <c r="O179" s="3">
-        <v>0.84864583333333332</v>
-      </c>
-    </row>
-    <row r="180" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+        <v>0.85987268518518523</v>
+      </c>
+    </row>
+    <row r="180" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A180" s="1" t="s">
         <v>45</v>
       </c>
       <c r="B180">
-        <v>146</v>
+        <v>10</v>
       </c>
       <c r="C180" t="s">
         <v>0</v>
@@ -9007,7 +9004,7 @@
         <v>0</v>
       </c>
       <c r="E180">
-        <v>0.52800000000000002</v>
+        <v>0.53100000000000003</v>
       </c>
       <c r="F180">
         <v>0</v>
@@ -9016,10 +9013,10 @@
         <v>0</v>
       </c>
       <c r="H180">
-        <v>34.200000000000003</v>
+        <v>34.624000000000002</v>
       </c>
       <c r="I180">
-        <v>888.05100000000004</v>
+        <v>893.53899999999999</v>
       </c>
       <c r="J180" t="s">
         <v>17</v>
@@ -9028,7 +9025,7 @@
         <v>0</v>
       </c>
       <c r="L180">
-        <v>2.59</v>
+        <v>2.6059999999999999</v>
       </c>
       <c r="M180">
         <v>0</v>
@@ -9037,15 +9034,15 @@
         <v>46247</v>
       </c>
       <c r="O180" s="3">
-        <v>0.85502314814814817</v>
-      </c>
-    </row>
-    <row r="181" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+        <v>0.83939814814814817</v>
+      </c>
+    </row>
+    <row r="181" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A181" s="1" t="s">
         <v>45</v>
       </c>
       <c r="B181">
-        <v>142</v>
+        <v>14</v>
       </c>
       <c r="C181" t="s">
         <v>0</v>
@@ -9054,7 +9051,7 @@
         <v>0</v>
       </c>
       <c r="E181">
-        <v>0.50800000000000001</v>
+        <v>0.53900000000000003</v>
       </c>
       <c r="F181">
         <v>0</v>
@@ -9063,10 +9060,10 @@
         <v>0</v>
       </c>
       <c r="H181">
-        <v>31.695</v>
+        <v>35.648000000000003</v>
       </c>
       <c r="I181">
-        <v>854.904</v>
+        <v>906.65499999999997</v>
       </c>
       <c r="J181" t="s">
         <v>17</v>
@@ -9075,7 +9072,7 @@
         <v>0</v>
       </c>
       <c r="L181">
-        <v>2.4940000000000002</v>
+        <v>2.645</v>
       </c>
       <c r="M181">
         <v>0</v>
@@ -9084,24 +9081,24 @@
         <v>46247</v>
       </c>
       <c r="O181" s="3">
-        <v>0.8539930555555556</v>
-      </c>
-    </row>
-    <row r="182" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+        <v>0.8404166666666667</v>
+      </c>
+    </row>
+    <row r="182" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A182" s="1" t="s">
         <v>45</v>
       </c>
       <c r="B182">
-        <v>150</v>
+        <v>18</v>
       </c>
       <c r="C182" t="s">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="D182">
         <v>0</v>
       </c>
       <c r="E182">
-        <v>0.35699999999999998</v>
+        <v>0.54400000000000004</v>
       </c>
       <c r="F182">
         <v>0</v>
@@ -9110,10 +9107,10 @@
         <v>0</v>
       </c>
       <c r="H182">
-        <v>15.625999999999999</v>
+        <v>36.231999999999999</v>
       </c>
       <c r="I182">
-        <v>600.27599999999995</v>
+        <v>914.04100000000005</v>
       </c>
       <c r="J182" t="s">
         <v>17</v>
@@ -9122,7 +9119,7 @@
         <v>0</v>
       </c>
       <c r="L182">
-        <v>1.7509999999999999</v>
+        <v>2.6659999999999999</v>
       </c>
       <c r="M182">
         <v>0</v>
@@ -9131,15 +9128,15 @@
         <v>46247</v>
       </c>
       <c r="O182" s="3">
-        <v>0.85682870370370368</v>
-      </c>
-    </row>
-    <row r="183" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+        <v>0.84149305555555554</v>
+      </c>
+    </row>
+    <row r="183" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A183" s="1" t="s">
         <v>45</v>
       </c>
       <c r="B183">
-        <v>154</v>
+        <v>22</v>
       </c>
       <c r="C183" t="s">
         <v>19</v>
@@ -9148,19 +9145,19 @@
         <v>0</v>
       </c>
       <c r="E183">
-        <v>0.35</v>
+        <v>0.375</v>
       </c>
       <c r="F183">
         <v>0</v>
       </c>
       <c r="G183">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="H183">
-        <v>15.005000000000001</v>
+        <v>17.242999999999999</v>
       </c>
       <c r="I183">
-        <v>588.22199999999998</v>
+        <v>1261.114</v>
       </c>
       <c r="J183" t="s">
         <v>17</v>
@@ -9169,7 +9166,7 @@
         <v>0</v>
       </c>
       <c r="L183">
-        <v>1.716</v>
+        <v>1.839</v>
       </c>
       <c r="M183">
         <v>0</v>
@@ -9178,36 +9175,36 @@
         <v>46247</v>
       </c>
       <c r="O183" s="3">
-        <v>0.85851851851851857</v>
-      </c>
-    </row>
-    <row r="184" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+        <v>0.84244212962962961</v>
+      </c>
+    </row>
+    <row r="184" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A184" s="1" t="s">
         <v>45</v>
       </c>
       <c r="B184">
-        <v>158</v>
+        <v>26</v>
       </c>
       <c r="C184" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D184">
         <v>0</v>
       </c>
       <c r="E184">
-        <v>0.374</v>
+        <v>0.371</v>
       </c>
       <c r="F184">
         <v>0</v>
       </c>
       <c r="G184">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="H184">
-        <v>17.195</v>
+        <v>16.907</v>
       </c>
       <c r="I184">
-        <v>629.68299999999999</v>
+        <v>1248.7650000000001</v>
       </c>
       <c r="J184" t="s">
         <v>17</v>
@@ -9216,7 +9213,7 @@
         <v>0</v>
       </c>
       <c r="L184">
-        <v>1.837</v>
+        <v>1.821</v>
       </c>
       <c r="M184">
         <v>0</v>
@@ -9225,15 +9222,15 @@
         <v>46247</v>
       </c>
       <c r="O184" s="3">
-        <v>0.85935185185185181</v>
-      </c>
-    </row>
-    <row r="185" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+        <v>0.84321759259259255</v>
+      </c>
+    </row>
+    <row r="185" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A185" s="1" t="s">
         <v>45</v>
       </c>
       <c r="B185">
-        <v>162</v>
+        <v>30</v>
       </c>
       <c r="C185" t="s">
         <v>18</v>
@@ -9242,7 +9239,7 @@
         <v>0</v>
       </c>
       <c r="E185">
-        <v>0.39200000000000002</v>
+        <v>0.35699999999999998</v>
       </c>
       <c r="F185">
         <v>0</v>
@@ -9251,10 +9248,10 @@
         <v>0</v>
       </c>
       <c r="H185">
-        <v>18.869</v>
+        <v>15.590999999999999</v>
       </c>
       <c r="I185">
-        <v>659.62800000000004</v>
+        <v>599.60299999999995</v>
       </c>
       <c r="J185" t="s">
         <v>17</v>
@@ -9263,7 +9260,7 @@
         <v>0</v>
       </c>
       <c r="L185">
-        <v>1.9239999999999999</v>
+        <v>1.7490000000000001</v>
       </c>
       <c r="M185">
         <v>0</v>
@@ -9272,24 +9269,24 @@
         <v>46247</v>
       </c>
       <c r="O185" s="3">
-        <v>0.85987268518518523</v>
+        <v>0.8443518518518518</v>
       </c>
     </row>
     <row r="186" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A186" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B186">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="C186" t="s">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="D186">
         <v>0</v>
       </c>
       <c r="E186">
-        <v>0.53100000000000003</v>
+        <v>0.35599999999999998</v>
       </c>
       <c r="F186">
         <v>0</v>
@@ -9298,10 +9295,10 @@
         <v>0</v>
       </c>
       <c r="H186">
-        <v>34.624000000000002</v>
+        <v>15.534000000000001</v>
       </c>
       <c r="I186">
-        <v>893.53899999999999</v>
+        <v>598.5</v>
       </c>
       <c r="J186" t="s">
         <v>17</v>
@@ -9310,7 +9307,7 @@
         <v>0</v>
       </c>
       <c r="L186">
-        <v>2.6059999999999999</v>
+        <v>1.746</v>
       </c>
       <c r="M186">
         <v>0</v>
@@ -9319,15 +9316,15 @@
         <v>46247</v>
       </c>
       <c r="O186" s="3">
-        <v>0.83939814814814817</v>
-      </c>
-    </row>
-    <row r="187" spans="1:15" x14ac:dyDescent="0.3">
+        <v>0.84560185185185188</v>
+      </c>
+    </row>
+    <row r="187" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A187" s="1" t="s">
         <v>46</v>
       </c>
       <c r="B187">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C187" t="s">
         <v>0</v>
@@ -9336,7 +9333,7 @@
         <v>0</v>
       </c>
       <c r="E187">
-        <v>0.53900000000000003</v>
+        <v>0.49</v>
       </c>
       <c r="F187">
         <v>0</v>
@@ -9345,10 +9342,10 @@
         <v>0</v>
       </c>
       <c r="H187">
-        <v>35.648000000000003</v>
+        <v>29.385000000000002</v>
       </c>
       <c r="I187">
-        <v>906.65499999999997</v>
+        <v>823.15599999999995</v>
       </c>
       <c r="J187" t="s">
         <v>17</v>
@@ -9357,7 +9354,7 @@
         <v>0</v>
       </c>
       <c r="L187">
-        <v>2.645</v>
+        <v>2.4009999999999998</v>
       </c>
       <c r="M187">
         <v>0</v>
@@ -9366,15 +9363,15 @@
         <v>46247</v>
       </c>
       <c r="O187" s="3">
-        <v>0.8404166666666667</v>
-      </c>
-    </row>
-    <row r="188" spans="1:15" x14ac:dyDescent="0.3">
+        <v>0.84018518518518515</v>
+      </c>
+    </row>
+    <row r="188" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A188" s="1" t="s">
         <v>46</v>
       </c>
       <c r="B188">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C188" t="s">
         <v>0</v>
@@ -9383,7 +9380,7 @@
         <v>0</v>
       </c>
       <c r="E188">
-        <v>0.54400000000000004</v>
+        <v>0.45300000000000001</v>
       </c>
       <c r="F188">
         <v>0</v>
@@ -9392,10 +9389,10 @@
         <v>0</v>
       </c>
       <c r="H188">
-        <v>36.231999999999999</v>
+        <v>25.131</v>
       </c>
       <c r="I188">
-        <v>914.04100000000005</v>
+        <v>761.24800000000005</v>
       </c>
       <c r="J188" t="s">
         <v>17</v>
@@ -9404,7 +9401,7 @@
         <v>0</v>
       </c>
       <c r="L188">
-        <v>2.6659999999999999</v>
+        <v>2.2210000000000001</v>
       </c>
       <c r="M188">
         <v>0</v>
@@ -9413,36 +9410,36 @@
         <v>46247</v>
       </c>
       <c r="O188" s="3">
-        <v>0.84149305555555554</v>
-      </c>
-    </row>
-    <row r="189" spans="1:15" x14ac:dyDescent="0.3">
+        <v>0.84107638888888892</v>
+      </c>
+    </row>
+    <row r="189" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A189" s="1" t="s">
         <v>46</v>
       </c>
       <c r="B189">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C189" t="s">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="D189">
         <v>0</v>
       </c>
       <c r="E189">
-        <v>0.375</v>
+        <v>0.48899999999999999</v>
       </c>
       <c r="F189">
         <v>0</v>
       </c>
       <c r="G189">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="H189">
-        <v>17.242999999999999</v>
+        <v>29.314</v>
       </c>
       <c r="I189">
-        <v>1261.114</v>
+        <v>822.16</v>
       </c>
       <c r="J189" t="s">
         <v>17</v>
@@ -9451,7 +9448,7 @@
         <v>0</v>
       </c>
       <c r="L189">
-        <v>1.839</v>
+        <v>2.3980000000000001</v>
       </c>
       <c r="M189">
         <v>0</v>
@@ -9460,15 +9457,15 @@
         <v>46247</v>
       </c>
       <c r="O189" s="3">
-        <v>0.84244212962962961</v>
-      </c>
-    </row>
-    <row r="190" spans="1:15" x14ac:dyDescent="0.3">
+        <v>0.84189814814814812</v>
+      </c>
+    </row>
+    <row r="190" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A190" s="1" t="s">
         <v>46</v>
       </c>
       <c r="B190">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C190" t="s">
         <v>19</v>
@@ -9477,7 +9474,7 @@
         <v>0</v>
       </c>
       <c r="E190">
-        <v>0.371</v>
+        <v>0.308</v>
       </c>
       <c r="F190">
         <v>0</v>
@@ -9486,10 +9483,10 @@
         <v>70</v>
       </c>
       <c r="H190">
-        <v>16.907</v>
+        <v>11.661</v>
       </c>
       <c r="I190">
-        <v>1248.7650000000001</v>
+        <v>1037.104</v>
       </c>
       <c r="J190" t="s">
         <v>17</v>
@@ -9498,7 +9495,7 @@
         <v>0</v>
       </c>
       <c r="L190">
-        <v>1.821</v>
+        <v>1.5129999999999999</v>
       </c>
       <c r="M190">
         <v>0</v>
@@ -9507,36 +9504,36 @@
         <v>46247</v>
       </c>
       <c r="O190" s="3">
-        <v>0.84321759259259255</v>
-      </c>
-    </row>
-    <row r="191" spans="1:15" x14ac:dyDescent="0.3">
+        <v>0.84288194444444442</v>
+      </c>
+    </row>
+    <row r="191" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A191" s="1" t="s">
         <v>46</v>
       </c>
       <c r="B191">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C191" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D191">
         <v>0</v>
       </c>
       <c r="E191">
-        <v>0.35699999999999998</v>
+        <v>0.34899999999999998</v>
       </c>
       <c r="F191">
         <v>0</v>
       </c>
       <c r="G191">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="H191">
-        <v>15.590999999999999</v>
+        <v>14.974</v>
       </c>
       <c r="I191">
-        <v>599.60299999999995</v>
+        <v>1175.2339999999999</v>
       </c>
       <c r="J191" t="s">
         <v>17</v>
@@ -9545,7 +9542,7 @@
         <v>0</v>
       </c>
       <c r="L191">
-        <v>1.7490000000000001</v>
+        <v>1.714</v>
       </c>
       <c r="M191">
         <v>0</v>
@@ -9554,15 +9551,15 @@
         <v>46247</v>
       </c>
       <c r="O191" s="3">
-        <v>0.8443518518518518</v>
-      </c>
-    </row>
-    <row r="192" spans="1:15" x14ac:dyDescent="0.3">
+        <v>0.84378472222222223</v>
+      </c>
+    </row>
+    <row r="192" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A192" s="1" t="s">
         <v>46</v>
       </c>
       <c r="B192">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C192" t="s">
         <v>18</v>
@@ -9571,7 +9568,7 @@
         <v>0</v>
       </c>
       <c r="E192">
-        <v>0.35599999999999998</v>
+        <v>0.315</v>
       </c>
       <c r="F192">
         <v>0</v>
@@ -9580,10 +9577,10 @@
         <v>0</v>
       </c>
       <c r="H192">
-        <v>15.534000000000001</v>
+        <v>12.173999999999999</v>
       </c>
       <c r="I192">
-        <v>598.5</v>
+        <v>529.82500000000005</v>
       </c>
       <c r="J192" t="s">
         <v>17</v>
@@ -9592,7 +9589,7 @@
         <v>0</v>
       </c>
       <c r="L192">
-        <v>1.746</v>
+        <v>1.5449999999999999</v>
       </c>
       <c r="M192">
         <v>0</v>
@@ -9601,24 +9598,24 @@
         <v>46247</v>
       </c>
       <c r="O192" s="3">
-        <v>0.84560185185185188</v>
+        <v>0.84541666666666671</v>
       </c>
     </row>
     <row r="193" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A193" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B193">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="C193" t="s">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="D193">
         <v>0</v>
       </c>
       <c r="E193">
-        <v>0.49</v>
+        <v>0.308</v>
       </c>
       <c r="F193">
         <v>0</v>
@@ -9627,10 +9624,10 @@
         <v>0</v>
       </c>
       <c r="H193">
-        <v>29.385000000000002</v>
+        <v>11.608000000000001</v>
       </c>
       <c r="I193">
-        <v>823.15599999999995</v>
+        <v>517.36800000000005</v>
       </c>
       <c r="J193" t="s">
         <v>17</v>
@@ -9639,7 +9636,7 @@
         <v>0</v>
       </c>
       <c r="L193">
-        <v>2.4009999999999998</v>
+        <v>1.5089999999999999</v>
       </c>
       <c r="M193">
         <v>0</v>
@@ -9648,288 +9645,6 @@
         <v>46247</v>
       </c>
       <c r="O193" s="3">
-        <v>0.84018518518518515</v>
-      </c>
-    </row>
-    <row r="194" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A194" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B194">
-        <v>17</v>
-      </c>
-      <c r="C194" t="s">
-        <v>0</v>
-      </c>
-      <c r="D194">
-        <v>0</v>
-      </c>
-      <c r="E194">
-        <v>0.45300000000000001</v>
-      </c>
-      <c r="F194">
-        <v>0</v>
-      </c>
-      <c r="G194">
-        <v>0</v>
-      </c>
-      <c r="H194">
-        <v>25.131</v>
-      </c>
-      <c r="I194">
-        <v>761.24800000000005</v>
-      </c>
-      <c r="J194" t="s">
-        <v>17</v>
-      </c>
-      <c r="K194">
-        <v>0</v>
-      </c>
-      <c r="L194">
-        <v>2.2210000000000001</v>
-      </c>
-      <c r="M194">
-        <v>0</v>
-      </c>
-      <c r="N194" s="2">
-        <v>46247</v>
-      </c>
-      <c r="O194" s="3">
-        <v>0.84107638888888892</v>
-      </c>
-    </row>
-    <row r="195" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A195" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B195">
-        <v>21</v>
-      </c>
-      <c r="C195" t="s">
-        <v>0</v>
-      </c>
-      <c r="D195">
-        <v>0</v>
-      </c>
-      <c r="E195">
-        <v>0.48899999999999999</v>
-      </c>
-      <c r="F195">
-        <v>0</v>
-      </c>
-      <c r="G195">
-        <v>0</v>
-      </c>
-      <c r="H195">
-        <v>29.314</v>
-      </c>
-      <c r="I195">
-        <v>822.16</v>
-      </c>
-      <c r="J195" t="s">
-        <v>17</v>
-      </c>
-      <c r="K195">
-        <v>0</v>
-      </c>
-      <c r="L195">
-        <v>2.3980000000000001</v>
-      </c>
-      <c r="M195">
-        <v>0</v>
-      </c>
-      <c r="N195" s="2">
-        <v>46247</v>
-      </c>
-      <c r="O195" s="3">
-        <v>0.84189814814814812</v>
-      </c>
-    </row>
-    <row r="196" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A196" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B196">
-        <v>25</v>
-      </c>
-      <c r="C196" t="s">
-        <v>19</v>
-      </c>
-      <c r="D196">
-        <v>0</v>
-      </c>
-      <c r="E196">
-        <v>0.308</v>
-      </c>
-      <c r="F196">
-        <v>0</v>
-      </c>
-      <c r="G196">
-        <v>70</v>
-      </c>
-      <c r="H196">
-        <v>11.661</v>
-      </c>
-      <c r="I196">
-        <v>1037.104</v>
-      </c>
-      <c r="J196" t="s">
-        <v>17</v>
-      </c>
-      <c r="K196">
-        <v>0</v>
-      </c>
-      <c r="L196">
-        <v>1.5129999999999999</v>
-      </c>
-      <c r="M196">
-        <v>0</v>
-      </c>
-      <c r="N196" s="2">
-        <v>46247</v>
-      </c>
-      <c r="O196" s="3">
-        <v>0.84288194444444442</v>
-      </c>
-    </row>
-    <row r="197" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A197" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B197">
-        <v>29</v>
-      </c>
-      <c r="C197" t="s">
-        <v>19</v>
-      </c>
-      <c r="D197">
-        <v>0</v>
-      </c>
-      <c r="E197">
-        <v>0.34899999999999998</v>
-      </c>
-      <c r="F197">
-        <v>0</v>
-      </c>
-      <c r="G197">
-        <v>70</v>
-      </c>
-      <c r="H197">
-        <v>14.974</v>
-      </c>
-      <c r="I197">
-        <v>1175.2339999999999</v>
-      </c>
-      <c r="J197" t="s">
-        <v>17</v>
-      </c>
-      <c r="K197">
-        <v>0</v>
-      </c>
-      <c r="L197">
-        <v>1.714</v>
-      </c>
-      <c r="M197">
-        <v>0</v>
-      </c>
-      <c r="N197" s="2">
-        <v>46247</v>
-      </c>
-      <c r="O197" s="3">
-        <v>0.84378472222222223</v>
-      </c>
-    </row>
-    <row r="198" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A198" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B198">
-        <v>33</v>
-      </c>
-      <c r="C198" t="s">
-        <v>18</v>
-      </c>
-      <c r="D198">
-        <v>0</v>
-      </c>
-      <c r="E198">
-        <v>0.315</v>
-      </c>
-      <c r="F198">
-        <v>0</v>
-      </c>
-      <c r="G198">
-        <v>0</v>
-      </c>
-      <c r="H198">
-        <v>12.173999999999999</v>
-      </c>
-      <c r="I198">
-        <v>529.82500000000005</v>
-      </c>
-      <c r="J198" t="s">
-        <v>17</v>
-      </c>
-      <c r="K198">
-        <v>0</v>
-      </c>
-      <c r="L198">
-        <v>1.5449999999999999</v>
-      </c>
-      <c r="M198">
-        <v>0</v>
-      </c>
-      <c r="N198" s="2">
-        <v>46247</v>
-      </c>
-      <c r="O198" s="3">
-        <v>0.84541666666666671</v>
-      </c>
-    </row>
-    <row r="199" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A199" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B199">
-        <v>37</v>
-      </c>
-      <c r="C199" t="s">
-        <v>18</v>
-      </c>
-      <c r="D199">
-        <v>0</v>
-      </c>
-      <c r="E199">
-        <v>0.308</v>
-      </c>
-      <c r="F199">
-        <v>0</v>
-      </c>
-      <c r="G199">
-        <v>0</v>
-      </c>
-      <c r="H199">
-        <v>11.608000000000001</v>
-      </c>
-      <c r="I199">
-        <v>517.36800000000005</v>
-      </c>
-      <c r="J199" t="s">
-        <v>17</v>
-      </c>
-      <c r="K199">
-        <v>0</v>
-      </c>
-      <c r="L199">
-        <v>1.5089999999999999</v>
-      </c>
-      <c r="M199">
-        <v>0</v>
-      </c>
-      <c r="N199" s="2">
-        <v>46247</v>
-      </c>
-      <c r="O199" s="3">
         <v>0.84620370370370368</v>
       </c>
     </row>
